--- a/docs/Severance Design Docs.xlsx
+++ b/docs/Severance Design Docs.xlsx
@@ -15,11 +15,12 @@
     <sheet name="Base Moves" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Boss Specials" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Damage Table" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Balance Log" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sim Results" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Balance Log" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Balance Log'!$A$4:$G$30</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Order'!$A$4:$H$20</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Balance Log'!$A$4:$G$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Order'!$A$4:$H$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="522">
   <si>
     <t xml:space="preserve">Severance - Monster Stats</t>
   </si>
@@ -258,6 +259,9 @@
     <t xml:space="preserve">Planned (mana class)</t>
   </si>
   <si>
+    <t xml:space="preserve">Planned: Paladin Faith bar (fills when you take damage, buffs your next ability when full). See the Sim Results tab.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paladin Abilities</t>
   </si>
   <si>
@@ -843,7 +847,7 @@
     <t xml:space="preserve">Mana bar</t>
   </si>
   <si>
-    <t xml:space="preserve">show_mana_bar in player.py, show MP cost in the menu</t>
+    <t xml:space="preserve">show_mana_bar in player.py, MP cost in the menu. Tested in a sim</t>
   </si>
   <si>
     <t xml:space="preserve">Sorcerer class + Mana Tide</t>
@@ -861,6 +865,27 @@
     <t xml:space="preserve">Tune stats + mana costs</t>
   </si>
   <si>
+    <t xml:space="preserve">Paladin Faith bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micha (mechanic) + Claude (numbers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fills when you take damage. When full, your next ability gets a power buff, then it empties. Sims on the Sim Results tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-tune enemies for Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All dungeons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith makes the Paladin stronger, so enemies need a small buff to keep the same difficulty</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial tips per room</t>
   </si>
   <si>
@@ -870,18 +895,12 @@
     <t xml:space="preserve">XP rework: small XP from enemies, big from bosses</t>
   </si>
   <si>
-    <t xml:space="preserve">All dungeons</t>
-  </si>
-  <si>
     <t xml:space="preserve">Numbers only. Suggested split is on Dungeon Plans</t>
   </si>
   <si>
     <t xml:space="preserve">Cheetah Growl (stun)</t>
   </si>
   <si>
-    <t xml:space="preserve">Micha (mechanic) + Claude (numbers)</t>
-  </si>
-  <si>
     <t xml:space="preserve">stunned flag, Move effect, skip turn. No damage vs 0.5x hit undecided</t>
   </si>
   <si>
@@ -909,6 +928,9 @@
     <t xml:space="preserve">Micha (mechanic) + Claude (stats)</t>
   </si>
   <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Boss adds enemies to the fight mid-battle</t>
   </si>
   <si>
@@ -927,7 +949,7 @@
     <t xml:space="preserve">Outpost</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
+    <t xml:space="preserve">14</t>
   </si>
   <si>
     <t xml:space="preserve">Enemies/bosses drop gold, spend at a shop between dungeons (e.g. mana potions)</t>
@@ -1093,6 +1115,144 @@
   </si>
   <si>
     <t xml:space="preserve">Enraged Devastating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severance - Simulation Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each number = 4,000 simulated full runs of the dungeon (run by Claude, 1 Oct 2026). Smart = reacts to warnings and uses abilities well. Casual = uses whatever is ready, ignores warnings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idea: Paladin Faith Bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Faith fills up when the Paladin takes damage (e.g. 2 Faith for every 1 HP lost, full at 100).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  When Faith is full, the next ability you use gets a power buff (more damage or more healing), then Faith empties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Fits the tank role: the Paladin gets stronger by taking hits. Plays differently from the Sorcerer's mana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Open questions: how big the buff is, whether Faith resets each room or carries over, and whether Defend / Divine Aegis add Faith.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status: idea only, not in the code yet. Build Order steps 6-7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 1: Should the Paladin have a bar? (Holy Strike costs from the bar, keeps its 4-turn cooldown)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainforest Lv1 - Smart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainforest Lv1 - Casual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spaceship Lv2 - Smart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spaceship Lv2 - Casual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takeaway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No bar (current game)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana 50, Holy Strike costs 10, +2 per turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never runs out: the bar is just decoration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana 50, Holy Strike costs 20, +3 per turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Much harder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana 50, Holy Strike costs 20, +2 per turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Far too hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana 40, Holy Strike costs 20, no regen, refills on rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best mana option: ~2 Holy Strikes per room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve: fills from damage taken, Holy Strike costs 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fits a tank, hard for casual players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve: fills from damage taken, Holy Strike costs 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result: Faith (below) was picked over mana and Resolve. It doesn't lock abilities, it rewards taking hits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 2: Faith bar - fills from damage taken, buffs your next ability when full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buffs per Rainforest run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buffs per Spaceship run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP left after Rainforest (smart)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 2 per HP lost, full=100, +25%, resets each room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 1 per HP lost, full=100, +25%, resets each room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 1 per HP lost, full=100, +50%, resets each room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 1 per HP lost, full=50, +50%, resets each room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 2 per HP lost, full=100, +50%, resets each room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 2 per HP lost, full=100, +50%, kept between rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 2 per HP lost, full=100, +25%, kept between rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 2 per HP lost, full=100, +100%, kept between rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith: 3 per HP lost, full=100, +50%, kept between rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Every Faith version makes the game easier, because it's a free buff. Bigger buff or Faith carried between rooms = easier still.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  '1 per HP lost, full at 100, resets each room' almost never fills (0.1 buffs per run), so it does nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Suggested start (green): 2 Faith per HP lost, full at 100, +25% buff, resets each room. About 1-2 buffs per dungeon, +5% smart / +9% casual win rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  After adding Faith, re-tune enemies slightly (Build Order step 7) to get back to the old difficulty.</t>
   </si>
   <si>
     <t xml:space="preserve">Balance Log</t>
@@ -1534,7 +1694,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1568,7 +1728,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6E9F3"/>
-        <bgColor rgb="FFE3F1E3"/>
+        <bgColor rgb="FFEEF0F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF0F4"/>
+        <bgColor rgb="FFE6E9F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -1621,7 +1787,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1802,6 +1968,62 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1909,7 +2131,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF4D6"/>
-      <rgbColor rgb="FFE6E9F3"/>
+      <rgbColor rgb="FFEEF0F4"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1923,9 +2145,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFE6E9F3"/>
+      <rgbColor rgb="FFE3F1E3"/>
       <rgbColor rgb="FFF3E6E6"/>
-      <rgbColor rgb="FFE3F1E3"/>
-      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -3074,61 +3296,66 @@
         <v>74</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="20" t="n">
         <v>1</v>
@@ -3140,7 +3367,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="20" t="n">
         <v>0</v>
@@ -3161,18 +3388,18 @@
         <v>38</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" s="20" t="n">
         <v>1</v>
@@ -3184,7 +3411,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" s="20" t="n">
         <v>0</v>
@@ -3205,18 +3432,18 @@
         <v>58</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" s="20" t="n">
         <v>2</v>
@@ -3228,7 +3455,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H13" s="20" t="n">
         <v>0</v>
@@ -3249,18 +3476,18 @@
         <v>38</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D14" s="20" t="n">
         <v>5</v>
@@ -3272,7 +3499,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H14" s="20" t="n">
         <v>0</v>
@@ -3293,18 +3520,18 @@
         <v>87 HP</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D15" s="20" t="n">
         <v>9</v>
@@ -3316,7 +3543,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="20" t="n">
         <v>0</v>
@@ -3329,24 +3556,24 @@
         <v>18</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D16" s="20" t="n">
         <v>13</v>
@@ -3358,7 +3585,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" s="20" t="n">
         <v>0</v>
@@ -3379,18 +3606,18 @@
         <v>46</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" s="20" t="n">
         <v>20</v>
@@ -3402,7 +3629,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" s="20" t="n">
         <v>0</v>
@@ -3423,30 +3650,30 @@
         <v>116</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
@@ -3458,13 +3685,13 @@
         <v>11</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3496,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4128,7 +4355,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4167,58 +4394,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4229,37 +4456,37 @@
         <v>19</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H6" s="26" t="s">
         <v>28</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K6" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4270,37 +4497,37 @@
         <v>33</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M7" s="26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4308,40 +4535,40 @@
         <v>3</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L8" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4349,13 +4576,13 @@
         <v>22</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>22</v>
@@ -4364,53 +4591,53 @@
         <v>22</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H9" s="26" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K9" s="28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L9" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M9" s="26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -4427,25 +4654,25 @@
         <v>19</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D13" s="26" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
       <c r="K13" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4456,25 +4683,25 @@
         <v>19</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>36</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
       <c r="K14" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4485,25 +4712,25 @@
         <v>19</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4517,22 +4744,22 @@
         <v>30</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
       <c r="K16" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4543,23 +4770,23 @@
         <v>33</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
       <c r="K17" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4570,23 +4797,23 @@
         <v>33</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>36</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
       <c r="J18" s="26"/>
       <c r="K18" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4597,25 +4824,25 @@
         <v>33</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="F19" s="26" t="s">
-        <v>205</v>
-      </c>
       <c r="G19" s="26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
       <c r="K19" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4626,25 +4853,25 @@
         <v>33</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>30</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F20" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
       <c r="K20" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4655,25 +4882,25 @@
         <v>33</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D21" s="26" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
       <c r="K21" s="27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4684,25 +4911,25 @@
         <v>33</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F22" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
       <c r="J22" s="26"/>
       <c r="K22" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4710,16 +4937,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D23" s="26" t="s">
         <v>5</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>22</v>
@@ -4729,7 +4956,7 @@
       <c r="I23" s="26"/>
       <c r="J23" s="26"/>
       <c r="K23" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4737,28 +4964,28 @@
         <v>3</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F24" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
       <c r="K24" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4766,28 +4993,28 @@
         <v>3</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D25" s="26" t="s">
         <v>5</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
       <c r="K25" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4795,16 +5022,16 @@
         <v>3</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F26" s="26" t="s">
         <v>22</v>
@@ -4814,7 +5041,7 @@
       <c r="I26" s="26"/>
       <c r="J26" s="26"/>
       <c r="K26" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4822,28 +5049,28 @@
         <v>3</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>5</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F27" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
       <c r="J27" s="26"/>
       <c r="K27" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4851,93 +5078,93 @@
         <v>3</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D28" s="26" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
       <c r="J28" s="26"/>
       <c r="K28" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="30" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -4953,7 +5180,7 @@
         <v>18</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>5</v>
@@ -4968,7 +5195,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>8</v>
@@ -4983,7 +5210,7 @@
         <v>26</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>12</v>
@@ -4995,10 +5222,10 @@
     <row r="45" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="26"/>
       <c r="B45" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>245</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>30</v>
@@ -5013,7 +5240,7 @@
         <v>32</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>6</v>
@@ -5028,7 +5255,7 @@
         <v>35</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>16</v>
@@ -5043,7 +5270,7 @@
         <v>37</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>14</v>
@@ -5055,10 +5282,10 @@
     <row r="49" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="26"/>
       <c r="B49" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="26" t="s">
         <v>248</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>247</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>45</v>
@@ -5069,7 +5296,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D50" s="31" t="n">
         <f aca="false">2*D42+3*D43+D44+D45</f>
@@ -5082,7 +5309,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D51" s="31" t="n">
         <f aca="false">2*D42+3*D43+D44</f>
@@ -5095,7 +5322,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D52" s="31" t="n">
         <f aca="false">5*D46+D47+2*D48+D49</f>
@@ -5108,7 +5335,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D53" s="31" t="n">
         <f aca="false">5*D46+D47+2*D48</f>
@@ -5121,7 +5348,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -5159,7 +5386,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
@@ -5174,32 +5401,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>49</v>
@@ -5213,25 +5440,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F5" s="33" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5239,51 +5466,51 @@
         <v>2</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="H6" s="34" t="s">
         <v>267</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F7" s="33" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>172</v>
+        <v>271</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5291,25 +5518,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>72</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F8" s="33" t="s">
         <v>27</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5317,51 +5544,51 @@
         <v>5</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C9" s="26" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>264</v>
+        <v>158</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5369,51 +5596,51 @@
         <v>7</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>22</v>
+        <v>282</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F12" s="33" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H12" s="36" t="s">
-        <v>284</v>
+        <v>285</v>
+      </c>
+      <c r="H12" s="35" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5421,16 +5648,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
       <c r="F13" s="33" t="s">
         <v>22</v>
@@ -5439,10 +5666,10 @@
         <v>287</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
@@ -5450,13 +5677,13 @@
         <v>288</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
       <c r="F14" s="33" t="s">
         <v>22</v>
@@ -5464,8 +5691,8 @@
       <c r="G14" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="H14" s="35" t="s">
-        <v>172</v>
+      <c r="H14" s="36" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5473,42 +5700,42 @@
         <v>11</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>247</v>
+        <v>164</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>189</v>
+        <v>22</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>110</v>
+        <v>248</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>294</v>
+        <v>158</v>
       </c>
       <c r="F16" s="33" t="s">
         <v>22</v>
@@ -5517,7 +5744,7 @@
         <v>295</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5528,13 +5755,13 @@
         <v>296</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>263</v>
-      </c>
       <c r="E17" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F17" s="33" t="s">
         <v>298</v>
@@ -5543,7 +5770,7 @@
         <v>299</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5554,10 +5781,10 @@
         <v>300</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E18" s="33" t="s">
         <v>301</v>
@@ -5569,10 +5796,10 @@
         <v>302</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
@@ -5580,53 +5807,105 @@
         <v>303</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>110</v>
+        <v>304</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="C20" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="E20" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>172</v>
+      <c r="G21" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H21" s="35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="H22" s="35" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H20"/>
-  <conditionalFormatting sqref="H5:H20">
+  <autoFilter ref="A4:H22"/>
+  <conditionalFormatting sqref="H5:H22">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Done"</formula>
     </cfRule>
@@ -5641,7 +5920,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H20" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H22" type="list">
       <formula1>"Done,In progress,Not started,Undecided"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5675,32 +5954,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5717,15 +5996,15 @@
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B6" s="37" t="n">
         <v>0.2</v>
@@ -5737,15 +6016,15 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B7" s="37" t="n">
         <v>0.2</v>
@@ -5757,15 +6036,15 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B8" s="37" t="n">
         <v>0.1</v>
@@ -5777,15 +6056,15 @@
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>22</v>
@@ -5797,15 +6076,15 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B11" s="39" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -5843,12 +6122,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5856,31 +6135,31 @@
         <v>30</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5916,7 +6195,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5924,7 +6203,7 @@
         <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C6" s="37" t="n">
         <v>0.2</v>
@@ -5952,7 +6231,7 @@
         <v>34</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5960,7 +6239,7 @@
         <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C7" s="37" t="n">
         <v>0.15</v>
@@ -5988,7 +6267,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6024,7 +6303,7 @@
         <v>119</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6032,7 +6311,7 @@
         <v>47</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C9" s="37" t="n">
         <v>0.15</v>
@@ -6060,7 +6339,7 @@
         <v>189</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6068,7 +6347,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C10" s="37" t="n">
         <v>0.15</v>
@@ -6096,7 +6375,7 @@
         <v>113</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6104,7 +6383,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C11" s="37" t="n">
         <v>0.1</v>
@@ -6132,12 +6411,12 @@
         <v>88</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -6169,12 +6448,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6185,22 +6464,22 @@
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6657,6 +6936,553 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="45" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="46" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="47" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="48" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="48" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="48" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="48" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="46" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="47" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" s="50" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D13" s="50" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="F14" s="51" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="51" t="s">
+        <v>380</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="F16" s="51" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="51" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17" s="25" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D17" s="25" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="51" t="s">
+        <v>386</v>
+      </c>
+      <c r="B18" s="25" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="51" t="s">
+        <v>388</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="46" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="47" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="B24" s="50" t="n">
+        <v>0.86625</v>
+      </c>
+      <c r="C24" s="50" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="D24" s="50" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="E24" s="50" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="F24" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="53" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="54" t="s">
+        <v>394</v>
+      </c>
+      <c r="B25" s="55" t="n">
+        <v>0.91575</v>
+      </c>
+      <c r="C25" s="55" t="n">
+        <v>0.72775</v>
+      </c>
+      <c r="D25" s="55" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="E25" s="55" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F25" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H25" s="57" t="n">
+        <v>0.258333333333333</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="51" t="s">
+        <v>395</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>0.92425</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>0.63175</v>
+      </c>
+      <c r="F26" s="58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="51" t="s">
+        <v>396</v>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>0.87675</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>0.9285</v>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>0.62375</v>
+      </c>
+      <c r="F27" s="58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="51" t="s">
+        <v>397</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>0.95275</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="D28" s="25" t="n">
+        <v>0.9685</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="F28" s="58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G28" s="58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>0.308333333333333</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="51" t="s">
+        <v>398</v>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>0.815</v>
+      </c>
+      <c r="D29" s="25" t="n">
+        <v>0.9635</v>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>0.78075</v>
+      </c>
+      <c r="F29" s="58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G29" s="58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>0.304166666666667</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="D30" s="25" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="F30" s="58" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G30" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>0.316666666666667</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="51" t="s">
+        <v>400</v>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>0.93475</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="D31" s="25" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>0.75075</v>
+      </c>
+      <c r="F31" s="58" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G31" s="58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>0.266666666666667</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="51" t="s">
+        <v>401</v>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>0.98525</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>0.90425</v>
+      </c>
+      <c r="D32" s="25" t="n">
+        <v>0.99625</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="F32" s="58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G32" s="58" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="51" t="s">
+        <v>402</v>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>0.8385</v>
+      </c>
+      <c r="D33" s="25" t="n">
+        <v>0.98725</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="F33" s="58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G33" s="58" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="48" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="48" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="48" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="48" t="s">
+        <v>406</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6674,633 +7500,633 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>354</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>362</v>
+        <v>415</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>364</v>
+        <v>417</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>362</v>
+        <v>415</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>373</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>376</v>
+        <v>429</v>
       </c>
       <c r="D7" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>378</v>
+        <v>431</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>379</v>
+        <v>432</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>380</v>
+        <v>433</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>393</v>
+        <v>446</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>395</v>
+        <v>448</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>397</v>
+        <v>450</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>376</v>
+        <v>429</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>399</v>
+        <v>452</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>400</v>
+        <v>453</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>401</v>
+        <v>454</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>402</v>
+        <v>455</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>403</v>
+        <v>456</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>408</v>
+        <v>461</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>409</v>
+        <v>462</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>410</v>
+        <v>463</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>411</v>
+        <v>464</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>414</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>417</v>
+        <v>470</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>421</v>
+        <v>474</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>423</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>424</v>
+        <v>477</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>425</v>
+        <v>478</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>426</v>
+        <v>479</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>427</v>
+        <v>480</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>428</v>
+        <v>481</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>429</v>
+        <v>482</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>430</v>
+        <v>483</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>431</v>
+        <v>484</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>432</v>
+        <v>485</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>433</v>
+        <v>486</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>436</v>
+        <v>489</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>437</v>
+        <v>490</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>438</v>
+        <v>491</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>439</v>
+        <v>492</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>441</v>
+        <v>494</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>443</v>
+        <v>496</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>444</v>
+        <v>497</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>445</v>
+        <v>498</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>446</v>
+        <v>499</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>430</v>
+        <v>483</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>447</v>
+        <v>500</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>448</v>
+        <v>501</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>450</v>
+        <v>503</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>451</v>
+        <v>504</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>452</v>
+        <v>505</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>453</v>
+        <v>506</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>454</v>
+        <v>507</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>456</v>
+        <v>509</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>457</v>
+        <v>510</v>
       </c>
       <c r="D28" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>458</v>
+        <v>511</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>459</v>
+        <v>512</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>460</v>
+        <v>513</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>461</v>
+        <v>514</v>
       </c>
       <c r="D29" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>462</v>
+        <v>515</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>463</v>
+        <v>516</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>464</v>
+        <v>517</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>465</v>
+        <v>518</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>466</v>
+        <v>519</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>467</v>
+        <v>520</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>468</v>
+        <v>521</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Severance Design Docs.xlsx
+++ b/docs/Severance Design Docs.xlsx
@@ -19,8 +19,8 @@
     <sheet name="Balance Log" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Balance Log'!$A$4:$G$30</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Order'!$A$4:$H$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Balance Log'!$A$4:$G$32</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Order'!$A$4:$H$24</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="578">
   <si>
     <t xml:space="preserve">Severance - Monster Stats</t>
   </si>
@@ -238,7 +238,7 @@
     <t xml:space="preserve">Max Mana</t>
   </si>
   <si>
-    <t xml:space="preserve">Mana Regen</t>
+    <t xml:space="preserve">Mana Regen per Turn</t>
   </si>
   <si>
     <t xml:space="preserve">Max Level</t>
@@ -256,12 +256,12 @@
     <t xml:space="preserve">Magic</t>
   </si>
   <si>
-    <t xml:space="preserve">Planned (mana class)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Planned: Paladin Faith bar (fills when you take damage, buffs your next ability when full). See the Sim Results tab.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sorcerer starts every dungeon with full mana and regenerates mana each turn. Its abilities use the elements from the Sorcerer note.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paladin Abilities</t>
   </si>
   <si>
@@ -394,10 +394,7 @@
     <t xml:space="preserve">Ultimate: 4x attack</t>
   </si>
   <si>
-    <t xml:space="preserve">Raw Effect = damage before the enemy's defence and the ±20% random roll (see the Damage Table tab for after-defence numbers).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heals use max HP at that level. Lifesteal heals 50% of the damage that actually lands.</t>
+    <t xml:space="preserve">Raw Effect = damage before the enemy's defence and the ±20% random roll (see the Damage Table tab).</t>
   </si>
   <si>
     <t xml:space="preserve">Paladin Stats by Level</t>
@@ -421,6 +418,78 @@
     <t xml:space="preserve">Starts with Shield Bash, Holy Strike</t>
   </si>
   <si>
+    <t xml:space="preserve">Sorcerer Abilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Bolt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire. Cheap main attack, usable almost every turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana Tide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water. Restores 40% of max mana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain Lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning. Hits every enemy for 1.2x attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frost Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice. Heals 20% of max HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wind Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wind. Blocks ALL damage for the rest of the turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steam Burst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire + Water. 1.8x hit, heals you for half the damage dealt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth + Fire. Ultimate: 4.5x attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorcerer Stats by Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with Fire Bolt, Mana Tide</t>
+  </si>
+  <si>
     <t xml:space="preserve">XP to Next Level = 50 x level (from xp_needed() in player.py). Levelling up fully heals you.</t>
   </si>
   <si>
@@ -850,10 +919,19 @@
     <t xml:space="preserve">show_mana_bar in player.py, MP cost in the menu. Tested in a sim</t>
   </si>
   <si>
+    <t xml:space="preserve">Simulation script (sims/simulate.py)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micha + Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs 1,000 dungeons with a smart bot and a mash bot, pick the class. Run with: python -m sims.simulate</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sorcerer class + Mana Tide</t>
   </si>
   <si>
-    <t xml:space="preserve">Add to class select. Add tests: can't cast without mana, regen caps at max</t>
+    <t xml:space="preserve">ManaAbility, 7 elemental abilities, class select. Add tests: can't cast without mana, regen caps at max</t>
   </si>
   <si>
     <t xml:space="preserve">Sorcerer balance sims</t>
@@ -862,7 +940,16 @@
     <t xml:space="preserve">Claude</t>
   </si>
   <si>
-    <t xml:space="preserve">Tune stats + mana costs</t>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainforest: 35% -&gt; 86% after 100 HP, 5 Def, Fire Bolt 1.8x. Results on Sim Results tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smarter sim bot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use AOE when 2+ enemies, strongest ability first. Current bot uses abilities in menu order, so Spaceship numbers are low</t>
   </si>
   <si>
     <t xml:space="preserve">Paladin Faith bar</t>
@@ -880,7 +967,7 @@
     <t xml:space="preserve">All dungeons</t>
   </si>
   <si>
-    <t xml:space="preserve">6</t>
+    <t xml:space="preserve">8</t>
   </si>
   <si>
     <t xml:space="preserve">Faith makes the Paladin stronger, so enemies need a small buff to keep the same difficulty</t>
@@ -928,7 +1015,7 @@
     <t xml:space="preserve">Micha (mechanic) + Claude (stats)</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
+    <t xml:space="preserve">14</t>
   </si>
   <si>
     <t xml:space="preserve">Boss adds enemies to the fight mid-battle</t>
@@ -949,9 +1036,6 @@
     <t xml:space="preserve">Outpost</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Enemies/bosses drop gold, spend at a shop between dungeons (e.g. mana potions)</t>
   </si>
   <si>
@@ -1255,6 +1339,66 @@
     <t xml:space="preserve">•  After adding Faith, re-tune enemies slightly (Build Order step 7) to get back to the old difficulty.</t>
   </si>
   <si>
+    <t xml:space="preserve">Test 3: Sorcerer stats - Rainforest at Lv 1 (Micha's simulate.py, 3,000 runs each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart bot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mash bot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paladin (for comparison)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target to match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorcerer first version: 90 HP, 3 Def, Fire Bolt 1.6x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Far too fragile: Pounce kills it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110 HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP is the big fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110 HP, 5 Def</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 HP, 5 Def, Defend ÷3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Bolt every turn (cooldown 0), 90 HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More damage doesn't help without HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 HP, Fire Bolt cooldown 0, +6 regen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 HP, 5 Def, Fire Bolt 1.8x (chosen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the Paladin, still squishier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105 HP, 5 Def, Fire Bolt 1.8x, +5 regen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110 HP, 6 Def, Fire Bolt 1.8x, +5 regen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spaceship at Lv 2 with the same bot: Paladin 48%, Sorcerer 61%. Low for both because the bot uses abilities in menu order (no AOE priority) - see Build Order step 7.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Balance Log</t>
   </si>
   <si>
@@ -1598,13 +1742,37 @@
   </si>
   <si>
     <t xml:space="preserve">Longer dungeon, same difficulty (2 keeps XP under the Lv 2 trap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorcerer class added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 HP / 13 Atk / 3 Def, 60 mana, +4 regen, Fire Bolt 1.6x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second playable class (Magic DPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorcerer HP / Defence / Fire Bolt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 / 3 / 1.6x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 / 5 / 1.8x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart bot only won 35% of Rainforest runs (Paladin 88%). Now 86%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation (Micha's simulate.py)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="General"/>
@@ -1612,6 +1780,7 @@
     <numFmt numFmtId="168" formatCode="0.0\x"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0.00\x"/>
+    <numFmt numFmtId="171" formatCode="0.00\x"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1787,7 +1956,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1868,6 +2037,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1940,7 +2125,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1948,7 +2133,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1968,32 +2153,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3132,38 +3297,38 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
@@ -3207,1155 +3372,2203 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="24" t="n">
         <v>120</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="25" t="n">
         <f aca="false">1-1/I6</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="20" t="n">
+      <c r="L6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="20" t="n">
+      <c r="M6" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="N6" s="22" t="s">
+      <c r="N6" s="26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <f aca="false">1-1/I7</f>
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="N7" s="26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="J13" s="26" t="n">
+        <f aca="false">INDEX($C$24:$C$43,D13)</f>
+        <v>10</v>
+      </c>
+      <c r="K13" s="26" t="n">
+        <f aca="false">ROUND(J13*E13,0)</f>
+        <v>13</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <f aca="false">ROUND($C$43*E13,0)</f>
+        <v>38</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="J14" s="26" t="n">
+        <f aca="false">INDEX($C$24:$C$43,D14)</f>
+        <v>10</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <f aca="false">ROUND(J14*E14,0)</f>
+        <v>20</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <f aca="false">ROUND($C$43*E14,0)</f>
+        <v>58</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="J15" s="26" t="n">
+        <f aca="false">INDEX($C$24:$C$43,D15)</f>
+        <v>11</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <f aca="false">ROUND(J15*E15,0)</f>
+        <v>14</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <f aca="false">ROUND($C$43*E15,0)</f>
+        <v>38</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="J16" s="26" t="n">
+        <f aca="false">INDEX($C$24:$C$43,D16)</f>
+        <v>14</v>
+      </c>
+      <c r="K16" s="26" t="str">
+        <f aca="false">ROUND(INDEX($B$24:$B$43,D16)*E16,0)&amp;" HP"</f>
+        <v>42 HP</v>
+      </c>
+      <c r="L16" s="26" t="str">
+        <f aca="false">ROUND($B$43*E16,0)&amp;" HP"</f>
+        <v>87 HP</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="J17" s="26" t="n">
+        <f aca="false">INDEX($C$24:$C$43,D17)</f>
+        <v>18</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <f aca="false">INDEX($C$24:$C$43,D18)</f>
         <v>22</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="K18" s="26" t="n">
+        <f aca="false">ROUND(J18*E18,0)</f>
+        <v>35</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <f aca="false">ROUND($C$43*E18,0)</f>
+        <v>46</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J19" s="26" t="n">
+        <f aca="false">INDEX($C$24:$C$43,D19)</f>
+        <v>29</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <f aca="false">ROUND(J19*E19,0)</f>
+        <v>116</v>
+      </c>
+      <c r="L19" s="26" t="n">
+        <f aca="false">ROUND($C$43*E19,0)</f>
+        <v>116</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="26" t="n">
+        <f aca="false">$C$6+(A24-1)*$F$6</f>
+        <v>120</v>
+      </c>
+      <c r="C24" s="26" t="n">
+        <f aca="false">$D$6+(A24-1)*$G$6</f>
+        <v>10</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <f aca="false">$E$6+(A24-1)*$H$6</f>
+        <v>6</v>
+      </c>
+      <c r="E24" s="29" t="n">
+        <f aca="false">1-100/(100+D24)</f>
+        <v>0.0566037735849057</v>
+      </c>
+      <c r="F24" s="26" t="n">
+        <f aca="false">IF(A24&lt;$M$6,50*A24,"MAX")</f>
+        <v>50</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <f aca="false">25*A24*(A24-1)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="26" t="n">
+        <f aca="false">$C$6+(A25-1)*$F$6</f>
+        <v>132</v>
+      </c>
+      <c r="C25" s="26" t="n">
+        <f aca="false">$D$6+(A25-1)*$G$6</f>
+        <v>11</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <f aca="false">$E$6+(A25-1)*$H$6</f>
+        <v>9</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <f aca="false">1-100/(100+D25)</f>
+        <v>0.0825688073394495</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <f aca="false">IF(A25&lt;$M$6,50*A25,"MAX")</f>
+        <v>100</v>
+      </c>
+      <c r="G25" s="26" t="n">
+        <f aca="false">25*A25*(A25-1)</f>
+        <v>50</v>
+      </c>
+      <c r="H25" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A25,$D$13:$D$19,0)),"")</f>
+        <v>Holy Ground</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="26" t="n">
+        <f aca="false">$C$6+(A26-1)*$F$6</f>
+        <v>144</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <f aca="false">$D$6+(A26-1)*$G$6</f>
+        <v>12</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <f aca="false">$E$6+(A26-1)*$H$6</f>
+        <v>12</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <f aca="false">1-100/(100+D26)</f>
+        <v>0.107142857142857</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <f aca="false">IF(A26&lt;$M$6,50*A26,"MAX")</f>
+        <v>150</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <f aca="false">25*A26*(A26-1)</f>
+        <v>150</v>
+      </c>
+      <c r="H26" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A26,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="26" t="n">
+        <f aca="false">$C$6+(A27-1)*$F$6</f>
+        <v>156</v>
+      </c>
+      <c r="C27" s="26" t="n">
+        <f aca="false">$D$6+(A27-1)*$G$6</f>
+        <v>13</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <f aca="false">$E$6+(A27-1)*$H$6</f>
+        <v>15</v>
+      </c>
+      <c r="E27" s="29" t="n">
+        <f aca="false">1-100/(100+D27)</f>
+        <v>0.130434782608696</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <f aca="false">IF(A27&lt;$M$6,50*A27,"MAX")</f>
+        <v>200</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <f aca="false">25*A27*(A27-1)</f>
+        <v>300</v>
+      </c>
+      <c r="H27" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A27,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="26" t="n">
+        <f aca="false">$C$6+(A28-1)*$F$6</f>
+        <v>168</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <f aca="false">$D$6+(A28-1)*$G$6</f>
+        <v>14</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <f aca="false">$E$6+(A28-1)*$H$6</f>
+        <v>18</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <f aca="false">1-100/(100+D28)</f>
+        <v>0.152542372881356</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <f aca="false">IF(A28&lt;$M$6,50*A28,"MAX")</f>
+        <v>250</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <f aca="false">25*A28*(A28-1)</f>
+        <v>500</v>
+      </c>
+      <c r="H28" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A28,$D$13:$D$19,0)),"")</f>
+        <v>Lay on Hands</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="26" t="n">
+        <f aca="false">$C$6+(A29-1)*$F$6</f>
+        <v>180</v>
+      </c>
+      <c r="C29" s="26" t="n">
+        <f aca="false">$D$6+(A29-1)*$G$6</f>
+        <v>15</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <f aca="false">$E$6+(A29-1)*$H$6</f>
+        <v>21</v>
+      </c>
+      <c r="E29" s="29" t="n">
+        <f aca="false">1-100/(100+D29)</f>
+        <v>0.173553719008264</v>
+      </c>
+      <c r="F29" s="26" t="n">
+        <f aca="false">IF(A29&lt;$M$6,50*A29,"MAX")</f>
+        <v>300</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <f aca="false">25*A29*(A29-1)</f>
+        <v>750</v>
+      </c>
+      <c r="H29" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A29,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="26" t="n">
+        <f aca="false">$C$6+(A30-1)*$F$6</f>
+        <v>192</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <f aca="false">$D$6+(A30-1)*$G$6</f>
+        <v>16</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <f aca="false">$E$6+(A30-1)*$H$6</f>
+        <v>24</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <f aca="false">1-100/(100+D30)</f>
+        <v>0.193548387096774</v>
+      </c>
+      <c r="F30" s="26" t="n">
+        <f aca="false">IF(A30&lt;$M$6,50*A30,"MAX")</f>
+        <v>350</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <f aca="false">25*A30*(A30-1)</f>
+        <v>1050</v>
+      </c>
+      <c r="H30" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A30,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="26" t="n">
+        <f aca="false">$C$6+(A31-1)*$F$6</f>
+        <v>204</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <f aca="false">$D$6+(A31-1)*$G$6</f>
+        <v>17</v>
+      </c>
+      <c r="D31" s="26" t="n">
+        <f aca="false">$E$6+(A31-1)*$H$6</f>
+        <v>27</v>
+      </c>
+      <c r="E31" s="29" t="n">
+        <f aca="false">1-100/(100+D31)</f>
+        <v>0.21259842519685</v>
+      </c>
+      <c r="F31" s="26" t="n">
+        <f aca="false">IF(A31&lt;$M$6,50*A31,"MAX")</f>
+        <v>400</v>
+      </c>
+      <c r="G31" s="26" t="n">
+        <f aca="false">25*A31*(A31-1)</f>
+        <v>1400</v>
+      </c>
+      <c r="H31" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A31,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="26" t="n">
+        <f aca="false">$C$6+(A32-1)*$F$6</f>
+        <v>216</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <f aca="false">$D$6+(A32-1)*$G$6</f>
+        <v>18</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <f aca="false">$E$6+(A32-1)*$H$6</f>
+        <v>30</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <f aca="false">1-100/(100+D32)</f>
+        <v>0.230769230769231</v>
+      </c>
+      <c r="F32" s="26" t="n">
+        <f aca="false">IF(A32&lt;$M$6,50*A32,"MAX")</f>
+        <v>450</v>
+      </c>
+      <c r="G32" s="26" t="n">
+        <f aca="false">25*A32*(A32-1)</f>
+        <v>1800</v>
+      </c>
+      <c r="H32" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A32,$D$13:$D$19,0)),"")</f>
+        <v>Divine Aegis</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="26" t="n">
+        <f aca="false">$C$6+(A33-1)*$F$6</f>
+        <v>228</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <f aca="false">$D$6+(A33-1)*$G$6</f>
+        <v>19</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <f aca="false">$E$6+(A33-1)*$H$6</f>
+        <v>33</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <f aca="false">1-100/(100+D33)</f>
+        <v>0.24812030075188</v>
+      </c>
+      <c r="F33" s="26" t="n">
+        <f aca="false">IF(A33&lt;$M$6,50*A33,"MAX")</f>
+        <v>500</v>
+      </c>
+      <c r="G33" s="26" t="n">
+        <f aca="false">25*A33*(A33-1)</f>
+        <v>2250</v>
+      </c>
+      <c r="H33" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A33,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" s="26" t="n">
+        <f aca="false">$C$6+(A34-1)*$F$6</f>
+        <v>240</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <f aca="false">$D$6+(A34-1)*$G$6</f>
+        <v>20</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <f aca="false">$E$6+(A34-1)*$H$6</f>
+        <v>36</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <f aca="false">1-100/(100+D34)</f>
+        <v>0.264705882352941</v>
+      </c>
+      <c r="F34" s="26" t="n">
+        <f aca="false">IF(A34&lt;$M$6,50*A34,"MAX")</f>
+        <v>550</v>
+      </c>
+      <c r="G34" s="26" t="n">
+        <f aca="false">25*A34*(A34-1)</f>
+        <v>2750</v>
+      </c>
+      <c r="H34" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A34,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" s="26" t="n">
+        <f aca="false">$C$6+(A35-1)*$F$6</f>
+        <v>252</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <f aca="false">$D$6+(A35-1)*$G$6</f>
+        <v>21</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <f aca="false">$E$6+(A35-1)*$H$6</f>
+        <v>39</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <f aca="false">1-100/(100+D35)</f>
+        <v>0.280575539568345</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <f aca="false">IF(A35&lt;$M$6,50*A35,"MAX")</f>
+        <v>600</v>
+      </c>
+      <c r="G35" s="26" t="n">
+        <f aca="false">25*A35*(A35-1)</f>
+        <v>3300</v>
+      </c>
+      <c r="H35" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A35,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B36" s="26" t="n">
+        <f aca="false">$C$6+(A36-1)*$F$6</f>
+        <v>264</v>
+      </c>
+      <c r="C36" s="26" t="n">
+        <f aca="false">$D$6+(A36-1)*$G$6</f>
         <v>22</v>
       </c>
-      <c r="K7" s="22" t="s">
+      <c r="D36" s="26" t="n">
+        <f aca="false">$E$6+(A36-1)*$H$6</f>
+        <v>42</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <f aca="false">1-100/(100+D36)</f>
+        <v>0.295774647887324</v>
+      </c>
+      <c r="F36" s="26" t="n">
+        <f aca="false">IF(A36&lt;$M$6,50*A36,"MAX")</f>
+        <v>650</v>
+      </c>
+      <c r="G36" s="26" t="n">
+        <f aca="false">25*A36*(A36-1)</f>
+        <v>3900</v>
+      </c>
+      <c r="H36" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A36,$D$13:$D$19,0)),"")</f>
+        <v>Radiant Slash</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B37" s="26" t="n">
+        <f aca="false">$C$6+(A37-1)*$F$6</f>
+        <v>276</v>
+      </c>
+      <c r="C37" s="26" t="n">
+        <f aca="false">$D$6+(A37-1)*$G$6</f>
+        <v>23</v>
+      </c>
+      <c r="D37" s="26" t="n">
+        <f aca="false">$E$6+(A37-1)*$H$6</f>
+        <v>45</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <f aca="false">1-100/(100+D37)</f>
+        <v>0.310344827586207</v>
+      </c>
+      <c r="F37" s="26" t="n">
+        <f aca="false">IF(A37&lt;$M$6,50*A37,"MAX")</f>
+        <v>700</v>
+      </c>
+      <c r="G37" s="26" t="n">
+        <f aca="false">25*A37*(A37-1)</f>
+        <v>4550</v>
+      </c>
+      <c r="H37" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A37,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B38" s="26" t="n">
+        <f aca="false">$C$6+(A38-1)*$F$6</f>
+        <v>288</v>
+      </c>
+      <c r="C38" s="26" t="n">
+        <f aca="false">$D$6+(A38-1)*$G$6</f>
+        <v>24</v>
+      </c>
+      <c r="D38" s="26" t="n">
+        <f aca="false">$E$6+(A38-1)*$H$6</f>
+        <v>48</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <f aca="false">1-100/(100+D38)</f>
+        <v>0.324324324324324</v>
+      </c>
+      <c r="F38" s="26" t="n">
+        <f aca="false">IF(A38&lt;$M$6,50*A38,"MAX")</f>
+        <v>750</v>
+      </c>
+      <c r="G38" s="26" t="n">
+        <f aca="false">25*A38*(A38-1)</f>
+        <v>5250</v>
+      </c>
+      <c r="H38" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A38,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B39" s="26" t="n">
+        <f aca="false">$C$6+(A39-1)*$F$6</f>
+        <v>300</v>
+      </c>
+      <c r="C39" s="26" t="n">
+        <f aca="false">$D$6+(A39-1)*$G$6</f>
+        <v>25</v>
+      </c>
+      <c r="D39" s="26" t="n">
+        <f aca="false">$E$6+(A39-1)*$H$6</f>
+        <v>51</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <f aca="false">1-100/(100+D39)</f>
+        <v>0.337748344370861</v>
+      </c>
+      <c r="F39" s="26" t="n">
+        <f aca="false">IF(A39&lt;$M$6,50*A39,"MAX")</f>
+        <v>800</v>
+      </c>
+      <c r="G39" s="26" t="n">
+        <f aca="false">25*A39*(A39-1)</f>
+        <v>6000</v>
+      </c>
+      <c r="H39" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A39,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" s="26" t="n">
+        <f aca="false">$C$6+(A40-1)*$F$6</f>
+        <v>312</v>
+      </c>
+      <c r="C40" s="26" t="n">
+        <f aca="false">$D$6+(A40-1)*$G$6</f>
+        <v>26</v>
+      </c>
+      <c r="D40" s="26" t="n">
+        <f aca="false">$E$6+(A40-1)*$H$6</f>
+        <v>54</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <f aca="false">1-100/(100+D40)</f>
+        <v>0.350649350649351</v>
+      </c>
+      <c r="F40" s="26" t="n">
+        <f aca="false">IF(A40&lt;$M$6,50*A40,"MAX")</f>
+        <v>850</v>
+      </c>
+      <c r="G40" s="26" t="n">
+        <f aca="false">25*A40*(A40-1)</f>
+        <v>6800</v>
+      </c>
+      <c r="H40" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A40,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="B41" s="26" t="n">
+        <f aca="false">$C$6+(A41-1)*$F$6</f>
+        <v>324</v>
+      </c>
+      <c r="C41" s="26" t="n">
+        <f aca="false">$D$6+(A41-1)*$G$6</f>
+        <v>27</v>
+      </c>
+      <c r="D41" s="26" t="n">
+        <f aca="false">$E$6+(A41-1)*$H$6</f>
+        <v>57</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <f aca="false">1-100/(100+D41)</f>
+        <v>0.363057324840764</v>
+      </c>
+      <c r="F41" s="26" t="n">
+        <f aca="false">IF(A41&lt;$M$6,50*A41,"MAX")</f>
+        <v>900</v>
+      </c>
+      <c r="G41" s="26" t="n">
+        <f aca="false">25*A41*(A41-1)</f>
+        <v>7650</v>
+      </c>
+      <c r="H41" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A41,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B42" s="26" t="n">
+        <f aca="false">$C$6+(A42-1)*$F$6</f>
+        <v>336</v>
+      </c>
+      <c r="C42" s="26" t="n">
+        <f aca="false">$D$6+(A42-1)*$G$6</f>
+        <v>28</v>
+      </c>
+      <c r="D42" s="26" t="n">
+        <f aca="false">$E$6+(A42-1)*$H$6</f>
+        <v>60</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <f aca="false">1-100/(100+D42)</f>
+        <v>0.375</v>
+      </c>
+      <c r="F42" s="26" t="n">
+        <f aca="false">IF(A42&lt;$M$6,50*A42,"MAX")</f>
+        <v>950</v>
+      </c>
+      <c r="G42" s="26" t="n">
+        <f aca="false">25*A42*(A42-1)</f>
+        <v>8550</v>
+      </c>
+      <c r="H42" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A42,$D$13:$D$19,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B43" s="26" t="n">
+        <f aca="false">$C$6+(A43-1)*$F$6</f>
+        <v>348</v>
+      </c>
+      <c r="C43" s="26" t="n">
+        <f aca="false">$D$6+(A43-1)*$G$6</f>
+        <v>29</v>
+      </c>
+      <c r="D43" s="26" t="n">
+        <f aca="false">$E$6+(A43-1)*$H$6</f>
+        <v>63</v>
+      </c>
+      <c r="E43" s="29" t="n">
+        <f aca="false">1-100/(100+D43)</f>
+        <v>0.386503067484663</v>
+      </c>
+      <c r="F43" s="26" t="str">
+        <f aca="false">IF(A43&lt;$M$6,50*A43,"MAX")</f>
+        <v>MAX</v>
+      </c>
+      <c r="G43" s="26" t="n">
+        <f aca="false">25*A43*(A43-1)</f>
+        <v>9500</v>
+      </c>
+      <c r="H43" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A43,$D$13:$D$19,0)),"")</f>
+        <v>Judgement</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F48" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H48" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="22" t="s">
+      <c r="J48" s="26" t="n">
+        <f aca="false">INDEX($C$59:$C$78,D48)</f>
+        <v>13</v>
+      </c>
+      <c r="K48" s="26" t="n">
+        <f aca="false">ROUND(J48*E48,0)</f>
+        <v>23</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <f aca="false">ROUND($C$78*E48,0)</f>
+        <v>92</v>
+      </c>
+      <c r="M48" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F49" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H49" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="J49" s="26" t="n">
+        <f aca="false">INDEX($C$59:$C$78,D49)</f>
+        <v>13</v>
+      </c>
+      <c r="K49" s="26" t="str">
+        <f aca="false">ROUND($K$7*E49,0)&amp;" MP"</f>
+        <v>24 MP</v>
+      </c>
+      <c r="L49" s="26" t="str">
+        <f aca="false">ROUND($K$7*E49,0)&amp;" MP"</f>
+        <v>24 MP</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F50" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I50" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="22" t="s">
+      <c r="J50" s="26" t="n">
+        <f aca="false">INDEX($C$59:$C$78,D50)</f>
+        <v>15</v>
+      </c>
+      <c r="K50" s="26" t="n">
+        <f aca="false">ROUND(J50*E50,0)</f>
+        <v>18</v>
+      </c>
+      <c r="L50" s="26" t="n">
+        <f aca="false">ROUND($C$78*E50,0)</f>
+        <v>61</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F51" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I51" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="26" t="n">
+        <f aca="false">INDEX($C$59:$C$78,D51)</f>
+        <v>21</v>
+      </c>
+      <c r="K51" s="26" t="str">
+        <f aca="false">ROUND(INDEX($B$59:$B$78,D51)*E51,0)&amp;" HP"</f>
+        <v>26 HP</v>
+      </c>
+      <c r="L51" s="26" t="str">
+        <f aca="false">ROUND($B$78*E51,0)&amp;" HP"</f>
+        <v>50 HP</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E52" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I52" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" s="26" t="n">
+        <f aca="false">INDEX($C$59:$C$78,D52)</f>
+        <v>29</v>
+      </c>
+      <c r="K52" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="L52" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E53" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F53" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J53" s="26" t="n">
+        <f aca="false">INDEX($C$59:$C$78,D53)</f>
+        <v>37</v>
+      </c>
+      <c r="K53" s="26" t="n">
+        <f aca="false">ROUND(J53*E53,0)</f>
+        <v>67</v>
+      </c>
+      <c r="L53" s="26" t="n">
+        <f aca="false">ROUND($C$78*E53,0)</f>
         <v>92</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="M53" s="23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" s="27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F54" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H54" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="I54" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" s="26" t="n">
+        <f aca="false">INDEX($C$59:$C$78,D54)</f>
+        <v>51</v>
+      </c>
+      <c r="K54" s="26" t="n">
+        <f aca="false">ROUND(J54*E54,0)</f>
+        <v>230</v>
+      </c>
+      <c r="L54" s="26" t="n">
+        <f aca="false">ROUND($C$78*E54,0)</f>
+        <v>230</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F11" s="20" t="n">
+      <c r="B59" s="26" t="n">
+        <f aca="false">$C$7+(A59-1)*$F$7</f>
+        <v>100</v>
+      </c>
+      <c r="C59" s="26" t="n">
+        <f aca="false">$D$7+(A59-1)*$G$7</f>
+        <v>13</v>
+      </c>
+      <c r="D59" s="26" t="n">
+        <f aca="false">$E$7+(A59-1)*$H$7</f>
+        <v>5</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <f aca="false">1-100/(100+D59)</f>
+        <v>0.0476190476190477</v>
+      </c>
+      <c r="F59" s="26" t="n">
+        <f aca="false">IF(A59&lt;$M$7,50*A59,"MAX")</f>
+        <v>50</v>
+      </c>
+      <c r="G59" s="26" t="n">
+        <f aca="false">25*A59*(A59-1)</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="22" t="s">
+      <c r="B60" s="26" t="n">
+        <f aca="false">$C$7+(A60-1)*$F$7</f>
+        <v>108</v>
+      </c>
+      <c r="C60" s="26" t="n">
+        <f aca="false">$D$7+(A60-1)*$G$7</f>
+        <v>15</v>
+      </c>
+      <c r="D60" s="26" t="n">
+        <f aca="false">$E$7+(A60-1)*$H$7</f>
+        <v>6</v>
+      </c>
+      <c r="E60" s="29" t="n">
+        <f aca="false">1-100/(100+D60)</f>
+        <v>0.0566037735849057</v>
+      </c>
+      <c r="F60" s="26" t="n">
+        <f aca="false">IF(A60&lt;$M$7,50*A60,"MAX")</f>
+        <v>100</v>
+      </c>
+      <c r="G60" s="26" t="n">
+        <f aca="false">25*A60*(A60-1)</f>
+        <v>50</v>
+      </c>
+      <c r="H60" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A60,$D$48:$D$54,0)),"")</f>
+        <v>Chain Lightning</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="26" t="n">
+        <f aca="false">$C$7+(A61-1)*$F$7</f>
+        <v>116</v>
+      </c>
+      <c r="C61" s="26" t="n">
+        <f aca="false">$D$7+(A61-1)*$G$7</f>
+        <v>17</v>
+      </c>
+      <c r="D61" s="26" t="n">
+        <f aca="false">$E$7+(A61-1)*$H$7</f>
+        <v>7</v>
+      </c>
+      <c r="E61" s="29" t="n">
+        <f aca="false">1-100/(100+D61)</f>
+        <v>0.0654205607476636</v>
+      </c>
+      <c r="F61" s="26" t="n">
+        <f aca="false">IF(A61&lt;$M$7,50*A61,"MAX")</f>
+        <v>150</v>
+      </c>
+      <c r="G61" s="26" t="n">
+        <f aca="false">25*A61*(A61-1)</f>
+        <v>150</v>
+      </c>
+      <c r="H61" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A61,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" s="26" t="n">
+        <f aca="false">$C$7+(A62-1)*$F$7</f>
+        <v>124</v>
+      </c>
+      <c r="C62" s="26" t="n">
+        <f aca="false">$D$7+(A62-1)*$G$7</f>
+        <v>19</v>
+      </c>
+      <c r="D62" s="26" t="n">
+        <f aca="false">$E$7+(A62-1)*$H$7</f>
+        <v>8</v>
+      </c>
+      <c r="E62" s="29" t="n">
+        <f aca="false">1-100/(100+D62)</f>
+        <v>0.0740740740740741</v>
+      </c>
+      <c r="F62" s="26" t="n">
+        <f aca="false">IF(A62&lt;$M$7,50*A62,"MAX")</f>
+        <v>200</v>
+      </c>
+      <c r="G62" s="26" t="n">
+        <f aca="false">25*A62*(A62-1)</f>
+        <v>300</v>
+      </c>
+      <c r="H62" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A62,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B63" s="26" t="n">
+        <f aca="false">$C$7+(A63-1)*$F$7</f>
+        <v>132</v>
+      </c>
+      <c r="C63" s="26" t="n">
+        <f aca="false">$D$7+(A63-1)*$G$7</f>
+        <v>21</v>
+      </c>
+      <c r="D63" s="26" t="n">
+        <f aca="false">$E$7+(A63-1)*$H$7</f>
+        <v>9</v>
+      </c>
+      <c r="E63" s="29" t="n">
+        <f aca="false">1-100/(100+D63)</f>
+        <v>0.0825688073394495</v>
+      </c>
+      <c r="F63" s="26" t="n">
+        <f aca="false">IF(A63&lt;$M$7,50*A63,"MAX")</f>
+        <v>250</v>
+      </c>
+      <c r="G63" s="26" t="n">
+        <f aca="false">25*A63*(A63-1)</f>
+        <v>500</v>
+      </c>
+      <c r="H63" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A63,$D$48:$D$54,0)),"")</f>
+        <v>Frost Ward</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B64" s="26" t="n">
+        <f aca="false">$C$7+(A64-1)*$F$7</f>
+        <v>140</v>
+      </c>
+      <c r="C64" s="26" t="n">
+        <f aca="false">$D$7+(A64-1)*$G$7</f>
+        <v>23</v>
+      </c>
+      <c r="D64" s="26" t="n">
+        <f aca="false">$E$7+(A64-1)*$H$7</f>
+        <v>10</v>
+      </c>
+      <c r="E64" s="29" t="n">
+        <f aca="false">1-100/(100+D64)</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="F64" s="26" t="n">
+        <f aca="false">IF(A64&lt;$M$7,50*A64,"MAX")</f>
+        <v>300</v>
+      </c>
+      <c r="G64" s="26" t="n">
+        <f aca="false">25*A64*(A64-1)</f>
+        <v>750</v>
+      </c>
+      <c r="H64" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A64,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B65" s="26" t="n">
+        <f aca="false">$C$7+(A65-1)*$F$7</f>
+        <v>148</v>
+      </c>
+      <c r="C65" s="26" t="n">
+        <f aca="false">$D$7+(A65-1)*$G$7</f>
+        <v>25</v>
+      </c>
+      <c r="D65" s="26" t="n">
+        <f aca="false">$E$7+(A65-1)*$H$7</f>
+        <v>11</v>
+      </c>
+      <c r="E65" s="29" t="n">
+        <f aca="false">1-100/(100+D65)</f>
+        <v>0.0990990990990991</v>
+      </c>
+      <c r="F65" s="26" t="n">
+        <f aca="false">IF(A65&lt;$M$7,50*A65,"MAX")</f>
+        <v>350</v>
+      </c>
+      <c r="G65" s="26" t="n">
+        <f aca="false">25*A65*(A65-1)</f>
+        <v>1050</v>
+      </c>
+      <c r="H65" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A65,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B66" s="26" t="n">
+        <f aca="false">$C$7+(A66-1)*$F$7</f>
+        <v>156</v>
+      </c>
+      <c r="C66" s="26" t="n">
+        <f aca="false">$D$7+(A66-1)*$G$7</f>
+        <v>27</v>
+      </c>
+      <c r="D66" s="26" t="n">
+        <f aca="false">$E$7+(A66-1)*$H$7</f>
+        <v>12</v>
+      </c>
+      <c r="E66" s="29" t="n">
+        <f aca="false">1-100/(100+D66)</f>
+        <v>0.107142857142857</v>
+      </c>
+      <c r="F66" s="26" t="n">
+        <f aca="false">IF(A66&lt;$M$7,50*A66,"MAX")</f>
+        <v>400</v>
+      </c>
+      <c r="G66" s="26" t="n">
+        <f aca="false">25*A66*(A66-1)</f>
+        <v>1400</v>
+      </c>
+      <c r="H66" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A66,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" s="26" t="n">
+        <f aca="false">$C$7+(A67-1)*$F$7</f>
+        <v>164</v>
+      </c>
+      <c r="C67" s="26" t="n">
+        <f aca="false">$D$7+(A67-1)*$G$7</f>
+        <v>29</v>
+      </c>
+      <c r="D67" s="26" t="n">
+        <f aca="false">$E$7+(A67-1)*$H$7</f>
+        <v>13</v>
+      </c>
+      <c r="E67" s="29" t="n">
+        <f aca="false">1-100/(100+D67)</f>
+        <v>0.115044247787611</v>
+      </c>
+      <c r="F67" s="26" t="n">
+        <f aca="false">IF(A67&lt;$M$7,50*A67,"MAX")</f>
+        <v>450</v>
+      </c>
+      <c r="G67" s="26" t="n">
+        <f aca="false">25*A67*(A67-1)</f>
+        <v>1800</v>
+      </c>
+      <c r="H67" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A67,$D$48:$D$54,0)),"")</f>
+        <v>Wind Step</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B68" s="26" t="n">
+        <f aca="false">$C$7+(A68-1)*$F$7</f>
+        <v>172</v>
+      </c>
+      <c r="C68" s="26" t="n">
+        <f aca="false">$D$7+(A68-1)*$G$7</f>
+        <v>31</v>
+      </c>
+      <c r="D68" s="26" t="n">
+        <f aca="false">$E$7+(A68-1)*$H$7</f>
+        <v>14</v>
+      </c>
+      <c r="E68" s="29" t="n">
+        <f aca="false">1-100/(100+D68)</f>
+        <v>0.12280701754386</v>
+      </c>
+      <c r="F68" s="26" t="n">
+        <f aca="false">IF(A68&lt;$M$7,50*A68,"MAX")</f>
+        <v>500</v>
+      </c>
+      <c r="G68" s="26" t="n">
+        <f aca="false">25*A68*(A68-1)</f>
+        <v>2250</v>
+      </c>
+      <c r="H68" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A68,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B69" s="26" t="n">
+        <f aca="false">$C$7+(A69-1)*$F$7</f>
+        <v>180</v>
+      </c>
+      <c r="C69" s="26" t="n">
+        <f aca="false">$D$7+(A69-1)*$G$7</f>
+        <v>33</v>
+      </c>
+      <c r="D69" s="26" t="n">
+        <f aca="false">$E$7+(A69-1)*$H$7</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="29" t="n">
+        <f aca="false">1-100/(100+D69)</f>
+        <v>0.130434782608696</v>
+      </c>
+      <c r="F69" s="26" t="n">
+        <f aca="false">IF(A69&lt;$M$7,50*A69,"MAX")</f>
+        <v>550</v>
+      </c>
+      <c r="G69" s="26" t="n">
+        <f aca="false">25*A69*(A69-1)</f>
+        <v>2750</v>
+      </c>
+      <c r="H69" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A69,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B70" s="26" t="n">
+        <f aca="false">$C$7+(A70-1)*$F$7</f>
+        <v>188</v>
+      </c>
+      <c r="C70" s="26" t="n">
+        <f aca="false">$D$7+(A70-1)*$G$7</f>
+        <v>35</v>
+      </c>
+      <c r="D70" s="26" t="n">
+        <f aca="false">$E$7+(A70-1)*$H$7</f>
+        <v>16</v>
+      </c>
+      <c r="E70" s="29" t="n">
+        <f aca="false">1-100/(100+D70)</f>
+        <v>0.137931034482759</v>
+      </c>
+      <c r="F70" s="26" t="n">
+        <f aca="false">IF(A70&lt;$M$7,50*A70,"MAX")</f>
+        <v>600</v>
+      </c>
+      <c r="G70" s="26" t="n">
+        <f aca="false">25*A70*(A70-1)</f>
+        <v>3300</v>
+      </c>
+      <c r="H70" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A70,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B71" s="26" t="n">
+        <f aca="false">$C$7+(A71-1)*$F$7</f>
+        <v>196</v>
+      </c>
+      <c r="C71" s="26" t="n">
+        <f aca="false">$D$7+(A71-1)*$G$7</f>
+        <v>37</v>
+      </c>
+      <c r="D71" s="26" t="n">
+        <f aca="false">$E$7+(A71-1)*$H$7</f>
+        <v>17</v>
+      </c>
+      <c r="E71" s="29" t="n">
+        <f aca="false">1-100/(100+D71)</f>
+        <v>0.145299145299145</v>
+      </c>
+      <c r="F71" s="26" t="n">
+        <f aca="false">IF(A71&lt;$M$7,50*A71,"MAX")</f>
+        <v>650</v>
+      </c>
+      <c r="G71" s="26" t="n">
+        <f aca="false">25*A71*(A71-1)</f>
+        <v>3900</v>
+      </c>
+      <c r="H71" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A71,$D$48:$D$54,0)),"")</f>
+        <v>Steam Burst</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B72" s="26" t="n">
+        <f aca="false">$C$7+(A72-1)*$F$7</f>
+        <v>204</v>
+      </c>
+      <c r="C72" s="26" t="n">
+        <f aca="false">$D$7+(A72-1)*$G$7</f>
+        <v>39</v>
+      </c>
+      <c r="D72" s="26" t="n">
+        <f aca="false">$E$7+(A72-1)*$H$7</f>
+        <v>18</v>
+      </c>
+      <c r="E72" s="29" t="n">
+        <f aca="false">1-100/(100+D72)</f>
+        <v>0.152542372881356</v>
+      </c>
+      <c r="F72" s="26" t="n">
+        <f aca="false">IF(A72&lt;$M$7,50*A72,"MAX")</f>
+        <v>700</v>
+      </c>
+      <c r="G72" s="26" t="n">
+        <f aca="false">25*A72*(A72-1)</f>
+        <v>4550</v>
+      </c>
+      <c r="H72" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A72,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B73" s="26" t="n">
+        <f aca="false">$C$7+(A73-1)*$F$7</f>
+        <v>212</v>
+      </c>
+      <c r="C73" s="26" t="n">
+        <f aca="false">$D$7+(A73-1)*$G$7</f>
+        <v>41</v>
+      </c>
+      <c r="D73" s="26" t="n">
+        <f aca="false">$E$7+(A73-1)*$H$7</f>
+        <v>19</v>
+      </c>
+      <c r="E73" s="29" t="n">
+        <f aca="false">1-100/(100+D73)</f>
+        <v>0.159663865546218</v>
+      </c>
+      <c r="F73" s="26" t="n">
+        <f aca="false">IF(A73&lt;$M$7,50*A73,"MAX")</f>
+        <v>750</v>
+      </c>
+      <c r="G73" s="26" t="n">
+        <f aca="false">25*A73*(A73-1)</f>
+        <v>5250</v>
+      </c>
+      <c r="H73" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A73,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B74" s="26" t="n">
+        <f aca="false">$C$7+(A74-1)*$F$7</f>
+        <v>220</v>
+      </c>
+      <c r="C74" s="26" t="n">
+        <f aca="false">$D$7+(A74-1)*$G$7</f>
+        <v>43</v>
+      </c>
+      <c r="D74" s="26" t="n">
+        <f aca="false">$E$7+(A74-1)*$H$7</f>
+        <v>20</v>
+      </c>
+      <c r="E74" s="29" t="n">
+        <f aca="false">1-100/(100+D74)</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F74" s="26" t="n">
+        <f aca="false">IF(A74&lt;$M$7,50*A74,"MAX")</f>
+        <v>800</v>
+      </c>
+      <c r="G74" s="26" t="n">
+        <f aca="false">25*A74*(A74-1)</f>
+        <v>6000</v>
+      </c>
+      <c r="H74" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A74,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B75" s="26" t="n">
+        <f aca="false">$C$7+(A75-1)*$F$7</f>
+        <v>228</v>
+      </c>
+      <c r="C75" s="26" t="n">
+        <f aca="false">$D$7+(A75-1)*$G$7</f>
+        <v>45</v>
+      </c>
+      <c r="D75" s="26" t="n">
+        <f aca="false">$E$7+(A75-1)*$H$7</f>
+        <v>21</v>
+      </c>
+      <c r="E75" s="29" t="n">
+        <f aca="false">1-100/(100+D75)</f>
+        <v>0.173553719008264</v>
+      </c>
+      <c r="F75" s="26" t="n">
+        <f aca="false">IF(A75&lt;$M$7,50*A75,"MAX")</f>
+        <v>850</v>
+      </c>
+      <c r="G75" s="26" t="n">
+        <f aca="false">25*A75*(A75-1)</f>
+        <v>6800</v>
+      </c>
+      <c r="H75" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A75,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="B76" s="26" t="n">
+        <f aca="false">$C$7+(A76-1)*$F$7</f>
+        <v>236</v>
+      </c>
+      <c r="C76" s="26" t="n">
+        <f aca="false">$D$7+(A76-1)*$G$7</f>
+        <v>47</v>
+      </c>
+      <c r="D76" s="26" t="n">
+        <f aca="false">$E$7+(A76-1)*$H$7</f>
         <v>22</v>
       </c>
-      <c r="J11" s="22" t="n">
-        <f aca="false">INDEX($C$25:$C$44,D11)</f>
-        <v>10</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <f aca="false">ROUND(J11*E11,0)</f>
-        <v>13</v>
-      </c>
-      <c r="L11" s="22" t="n">
-        <f aca="false">ROUND($C$44*E11,0)</f>
-        <v>38</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <f aca="false">INDEX($C$25:$C$44,D12)</f>
-        <v>10</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <f aca="false">ROUND(J12*E12,0)</f>
+      <c r="E76" s="29" t="n">
+        <f aca="false">1-100/(100+D76)</f>
+        <v>0.180327868852459</v>
+      </c>
+      <c r="F76" s="26" t="n">
+        <f aca="false">IF(A76&lt;$M$7,50*A76,"MAX")</f>
+        <v>900</v>
+      </c>
+      <c r="G76" s="26" t="n">
+        <f aca="false">25*A76*(A76-1)</f>
+        <v>7650</v>
+      </c>
+      <c r="H76" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A76,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B77" s="26" t="n">
+        <f aca="false">$C$7+(A77-1)*$F$7</f>
+        <v>244</v>
+      </c>
+      <c r="C77" s="26" t="n">
+        <f aca="false">$D$7+(A77-1)*$G$7</f>
+        <v>49</v>
+      </c>
+      <c r="D77" s="26" t="n">
+        <f aca="false">$E$7+(A77-1)*$H$7</f>
+        <v>23</v>
+      </c>
+      <c r="E77" s="29" t="n">
+        <f aca="false">1-100/(100+D77)</f>
+        <v>0.186991869918699</v>
+      </c>
+      <c r="F77" s="26" t="n">
+        <f aca="false">IF(A77&lt;$M$7,50*A77,"MAX")</f>
+        <v>950</v>
+      </c>
+      <c r="G77" s="26" t="n">
+        <f aca="false">25*A77*(A77-1)</f>
+        <v>8550</v>
+      </c>
+      <c r="H77" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A77,$D$48:$D$54,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="L12" s="22" t="n">
-        <f aca="false">ROUND($C$44*E12,0)</f>
-        <v>58</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="22" t="n">
-        <f aca="false">INDEX($C$25:$C$44,D13)</f>
-        <v>11</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <f aca="false">ROUND(J13*E13,0)</f>
-        <v>14</v>
-      </c>
-      <c r="L13" s="22" t="n">
-        <f aca="false">ROUND($C$44*E13,0)</f>
-        <v>38</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="24" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="22" t="n">
-        <f aca="false">INDEX($C$25:$C$44,D14)</f>
-        <v>14</v>
-      </c>
-      <c r="K14" s="22" t="str">
-        <f aca="false">ROUND(INDEX($B$25:$B$44,D14)*E14,0)&amp;" HP"</f>
-        <v>42 HP</v>
-      </c>
-      <c r="L14" s="22" t="str">
-        <f aca="false">ROUND($B$44*E14,0)&amp;" HP"</f>
-        <v>87 HP</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="22" t="n">
-        <f aca="false">INDEX($C$25:$C$44,D15)</f>
-        <v>18</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J16" s="22" t="n">
-        <f aca="false">INDEX($C$25:$C$44,D16)</f>
-        <v>22</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <f aca="false">ROUND(J16*E16,0)</f>
-        <v>35</v>
-      </c>
-      <c r="L16" s="22" t="n">
-        <f aca="false">ROUND($C$44*E16,0)</f>
-        <v>46</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="22" t="n">
-        <f aca="false">INDEX($C$25:$C$44,D17)</f>
-        <v>29</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <f aca="false">ROUND(J17*E17,0)</f>
-        <v>116</v>
-      </c>
-      <c r="L17" s="22" t="n">
-        <f aca="false">ROUND($C$44*E17,0)</f>
-        <v>116</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" s="22" t="n">
-        <f aca="false">$C$6+(A25-1)*$F$6</f>
-        <v>120</v>
-      </c>
-      <c r="C25" s="22" t="n">
-        <f aca="false">$D$6+(A25-1)*$G$6</f>
-        <v>10</v>
-      </c>
-      <c r="D25" s="22" t="n">
-        <f aca="false">$E$6+(A25-1)*$H$6</f>
-        <v>6</v>
-      </c>
-      <c r="E25" s="25" t="n">
-        <f aca="false">1-100/(100+D25)</f>
-        <v>0.0566037735849057</v>
-      </c>
-      <c r="F25" s="22" t="n">
-        <f aca="false">IF(A25&lt;$M$6,50*A25,"MAX")</f>
-        <v>50</v>
-      </c>
-      <c r="G25" s="22" t="n">
-        <f aca="false">25*A25*(A25-1)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="22" t="n">
-        <f aca="false">$C$6+(A26-1)*$F$6</f>
-        <v>132</v>
-      </c>
-      <c r="C26" s="22" t="n">
-        <f aca="false">$D$6+(A26-1)*$G$6</f>
-        <v>11</v>
-      </c>
-      <c r="D26" s="22" t="n">
-        <f aca="false">$E$6+(A26-1)*$H$6</f>
-        <v>9</v>
-      </c>
-      <c r="E26" s="25" t="n">
-        <f aca="false">1-100/(100+D26)</f>
-        <v>0.0825688073394495</v>
-      </c>
-      <c r="F26" s="22" t="n">
-        <f aca="false">IF(A26&lt;$M$6,50*A26,"MAX")</f>
-        <v>100</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <f aca="false">25*A26*(A26-1)</f>
-        <v>50</v>
-      </c>
-      <c r="H26" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A26,$D$11:$D$17,0)),"")</f>
-        <v>Holy Ground</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="22" t="n">
-        <f aca="false">$C$6+(A27-1)*$F$6</f>
-        <v>144</v>
-      </c>
-      <c r="C27" s="22" t="n">
-        <f aca="false">$D$6+(A27-1)*$G$6</f>
-        <v>12</v>
-      </c>
-      <c r="D27" s="22" t="n">
-        <f aca="false">$E$6+(A27-1)*$H$6</f>
-        <v>12</v>
-      </c>
-      <c r="E27" s="25" t="n">
-        <f aca="false">1-100/(100+D27)</f>
-        <v>0.107142857142857</v>
-      </c>
-      <c r="F27" s="22" t="n">
-        <f aca="false">IF(A27&lt;$M$6,50*A27,"MAX")</f>
-        <v>150</v>
-      </c>
-      <c r="G27" s="22" t="n">
-        <f aca="false">25*A27*(A27-1)</f>
-        <v>150</v>
-      </c>
-      <c r="H27" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A27,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B28" s="22" t="n">
-        <f aca="false">$C$6+(A28-1)*$F$6</f>
-        <v>156</v>
-      </c>
-      <c r="C28" s="22" t="n">
-        <f aca="false">$D$6+(A28-1)*$G$6</f>
-        <v>13</v>
-      </c>
-      <c r="D28" s="22" t="n">
-        <f aca="false">$E$6+(A28-1)*$H$6</f>
-        <v>15</v>
-      </c>
-      <c r="E28" s="25" t="n">
-        <f aca="false">1-100/(100+D28)</f>
-        <v>0.130434782608696</v>
-      </c>
-      <c r="F28" s="22" t="n">
-        <f aca="false">IF(A28&lt;$M$6,50*A28,"MAX")</f>
-        <v>200</v>
-      </c>
-      <c r="G28" s="22" t="n">
-        <f aca="false">25*A28*(A28-1)</f>
-        <v>300</v>
-      </c>
-      <c r="H28" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A28,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="22" t="n">
-        <f aca="false">$C$6+(A29-1)*$F$6</f>
-        <v>168</v>
-      </c>
-      <c r="C29" s="22" t="n">
-        <f aca="false">$D$6+(A29-1)*$G$6</f>
-        <v>14</v>
-      </c>
-      <c r="D29" s="22" t="n">
-        <f aca="false">$E$6+(A29-1)*$H$6</f>
-        <v>18</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <f aca="false">1-100/(100+D29)</f>
-        <v>0.152542372881356</v>
-      </c>
-      <c r="F29" s="22" t="n">
-        <f aca="false">IF(A29&lt;$M$6,50*A29,"MAX")</f>
-        <v>250</v>
-      </c>
-      <c r="G29" s="22" t="n">
-        <f aca="false">25*A29*(A29-1)</f>
-        <v>500</v>
-      </c>
-      <c r="H29" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A29,$D$11:$D$17,0)),"")</f>
-        <v>Lay on Hands</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B30" s="22" t="n">
-        <f aca="false">$C$6+(A30-1)*$F$6</f>
-        <v>180</v>
-      </c>
-      <c r="C30" s="22" t="n">
-        <f aca="false">$D$6+(A30-1)*$G$6</f>
-        <v>15</v>
-      </c>
-      <c r="D30" s="22" t="n">
-        <f aca="false">$E$6+(A30-1)*$H$6</f>
-        <v>21</v>
-      </c>
-      <c r="E30" s="25" t="n">
-        <f aca="false">1-100/(100+D30)</f>
-        <v>0.173553719008264</v>
-      </c>
-      <c r="F30" s="22" t="n">
-        <f aca="false">IF(A30&lt;$M$6,50*A30,"MAX")</f>
-        <v>300</v>
-      </c>
-      <c r="G30" s="22" t="n">
-        <f aca="false">25*A30*(A30-1)</f>
-        <v>750</v>
-      </c>
-      <c r="H30" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A30,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="B31" s="22" t="n">
-        <f aca="false">$C$6+(A31-1)*$F$6</f>
-        <v>192</v>
-      </c>
-      <c r="C31" s="22" t="n">
-        <f aca="false">$D$6+(A31-1)*$G$6</f>
-        <v>16</v>
-      </c>
-      <c r="D31" s="22" t="n">
-        <f aca="false">$E$6+(A31-1)*$H$6</f>
+      <c r="B78" s="26" t="n">
+        <f aca="false">$C$7+(A78-1)*$F$7</f>
+        <v>252</v>
+      </c>
+      <c r="C78" s="26" t="n">
+        <f aca="false">$D$7+(A78-1)*$G$7</f>
+        <v>51</v>
+      </c>
+      <c r="D78" s="26" t="n">
+        <f aca="false">$E$7+(A78-1)*$H$7</f>
         <v>24</v>
       </c>
-      <c r="E31" s="25" t="n">
-        <f aca="false">1-100/(100+D31)</f>
+      <c r="E78" s="29" t="n">
+        <f aca="false">1-100/(100+D78)</f>
         <v>0.193548387096774</v>
       </c>
-      <c r="F31" s="22" t="n">
-        <f aca="false">IF(A31&lt;$M$6,50*A31,"MAX")</f>
-        <v>350</v>
-      </c>
-      <c r="G31" s="22" t="n">
-        <f aca="false">25*A31*(A31-1)</f>
-        <v>1050</v>
-      </c>
-      <c r="H31" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A31,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B32" s="22" t="n">
-        <f aca="false">$C$6+(A32-1)*$F$6</f>
-        <v>204</v>
-      </c>
-      <c r="C32" s="22" t="n">
-        <f aca="false">$D$6+(A32-1)*$G$6</f>
-        <v>17</v>
-      </c>
-      <c r="D32" s="22" t="n">
-        <f aca="false">$E$6+(A32-1)*$H$6</f>
-        <v>27</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <f aca="false">1-100/(100+D32)</f>
-        <v>0.21259842519685</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <f aca="false">IF(A32&lt;$M$6,50*A32,"MAX")</f>
-        <v>400</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <f aca="false">25*A32*(A32-1)</f>
-        <v>1400</v>
-      </c>
-      <c r="H32" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A32,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B33" s="22" t="n">
-        <f aca="false">$C$6+(A33-1)*$F$6</f>
-        <v>216</v>
-      </c>
-      <c r="C33" s="22" t="n">
-        <f aca="false">$D$6+(A33-1)*$G$6</f>
-        <v>18</v>
-      </c>
-      <c r="D33" s="22" t="n">
-        <f aca="false">$E$6+(A33-1)*$H$6</f>
-        <v>30</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <f aca="false">1-100/(100+D33)</f>
-        <v>0.230769230769231</v>
-      </c>
-      <c r="F33" s="22" t="n">
-        <f aca="false">IF(A33&lt;$M$6,50*A33,"MAX")</f>
-        <v>450</v>
-      </c>
-      <c r="G33" s="22" t="n">
-        <f aca="false">25*A33*(A33-1)</f>
-        <v>1800</v>
-      </c>
-      <c r="H33" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A33,$D$11:$D$17,0)),"")</f>
-        <v>Divine Aegis</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B34" s="22" t="n">
-        <f aca="false">$C$6+(A34-1)*$F$6</f>
-        <v>228</v>
-      </c>
-      <c r="C34" s="22" t="n">
-        <f aca="false">$D$6+(A34-1)*$G$6</f>
-        <v>19</v>
-      </c>
-      <c r="D34" s="22" t="n">
-        <f aca="false">$E$6+(A34-1)*$H$6</f>
-        <v>33</v>
-      </c>
-      <c r="E34" s="25" t="n">
-        <f aca="false">1-100/(100+D34)</f>
-        <v>0.24812030075188</v>
-      </c>
-      <c r="F34" s="22" t="n">
-        <f aca="false">IF(A34&lt;$M$6,50*A34,"MAX")</f>
-        <v>500</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <f aca="false">25*A34*(A34-1)</f>
-        <v>2250</v>
-      </c>
-      <c r="H34" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A34,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B35" s="22" t="n">
-        <f aca="false">$C$6+(A35-1)*$F$6</f>
-        <v>240</v>
-      </c>
-      <c r="C35" s="22" t="n">
-        <f aca="false">$D$6+(A35-1)*$G$6</f>
-        <v>20</v>
-      </c>
-      <c r="D35" s="22" t="n">
-        <f aca="false">$E$6+(A35-1)*$H$6</f>
-        <v>36</v>
-      </c>
-      <c r="E35" s="25" t="n">
-        <f aca="false">1-100/(100+D35)</f>
-        <v>0.264705882352941</v>
-      </c>
-      <c r="F35" s="22" t="n">
-        <f aca="false">IF(A35&lt;$M$6,50*A35,"MAX")</f>
-        <v>550</v>
-      </c>
-      <c r="G35" s="22" t="n">
-        <f aca="false">25*A35*(A35-1)</f>
-        <v>2750</v>
-      </c>
-      <c r="H35" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A35,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B36" s="22" t="n">
-        <f aca="false">$C$6+(A36-1)*$F$6</f>
-        <v>252</v>
-      </c>
-      <c r="C36" s="22" t="n">
-        <f aca="false">$D$6+(A36-1)*$G$6</f>
-        <v>21</v>
-      </c>
-      <c r="D36" s="22" t="n">
-        <f aca="false">$E$6+(A36-1)*$H$6</f>
-        <v>39</v>
-      </c>
-      <c r="E36" s="25" t="n">
-        <f aca="false">1-100/(100+D36)</f>
-        <v>0.280575539568345</v>
-      </c>
-      <c r="F36" s="22" t="n">
-        <f aca="false">IF(A36&lt;$M$6,50*A36,"MAX")</f>
-        <v>600</v>
-      </c>
-      <c r="G36" s="22" t="n">
-        <f aca="false">25*A36*(A36-1)</f>
-        <v>3300</v>
-      </c>
-      <c r="H36" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A36,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="B37" s="22" t="n">
-        <f aca="false">$C$6+(A37-1)*$F$6</f>
-        <v>264</v>
-      </c>
-      <c r="C37" s="22" t="n">
-        <f aca="false">$D$6+(A37-1)*$G$6</f>
-        <v>22</v>
-      </c>
-      <c r="D37" s="22" t="n">
-        <f aca="false">$E$6+(A37-1)*$H$6</f>
-        <v>42</v>
-      </c>
-      <c r="E37" s="25" t="n">
-        <f aca="false">1-100/(100+D37)</f>
-        <v>0.295774647887324</v>
-      </c>
-      <c r="F37" s="22" t="n">
-        <f aca="false">IF(A37&lt;$M$6,50*A37,"MAX")</f>
-        <v>650</v>
-      </c>
-      <c r="G37" s="22" t="n">
-        <f aca="false">25*A37*(A37-1)</f>
-        <v>3900</v>
-      </c>
-      <c r="H37" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A37,$D$11:$D$17,0)),"")</f>
-        <v>Radiant Slash</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="B38" s="22" t="n">
-        <f aca="false">$C$6+(A38-1)*$F$6</f>
-        <v>276</v>
-      </c>
-      <c r="C38" s="22" t="n">
-        <f aca="false">$D$6+(A38-1)*$G$6</f>
-        <v>23</v>
-      </c>
-      <c r="D38" s="22" t="n">
-        <f aca="false">$E$6+(A38-1)*$H$6</f>
-        <v>45</v>
-      </c>
-      <c r="E38" s="25" t="n">
-        <f aca="false">1-100/(100+D38)</f>
-        <v>0.310344827586207</v>
-      </c>
-      <c r="F38" s="22" t="n">
-        <f aca="false">IF(A38&lt;$M$6,50*A38,"MAX")</f>
-        <v>700</v>
-      </c>
-      <c r="G38" s="22" t="n">
-        <f aca="false">25*A38*(A38-1)</f>
-        <v>4550</v>
-      </c>
-      <c r="H38" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A38,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B39" s="22" t="n">
-        <f aca="false">$C$6+(A39-1)*$F$6</f>
-        <v>288</v>
-      </c>
-      <c r="C39" s="22" t="n">
-        <f aca="false">$D$6+(A39-1)*$G$6</f>
-        <v>24</v>
-      </c>
-      <c r="D39" s="22" t="n">
-        <f aca="false">$E$6+(A39-1)*$H$6</f>
-        <v>48</v>
-      </c>
-      <c r="E39" s="25" t="n">
-        <f aca="false">1-100/(100+D39)</f>
-        <v>0.324324324324324</v>
-      </c>
-      <c r="F39" s="22" t="n">
-        <f aca="false">IF(A39&lt;$M$6,50*A39,"MAX")</f>
-        <v>750</v>
-      </c>
-      <c r="G39" s="22" t="n">
-        <f aca="false">25*A39*(A39-1)</f>
-        <v>5250</v>
-      </c>
-      <c r="H39" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A39,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B40" s="22" t="n">
-        <f aca="false">$C$6+(A40-1)*$F$6</f>
-        <v>300</v>
-      </c>
-      <c r="C40" s="22" t="n">
-        <f aca="false">$D$6+(A40-1)*$G$6</f>
-        <v>25</v>
-      </c>
-      <c r="D40" s="22" t="n">
-        <f aca="false">$E$6+(A40-1)*$H$6</f>
-        <v>51</v>
-      </c>
-      <c r="E40" s="25" t="n">
-        <f aca="false">1-100/(100+D40)</f>
-        <v>0.337748344370861</v>
-      </c>
-      <c r="F40" s="22" t="n">
-        <f aca="false">IF(A40&lt;$M$6,50*A40,"MAX")</f>
-        <v>800</v>
-      </c>
-      <c r="G40" s="22" t="n">
-        <f aca="false">25*A40*(A40-1)</f>
-        <v>6000</v>
-      </c>
-      <c r="H40" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A40,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="22" t="n">
-        <f aca="false">$C$6+(A41-1)*$F$6</f>
-        <v>312</v>
-      </c>
-      <c r="C41" s="22" t="n">
-        <f aca="false">$D$6+(A41-1)*$G$6</f>
-        <v>26</v>
-      </c>
-      <c r="D41" s="22" t="n">
-        <f aca="false">$E$6+(A41-1)*$H$6</f>
-        <v>54</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <f aca="false">1-100/(100+D41)</f>
-        <v>0.350649350649351</v>
-      </c>
-      <c r="F41" s="22" t="n">
-        <f aca="false">IF(A41&lt;$M$6,50*A41,"MAX")</f>
-        <v>850</v>
-      </c>
-      <c r="G41" s="22" t="n">
-        <f aca="false">25*A41*(A41-1)</f>
-        <v>6800</v>
-      </c>
-      <c r="H41" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A41,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="B42" s="22" t="n">
-        <f aca="false">$C$6+(A42-1)*$F$6</f>
-        <v>324</v>
-      </c>
-      <c r="C42" s="22" t="n">
-        <f aca="false">$D$6+(A42-1)*$G$6</f>
-        <v>27</v>
-      </c>
-      <c r="D42" s="22" t="n">
-        <f aca="false">$E$6+(A42-1)*$H$6</f>
-        <v>57</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <f aca="false">1-100/(100+D42)</f>
-        <v>0.363057324840764</v>
-      </c>
-      <c r="F42" s="22" t="n">
-        <f aca="false">IF(A42&lt;$M$6,50*A42,"MAX")</f>
-        <v>900</v>
-      </c>
-      <c r="G42" s="22" t="n">
-        <f aca="false">25*A42*(A42-1)</f>
-        <v>7650</v>
-      </c>
-      <c r="H42" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A42,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B43" s="22" t="n">
-        <f aca="false">$C$6+(A43-1)*$F$6</f>
-        <v>336</v>
-      </c>
-      <c r="C43" s="22" t="n">
-        <f aca="false">$D$6+(A43-1)*$G$6</f>
-        <v>28</v>
-      </c>
-      <c r="D43" s="22" t="n">
-        <f aca="false">$E$6+(A43-1)*$H$6</f>
-        <v>60</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <f aca="false">1-100/(100+D43)</f>
-        <v>0.375</v>
-      </c>
-      <c r="F43" s="22" t="n">
-        <f aca="false">IF(A43&lt;$M$6,50*A43,"MAX")</f>
-        <v>950</v>
-      </c>
-      <c r="G43" s="22" t="n">
-        <f aca="false">25*A43*(A43-1)</f>
-        <v>8550</v>
-      </c>
-      <c r="H43" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A43,$D$11:$D$17,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B44" s="22" t="n">
-        <f aca="false">$C$6+(A44-1)*$F$6</f>
-        <v>348</v>
-      </c>
-      <c r="C44" s="22" t="n">
-        <f aca="false">$D$6+(A44-1)*$G$6</f>
-        <v>29</v>
-      </c>
-      <c r="D44" s="22" t="n">
-        <f aca="false">$E$6+(A44-1)*$H$6</f>
-        <v>63</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <f aca="false">1-100/(100+D44)</f>
-        <v>0.386503067484663</v>
-      </c>
-      <c r="F44" s="22" t="str">
-        <f aca="false">IF(A44&lt;$M$6,50*A44,"MAX")</f>
+      <c r="F78" s="26" t="str">
+        <f aca="false">IF(A78&lt;$M$7,50*A78,"MAX")</f>
         <v>MAX</v>
       </c>
-      <c r="G44" s="22" t="n">
-        <f aca="false">25*A44*(A44-1)</f>
+      <c r="G78" s="26" t="n">
+        <f aca="false">25*A78*(A78-1)</f>
         <v>9500</v>
       </c>
-      <c r="H44" s="5" t="str">
-        <f aca="false">IFERROR(INDEX($A$11:$A$17,MATCH(A44,$D$11:$D$17,0)),"")</f>
-        <v>Judgement</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
-        <v>129</v>
+      <c r="H78" s="23" t="str">
+        <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A78,$D$48:$D$54,0)),"")</f>
+        <v>Meteor</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="21" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -4394,250 +5607,250 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="26" t="s">
+      <c r="C6" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>153</v>
+      <c r="I6" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="K6" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>163</v>
+      <c r="C7" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="L7" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="L8" s="26" t="s">
+      <c r="B8" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="L8" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="26" t="s">
-        <v>174</v>
+      <c r="M8" s="30" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="E9" s="26" t="s">
+      <c r="B9" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="H9" s="26" t="s">
+      <c r="G9" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="H9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="J9" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="K9" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="L9" s="26" t="s">
+      <c r="I9" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="L9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="26" t="s">
-        <v>181</v>
+      <c r="M9" s="30" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -4647,524 +5860,524 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="26" t="s">
+      <c r="C13" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="29" t="s">
-        <v>192</v>
+      <c r="E13" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="33" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" s="26" t="s">
+      <c r="C14" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="G14" s="26" t="s">
+      <c r="E14" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="F23" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D28" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="F20" s="26" t="s">
+      <c r="E28" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="28" t="s">
-        <v>212</v>
+      <c r="G28" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="32" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30" t="s">
-        <v>234</v>
+      <c r="A31" s="34" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="s">
-        <v>235</v>
+      <c r="A32" s="34" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30" t="s">
-        <v>236</v>
+      <c r="A33" s="34" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30" t="s">
-        <v>237</v>
+      <c r="A34" s="34" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="30" t="s">
-        <v>238</v>
+      <c r="A35" s="34" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="30" t="s">
-        <v>239</v>
+      <c r="A36" s="34" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30" t="s">
-        <v>240</v>
+      <c r="A37" s="34" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="30" t="s">
-        <v>241</v>
+      <c r="A38" s="34" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -5175,12 +6388,12 @@
       <c r="L41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26"/>
-      <c r="B42" s="26" t="s">
+      <c r="A42" s="30"/>
+      <c r="B42" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="26" t="s">
-        <v>246</v>
+      <c r="C42" s="30" t="s">
+        <v>269</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>5</v>
@@ -5190,12 +6403,12 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26" t="s">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="26" t="s">
-        <v>246</v>
+      <c r="C43" s="30" t="s">
+        <v>269</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>8</v>
@@ -5205,12 +6418,12 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="26"/>
-      <c r="B44" s="26" t="s">
+      <c r="A44" s="30"/>
+      <c r="B44" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="26" t="s">
-        <v>246</v>
+      <c r="C44" s="30" t="s">
+        <v>269</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>12</v>
@@ -5220,12 +6433,12 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>246</v>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>269</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>30</v>
@@ -5235,12 +6448,12 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="26"/>
-      <c r="B46" s="26" t="s">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="26" t="s">
-        <v>248</v>
+      <c r="C46" s="30" t="s">
+        <v>271</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>6</v>
@@ -5250,12 +6463,12 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="26"/>
-      <c r="B47" s="26" t="s">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="26" t="s">
-        <v>248</v>
+      <c r="C47" s="30" t="s">
+        <v>271</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>16</v>
@@ -5265,12 +6478,12 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26" t="s">
+      <c r="A48" s="30"/>
+      <c r="B48" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="26" t="s">
-        <v>248</v>
+      <c r="C48" s="30" t="s">
+        <v>271</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>14</v>
@@ -5280,12 +6493,12 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>248</v>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>271</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>45</v>
@@ -5296,59 +6509,59 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="D50" s="31" t="n">
+        <v>273</v>
+      </c>
+      <c r="D50" s="35" t="n">
         <f aca="false">2*D42+3*D43+D44+D45</f>
         <v>76</v>
       </c>
-      <c r="E50" s="31" t="n">
+      <c r="E50" s="35" t="n">
         <f aca="false">2*E42+3*E43+E44+E45</f>
         <v>67</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="D51" s="31" t="n">
+        <v>274</v>
+      </c>
+      <c r="D51" s="35" t="n">
         <f aca="false">2*D42+3*D43+D44</f>
         <v>46</v>
       </c>
-      <c r="E51" s="31" t="n">
+      <c r="E51" s="35" t="n">
         <f aca="false">2*E42+3*E43+E44</f>
         <v>17</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="D52" s="31" t="n">
+        <v>275</v>
+      </c>
+      <c r="D52" s="35" t="n">
         <f aca="false">5*D46+D47+2*D48+D49</f>
         <v>119</v>
       </c>
-      <c r="E52" s="31" t="n">
+      <c r="E52" s="35" t="n">
         <f aca="false">5*E46+E47+2*E48+E49</f>
         <v>121</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="D53" s="31" t="n">
+        <v>276</v>
+      </c>
+      <c r="D53" s="35" t="n">
         <f aca="false">5*D46+D47+2*D48</f>
         <v>74</v>
       </c>
-      <c r="E53" s="31" t="n">
+      <c r="E53" s="35" t="n">
         <f aca="false">5*E46+E47+2*E48</f>
         <v>26</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -5386,7 +6599,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
@@ -5401,511 +6614,563 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="G4" s="32" t="s">
+      <c r="A4" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="G4" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="B5" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="D5" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>267</v>
+      <c r="G5" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="26" t="s">
+      <c r="B6" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F6" s="33" t="s">
+      <c r="D6" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F6" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="H6" s="38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="H7" s="38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F7" s="33" t="s">
+      <c r="D14" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="H16" s="40" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="37" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="37" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="37" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="37" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="37" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F12" s="33" t="s">
+      <c r="B24" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="H14" s="36" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E20" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="33" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="H22" s="35" t="s">
-        <v>173</v>
+      <c r="G24" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="H24" s="39" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H22"/>
-  <conditionalFormatting sqref="H5:H22">
+  <autoFilter ref="A4:H24"/>
+  <conditionalFormatting sqref="H5:H24">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Done"</formula>
     </cfRule>
@@ -5920,7 +7185,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H22" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H24" type="list">
       <formula1>"Done,In progress,Not started,Undecided"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5954,139 +7219,139 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="38" t="n">
+      <c r="C5" s="42" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B6" s="37" t="n">
+        <v>352</v>
+      </c>
+      <c r="B6" s="41" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="38" t="n">
+      <c r="C6" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="B7" s="37" t="n">
+        <v>354</v>
+      </c>
+      <c r="B7" s="41" t="n">
         <v>0.2</v>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="42" t="n">
         <v>1.5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B8" s="37" t="n">
+        <v>356</v>
+      </c>
+      <c r="B8" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="38" t="n">
+      <c r="C9" s="42" t="n">
         <v>2.2</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="B11" s="39" t="n">
+        <v>362</v>
+      </c>
+      <c r="B11" s="43" t="n">
         <f aca="false">SUM(B5:B8)</f>
         <v>1</v>
       </c>
@@ -6122,12 +7387,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6135,31 +7400,31 @@
         <v>30</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6169,20 +7434,20 @@
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="41" t="n">
         <v>0.25</v>
       </c>
-      <c r="D5" s="38" t="n">
+      <c r="D5" s="42" t="n">
         <v>1.25</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="44" t="n">
         <f aca="false">D5*E5</f>
         <v>2.5</v>
       </c>
-      <c r="G5" s="41" t="n">
+      <c r="G5" s="45" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A5,Monsters!$A$5:$A$17,0))</f>
         <v>12</v>
       </c>
@@ -6195,7 +7460,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6203,22 +7468,22 @@
         <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C6" s="37" t="n">
+        <v>371</v>
+      </c>
+      <c r="C6" s="41" t="n">
         <v>0.2</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="42" t="n">
         <v>2.25</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="44" t="n">
         <f aca="false">D6*E6</f>
         <v>2.25</v>
       </c>
-      <c r="G6" s="41" t="n">
+      <c r="G6" s="45" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A6,Monsters!$A$5:$A$17,0))</f>
         <v>10</v>
       </c>
@@ -6231,7 +7496,7 @@
         <v>34</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6239,22 +7504,22 @@
         <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C7" s="37" t="n">
+        <v>373</v>
+      </c>
+      <c r="C7" s="41" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="42" t="n">
         <v>0.8</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="44" t="n">
         <f aca="false">D7*E7</f>
         <v>1.6</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="45" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A7,Monsters!$A$5:$A$17,0))</f>
         <v>10</v>
       </c>
@@ -6267,7 +7532,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6277,20 +7542,20 @@
       <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="41" t="n">
         <v>0.2</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="42" t="n">
         <v>2.5</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="44" t="n">
         <f aca="false">D8*E8</f>
         <v>2.5</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="45" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A8,Monsters!$A$5:$A$17,0))</f>
         <v>34</v>
       </c>
@@ -6303,7 +7568,7 @@
         <v>119</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6311,22 +7576,22 @@
         <v>47</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="C9" s="37" t="n">
+        <v>376</v>
+      </c>
+      <c r="C9" s="41" t="n">
         <v>0.15</v>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="42" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="44" t="n">
         <f aca="false">D9*E9</f>
         <v>3</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="45" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A9,Monsters!$A$5:$A$17,0))</f>
         <v>42</v>
       </c>
@@ -6339,7 +7604,7 @@
         <v>189</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6347,22 +7612,22 @@
         <v>47</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="C10" s="37" t="n">
+        <v>378</v>
+      </c>
+      <c r="C10" s="41" t="n">
         <v>0.15</v>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D10" s="42" t="n">
         <v>0.9</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="44" t="n">
         <f aca="false">D10*E10</f>
         <v>1.8</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="45" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A10,Monsters!$A$5:$A$17,0))</f>
         <v>42</v>
       </c>
@@ -6375,7 +7640,7 @@
         <v>113</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6383,22 +7648,22 @@
         <v>47</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C11" s="37" t="n">
+        <v>379</v>
+      </c>
+      <c r="C11" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D11" s="42" t="n">
         <v>1.4</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="44" t="n">
         <f aca="false">D11*E11</f>
         <v>1.4</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="45" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A11,Monsters!$A$5:$A$17,0))</f>
         <v>42</v>
       </c>
@@ -6411,12 +7676,12 @@
         <v>88</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -6448,12 +7713,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6464,30 +7729,30 @@
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="str">
+      <c r="A5" s="46" t="str">
         <f aca="false">Monsters!A5</f>
         <v>Mutated Tadpole</v>
       </c>
-      <c r="B5" s="41" t="n">
+      <c r="B5" s="45" t="n">
         <f aca="false">Monsters!F5</f>
         <v>4</v>
       </c>
@@ -6517,11 +7782,11 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="str">
+      <c r="A6" s="46" t="str">
         <f aca="false">Monsters!A6</f>
         <v>Mutated Frog</v>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="45" t="n">
         <f aca="false">Monsters!F6</f>
         <v>4</v>
       </c>
@@ -6551,11 +7816,11 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="str">
+      <c r="A7" s="46" t="str">
         <f aca="false">Monsters!A7</f>
         <v>Mutated Boar</v>
       </c>
-      <c r="B7" s="41" t="n">
+      <c r="B7" s="45" t="n">
         <f aca="false">Monsters!F7</f>
         <v>12</v>
       </c>
@@ -6585,11 +7850,11 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="str">
+      <c r="A8" s="47" t="str">
         <f aca="false">Monsters!A8</f>
         <v>Mutated Cheetah</v>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="48" t="n">
         <f aca="false">Monsters!F8</f>
         <v>12</v>
       </c>
@@ -6619,11 +7884,11 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="str">
+      <c r="A9" s="46" t="str">
         <f aca="false">Monsters!A9</f>
         <v>Security Drone</v>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="45" t="n">
         <f aca="false">Monsters!F9</f>
         <v>5</v>
       </c>
@@ -6653,11 +7918,11 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="str">
+      <c r="A10" s="46" t="str">
         <f aca="false">Monsters!A10</f>
         <v>Maintenance Bot</v>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="45" t="n">
         <f aca="false">Monsters!F10</f>
         <v>8</v>
       </c>
@@ -6687,11 +7952,11 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="str">
+      <c r="A11" s="46" t="str">
         <f aca="false">Monsters!A11</f>
         <v>Sentry Turret</v>
       </c>
-      <c r="B11" s="41" t="n">
+      <c r="B11" s="45" t="n">
         <f aca="false">Monsters!F11</f>
         <v>9</v>
       </c>
@@ -6721,11 +7986,11 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="str">
+      <c r="A12" s="47" t="str">
         <f aca="false">Monsters!A12</f>
         <v>Rogue Overseer</v>
       </c>
-      <c r="B12" s="44" t="n">
+      <c r="B12" s="48" t="n">
         <f aca="false">Monsters!F12</f>
         <v>10</v>
       </c>
@@ -6755,11 +8020,11 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="str">
+      <c r="A13" s="46" t="str">
         <f aca="false">Monsters!A13</f>
         <v>Rift Wisp</v>
       </c>
-      <c r="B13" s="41" t="n">
+      <c r="B13" s="45" t="n">
         <f aca="false">Monsters!F13</f>
         <v>18</v>
       </c>
@@ -6789,11 +8054,11 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="str">
+      <c r="A14" s="46" t="str">
         <f aca="false">Monsters!A14</f>
         <v>Rift Knight</v>
       </c>
-      <c r="B14" s="41" t="n">
+      <c r="B14" s="45" t="n">
         <f aca="false">Monsters!F14</f>
         <v>32</v>
       </c>
@@ -6823,11 +8088,11 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="str">
+      <c r="A15" s="46" t="str">
         <f aca="false">Monsters!A15</f>
         <v>Rift Stalker</v>
       </c>
-      <c r="B15" s="41" t="n">
+      <c r="B15" s="45" t="n">
         <f aca="false">Monsters!F15</f>
         <v>35</v>
       </c>
@@ -6857,11 +8122,11 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="str">
+      <c r="A16" s="47" t="str">
         <f aca="false">Monsters!A16</f>
         <v>Rift Warden</v>
       </c>
-      <c r="B16" s="44" t="n">
+      <c r="B16" s="48" t="n">
         <f aca="false">Monsters!F16</f>
         <v>34</v>
       </c>
@@ -6891,11 +8156,11 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="str">
+      <c r="A17" s="47" t="str">
         <f aca="false">Monsters!A17</f>
         <v>Hollow Colossus</v>
       </c>
-      <c r="B17" s="44" t="n">
+      <c r="B17" s="48" t="n">
         <f aca="false">Monsters!F17</f>
         <v>42</v>
       </c>
@@ -6940,84 +8205,84 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="45" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="46" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="47" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="48" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="48" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="48" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="48" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="47" t="s">
-        <v>369</v>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="34" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="34" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="B13" s="50" t="n">
         <v>0.887</v>
@@ -7032,168 +8297,168 @@
         <v>0.607</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="s">
-        <v>378</v>
-      </c>
-      <c r="B14" s="25" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="B14" s="29" t="n">
         <v>0.871</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="29" t="n">
         <v>0.645</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="29" t="n">
         <v>0.929</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="29" t="n">
         <v>0.619</v>
       </c>
-      <c r="F14" s="51" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="s">
-        <v>380</v>
-      </c>
-      <c r="B15" s="25" t="n">
+      <c r="F14" s="23" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="B15" s="29" t="n">
         <v>0.787</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="29" t="n">
         <v>0.45</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="29" t="n">
         <v>0.869</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="29" t="n">
         <v>0.525</v>
       </c>
-      <c r="F15" s="51" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="B16" s="25" t="n">
+      <c r="F15" s="23" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="29" t="n">
         <v>0.703</v>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="29" t="n">
         <v>0.337</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="29" t="n">
         <v>0.768</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="29" t="n">
         <v>0.287</v>
       </c>
-      <c r="F16" s="51" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="s">
-        <v>384</v>
-      </c>
-      <c r="B17" s="25" t="n">
+      <c r="F16" s="23" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="B17" s="29" t="n">
         <v>0.845</v>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="29" t="n">
         <v>0.655</v>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="29" t="n">
         <v>0.892</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="29" t="n">
         <v>0.578</v>
       </c>
-      <c r="F17" s="51" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="B18" s="25" t="n">
+      <c r="F17" s="23" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="B18" s="29" t="n">
         <v>0.855</v>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="29" t="n">
         <v>0.576</v>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="29" t="n">
         <v>0.885</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="29" t="n">
         <v>0.444</v>
       </c>
-      <c r="F18" s="51" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="s">
-        <v>388</v>
-      </c>
-      <c r="B19" s="25" t="n">
+      <c r="F18" s="23" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>416</v>
+      </c>
+      <c r="B19" s="29" t="n">
         <v>0.877</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="29" t="n">
         <v>0.592</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="29" t="n">
         <v>0.903</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="29" t="n">
         <v>0.381</v>
       </c>
-      <c r="F19" s="51" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="46" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="47" t="s">
-        <v>390</v>
+      <c r="F19" s="23" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="B24" s="50" t="n">
         <v>0.86625</v>
@@ -7207,268 +8472,426 @@
       <c r="E24" s="50" t="n">
         <v>0.614</v>
       </c>
-      <c r="F24" s="52" t="n">
+      <c r="F24" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="52" t="n">
+      <c r="G24" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="53" t="n">
+      <c r="H24" s="52" t="n">
         <v>0.225</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="54" t="s">
-        <v>394</v>
-      </c>
-      <c r="B25" s="55" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="53" t="s">
+        <v>422</v>
+      </c>
+      <c r="B25" s="54" t="n">
         <v>0.91575</v>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C25" s="54" t="n">
         <v>0.72775</v>
       </c>
-      <c r="D25" s="55" t="n">
+      <c r="D25" s="54" t="n">
         <v>0.9435</v>
       </c>
-      <c r="E25" s="55" t="n">
+      <c r="E25" s="54" t="n">
         <v>0.719</v>
       </c>
-      <c r="F25" s="56" t="n">
+      <c r="F25" s="55" t="n">
         <v>1.2</v>
       </c>
-      <c r="G25" s="56" t="n">
+      <c r="G25" s="55" t="n">
         <v>1.9</v>
       </c>
-      <c r="H25" s="57" t="n">
+      <c r="H25" s="56" t="n">
         <v>0.258333333333333</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="s">
-        <v>395</v>
-      </c>
-      <c r="B26" s="25" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="B26" s="29" t="n">
         <v>0.88</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="29" t="n">
         <v>0.659</v>
       </c>
-      <c r="D26" s="25" t="n">
+      <c r="D26" s="29" t="n">
         <v>0.92425</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="29" t="n">
         <v>0.63175</v>
       </c>
-      <c r="F26" s="58" t="n">
+      <c r="F26" s="57" t="n">
         <v>0.1</v>
       </c>
-      <c r="G26" s="58" t="n">
+      <c r="G26" s="57" t="n">
         <v>0.1</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="H26" s="25" t="n">
         <v>0.225</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="s">
-        <v>396</v>
-      </c>
-      <c r="B27" s="25" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="B27" s="29" t="n">
         <v>0.87675</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="29" t="n">
         <v>0.6865</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="29" t="n">
         <v>0.9285</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="29" t="n">
         <v>0.62375</v>
       </c>
-      <c r="F27" s="58" t="n">
+      <c r="F27" s="57" t="n">
         <v>0.1</v>
       </c>
-      <c r="G27" s="58" t="n">
+      <c r="G27" s="57" t="n">
         <v>0.1</v>
       </c>
-      <c r="H27" s="21" t="n">
+      <c r="H27" s="25" t="n">
         <v>0.225</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="51" t="s">
-        <v>397</v>
-      </c>
-      <c r="B28" s="25" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="B28" s="29" t="n">
         <v>0.95275</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="29" t="n">
         <v>0.806</v>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="29" t="n">
         <v>0.9685</v>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="29" t="n">
         <v>0.7745</v>
       </c>
-      <c r="F28" s="58" t="n">
+      <c r="F28" s="57" t="n">
         <v>1.2</v>
       </c>
-      <c r="G28" s="58" t="n">
+      <c r="G28" s="57" t="n">
         <v>1.9</v>
       </c>
-      <c r="H28" s="21" t="n">
+      <c r="H28" s="25" t="n">
         <v>0.308333333333333</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="B29" s="29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C29" s="29" t="n">
+        <v>0.815</v>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>0.9635</v>
+      </c>
+      <c r="E29" s="29" t="n">
+        <v>0.78075</v>
+      </c>
+      <c r="F29" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G29" s="57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H29" s="25" t="n">
+        <v>0.304166666666667</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="B30" s="29" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="F30" s="57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G30" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="25" t="n">
+        <v>0.316666666666667</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>0.93475</v>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="D31" s="29" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="E31" s="29" t="n">
+        <v>0.75075</v>
+      </c>
+      <c r="F31" s="57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G31" s="57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H31" s="25" t="n">
+        <v>0.266666666666667</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="B32" s="29" t="n">
+        <v>0.98525</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>0.90425</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>0.99625</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="F32" s="57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G32" s="57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H32" s="25" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>0.8385</v>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>0.98725</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="F33" s="57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G33" s="57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H33" s="25" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="34" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="34" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="34" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="34" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="19" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B29" s="25" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C29" s="25" t="n">
-        <v>0.815</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>0.9635</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>0.78075</v>
-      </c>
-      <c r="F29" s="58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G29" s="58" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H29" s="21" t="n">
-        <v>0.304166666666667</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="s">
-        <v>399</v>
-      </c>
-      <c r="B30" s="25" t="n">
-        <v>0.96875</v>
-      </c>
-      <c r="C30" s="25" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="D30" s="25" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>0.8535</v>
-      </c>
-      <c r="F30" s="58" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G30" s="58" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="21" t="n">
-        <v>0.316666666666667</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="s">
-        <v>400</v>
-      </c>
-      <c r="B31" s="25" t="n">
-        <v>0.93475</v>
-      </c>
-      <c r="C31" s="25" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="D31" s="25" t="n">
-        <v>0.9675</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>0.75075</v>
-      </c>
-      <c r="F31" s="58" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G31" s="58" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H31" s="21" t="n">
-        <v>0.266666666666667</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="s">
-        <v>401</v>
-      </c>
-      <c r="B32" s="25" t="n">
-        <v>0.98525</v>
-      </c>
-      <c r="C32" s="25" t="n">
-        <v>0.90425</v>
-      </c>
-      <c r="D32" s="25" t="n">
-        <v>0.99625</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>0.9605</v>
-      </c>
-      <c r="F32" s="58" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G32" s="58" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H32" s="21" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51" t="s">
-        <v>402</v>
-      </c>
-      <c r="B33" s="25" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="C33" s="25" t="n">
-        <v>0.8385</v>
-      </c>
-      <c r="D33" s="25" t="n">
-        <v>0.98725</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="F33" s="58" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G33" s="58" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H33" s="21" t="n">
-        <v>0.325</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="48" t="s">
+      <c r="B41" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="48" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="48" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="48" t="s">
-        <v>406</v>
+    <row r="42" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="49" t="s">
+        <v>438</v>
+      </c>
+      <c r="B42" s="50" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="C42" s="50" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="D42" s="49" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="B43" s="29" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="C43" s="29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="B44" s="29" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="C44" s="29" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="B45" s="29" t="n">
+        <v>0.818</v>
+      </c>
+      <c r="C45" s="29" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="D45" s="23"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="B46" s="29" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="C46" s="29" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="D46" s="23"/>
+    </row>
+    <row r="47" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C47" s="29" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="B48" s="29" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="C48" s="29" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D48" s="23"/>
+    </row>
+    <row r="49" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="B49" s="54" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="C49" s="54" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="B50" s="29" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="C50" s="29" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="B51" s="29" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="C51" s="29" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -7487,7 +8910,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
@@ -7500,637 +8923,683 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>407</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>408</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
-        <v>409</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>410</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>411</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>412</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>413</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>414</v>
+      <c r="A4" s="36" t="s">
+        <v>457</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>460</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>461</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>417</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>418</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>419</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>421</v>
+      <c r="A5" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>424</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>425</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>426</v>
+      <c r="C6" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>429</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="A7" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="D7" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>431</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>421</v>
+      <c r="E7" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="B8" s="26" t="s">
+      <c r="A8" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>432</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="C8" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="D8" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>434</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>421</v>
+      <c r="E8" s="30" t="s">
+        <v>481</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="D9" s="26" t="s">
+      <c r="A9" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="26" t="s">
-        <v>436</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>437</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>421</v>
+      <c r="E9" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>440</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>441</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>442</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>443</v>
+      <c r="A10" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>487</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>444</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>445</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>446</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>447</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>443</v>
+      <c r="A11" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>492</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>493</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>494</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>495</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>449</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>450</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>451</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>443</v>
+      <c r="A12" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>496</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>497</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>498</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>429</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>453</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>443</v>
+      <c r="A13" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>501</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>454</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>456</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>443</v>
+      <c r="A14" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>503</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>504</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>505</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B15" s="26" t="s">
+      <c r="A15" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B15" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>462</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>443</v>
+      <c r="C15" s="30" t="s">
+        <v>507</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>509</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>510</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>463</v>
-      </c>
-      <c r="D16" s="26" t="s">
+      <c r="A16" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>512</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>513</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>514</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B17" s="30" t="s">
         <v>464</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="D17" s="26" t="s">
+      <c r="C17" s="30" t="s">
+        <v>516</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>517</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>518</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>519</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>520</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>521</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>522</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>523</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>525</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>526</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>527</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>528</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>531</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>532</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>534</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>535</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>536</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>538</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>539</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>541</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>543</v>
+      </c>
+      <c r="G23" s="30" t="s">
         <v>469</v>
       </c>
-      <c r="E17" s="26" t="s">
-        <v>470</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>471</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>472</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>473</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>474</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>475</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>477</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>479</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>482</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>483</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>484</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>485</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C21" s="26" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="s">
         <v>486</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>487</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>488</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>489</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>490</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="B24" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D24" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E24" s="30" t="s">
+        <v>545</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>546</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>531</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="G25" s="30" t="s">
         <v>491</v>
       </c>
-      <c r="F22" s="26" t="s">
-        <v>492</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B23" s="26" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B26" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>493</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>494</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>495</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>496</v>
-      </c>
-      <c r="D24" s="26" t="s">
+      <c r="C26" s="30" t="s">
+        <v>550</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>551</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>552</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>553</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>554</v>
+      </c>
+      <c r="D27" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>499</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>483</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>500</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>503</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>504</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>505</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>506</v>
-      </c>
-      <c r="D27" s="26" t="s">
+      <c r="E27" s="30" t="s">
+        <v>555</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>556</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>557</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>558</v>
+      </c>
+      <c r="D28" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="26" t="s">
-        <v>507</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>508</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>510</v>
-      </c>
-      <c r="D28" s="26" t="s">
+      <c r="E28" s="30" t="s">
+        <v>559</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>560</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>561</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>562</v>
+      </c>
+      <c r="D29" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="26" t="s">
-        <v>511</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>512</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>513</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="D29" s="26" t="s">
+      <c r="E29" s="30" t="s">
+        <v>563</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>564</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30" t="s">
+        <v>565</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>566</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>567</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>568</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>569</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="30" t="s">
+        <v>565</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>570</v>
+      </c>
+      <c r="D31" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="26" t="s">
-        <v>515</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>516</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="s">
-        <v>517</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>518</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>519</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>521</v>
-      </c>
-      <c r="G30" s="26" t="s">
-        <v>443</v>
+      <c r="E31" s="30" t="s">
+        <v>571</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>572</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="30" t="s">
+        <v>565</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>573</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>574</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>575</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>576</v>
+      </c>
+      <c r="G32" s="30" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G30"/>
+  <autoFilter ref="A4:G32"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/Severance Design Docs.xlsx
+++ b/docs/Severance Design Docs.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Balance Log" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Balance Log'!$A$4:$G$32</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Balance Log'!$A$4:$G$33</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Order'!$A$4:$H$24</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="599">
   <si>
     <t xml:space="preserve">Severance - Monster Stats</t>
   </si>
@@ -949,7 +949,7 @@
     <t xml:space="preserve">Smarter sim bot</t>
   </si>
   <si>
-    <t xml:space="preserve">Use AOE when 2+ enemies, strongest ability first. Current bot uses abilities in menu order, so Spaceship numbers are low</t>
+    <t xml:space="preserve">AOE when 2+ enemies, strongest ability first, heals below half HP, Mana Tide only when nothing else is ready. Paladin Spaceship 48% -&gt; 86%</t>
   </si>
   <si>
     <t xml:space="preserve">Paladin Faith bar</t>
@@ -1399,6 +1399,57 @@
     <t xml:space="preserve">Spaceship at Lv 2 with the same bot: Paladin 48%, Sorcerer 61%. Low for both because the bot uses abilities in menu order (no AOE priority) - see Build Order step 7.</t>
   </si>
   <si>
+    <t xml:space="preserve">Test 4: Sorcerer mana in the Spaceship (smarter bot: AOE first, best ability, Mana Tide on off-turns; 5,000-8,000 runs each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorcerer before (regen 4, Chain Lightning 20 MP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs out of mana against groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana regen 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes the Rainforest too easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana regen 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max mana 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Bolt 8 MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain Lightning 15 MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only changes the Spaceship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain Lightning 12 MP (chosen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slightly harder than the Paladin on purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain Lightning 10 MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the Paladin exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain Lightning 15 MP, 1.3x power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Changing regen or max mana affects every fight from Lv 1, so the Rainforest gets too easy. Chain Lightning unlocks at Lv 2 (after the Rainforest boss), so it only changes the Spaceship.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  10 MP would have matched the Paladin exactly, but we picked 12 MP to keep a little bit of a challenge for the Sorcerer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Balance Log</t>
   </si>
   <si>
@@ -1766,6 +1817,18 @@
   </si>
   <si>
     <t xml:space="preserve">Simulation (Micha's simulate.py)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain Lightning mana cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorcerer ran out of mana in the Spaceship (64% vs Paladin 86%). 10 MP would have matched the Paladin exactly (86%), but we went with 12 (83%) to keep a little bit of a challenge. Rainforest unaffected (unlocks at Lv 2)</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +2019,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2187,6 +2250,10 @@
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4676,7 +4743,7 @@
         <v>101</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I50" s="26" t="s">
         <v>22</v>
@@ -6602,27 +6669,27 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="20" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
         <v>280</v>
       </c>
@@ -6648,7 +6715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="n">
         <v>1</v>
       </c>
@@ -6674,7 +6741,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="n">
         <v>2</v>
       </c>
@@ -6700,7 +6767,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="n">
         <v>3</v>
       </c>
@@ -6726,7 +6793,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="n">
         <v>4</v>
       </c>
@@ -6752,7 +6819,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="n">
         <v>5</v>
       </c>
@@ -6778,7 +6845,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="n">
         <v>6</v>
       </c>
@@ -6804,7 +6871,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="n">
         <v>7</v>
       </c>
@@ -6815,7 +6882,7 @@
         <v>111</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>288</v>
@@ -6826,11 +6893,11 @@
       <c r="G11" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="H11" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H11" s="38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="n">
         <v>8</v>
       </c>
@@ -6856,7 +6923,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="37" t="n">
         <v>9</v>
       </c>
@@ -6882,7 +6949,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="n">
         <v>10</v>
       </c>
@@ -6908,7 +6975,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="n">
         <v>11</v>
       </c>
@@ -6934,7 +7001,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="n">
         <v>12</v>
       </c>
@@ -6960,7 +7027,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="n">
         <v>13</v>
       </c>
@@ -6986,7 +7053,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="n">
         <v>14</v>
       </c>
@@ -7012,7 +7079,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="n">
         <v>15</v>
       </c>
@@ -7038,7 +7105,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="n">
         <v>16</v>
       </c>
@@ -7064,7 +7131,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="n">
         <v>17</v>
       </c>
@@ -7090,7 +7157,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="n">
         <v>18</v>
       </c>
@@ -7116,7 +7183,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="n">
         <v>19</v>
       </c>
@@ -7142,7 +7209,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="n">
         <v>20</v>
       </c>
@@ -8205,7 +8272,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -8892,6 +8959,175 @@
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>454</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="22" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="49" t="s">
+        <v>438</v>
+      </c>
+      <c r="B57" s="50" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C57" s="50" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="D57" s="49" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B58" s="29" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="C58" s="29" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B59" s="29" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="C59" s="29" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B60" s="29" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="C60" s="29" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="D60" s="23" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="B61" s="29" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="C61" s="29" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="B62" s="29" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="C62" s="29" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="B63" s="29" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C63" s="29" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="53" t="s">
+        <v>465</v>
+      </c>
+      <c r="B64" s="54" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C64" s="54" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="D64" s="53" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="B65" s="29" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C65" s="29" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="B66" s="29" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C66" s="29" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="58" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="58" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -8910,7 +9146,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
@@ -8923,683 +9159,706 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>282</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B8" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B11" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B12" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B15" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="D15" s="30" t="s">
+        <v>525</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>526</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>527</v>
+      </c>
+      <c r="G15" s="30" t="s">
         <v>508</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>509</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>510</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B16" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="G17" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B19" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="G19" s="30" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B21" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="G21" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>208</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="D22" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="G22" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B23" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="E23" s="30" t="s">
         <v>220</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="G23" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B24" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="D24" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B25" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="G25" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B26" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B27" s="30" t="s">
         <v>271</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="D27" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="30" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="B30" s="30" t="s">
         <v>269</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>72</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="D31" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="G31" s="30" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="30" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="B32" s="30" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="G32" s="30" t="s">
-        <v>577</v>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="30" t="s">
+        <v>582</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>595</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>596</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>597</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>598</v>
+      </c>
+      <c r="G33" s="30" t="s">
+        <v>594</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G32"/>
+  <autoFilter ref="A4:G33"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/Severance Design Docs.xlsx
+++ b/docs/Severance Design Docs.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Balance Log'!$A$4:$G$33</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Order'!$A$4:$H$24</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Order'!$A$4:$H$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="594">
   <si>
     <t xml:space="preserve">Severance - Monster Stats</t>
   </si>
@@ -256,9 +256,6 @@
     <t xml:space="preserve">Magic</t>
   </si>
   <si>
-    <t xml:space="preserve">Planned: Paladin Faith bar (fills when you take damage, buffs your next ability when full). See the Sim Results tab.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sorcerer starts every dungeon with full mana and regenerates mana each turn. Its abilities use the elements from the Sorcerer note.</t>
   </si>
   <si>
@@ -910,7 +907,7 @@
     <t xml:space="preserve">Automated tests (pytest)</t>
   </si>
   <si>
-    <t xml:space="preserve">8 tests: damage, blocking, healing, level-up stats, ability unlock, cooldowns. Run with: pytest -v</t>
+    <t xml:space="preserve">16 tests: damage, healing, levelling, mana, cooldowns, sim bot. Run with: python -m pytest -v</t>
   </si>
   <si>
     <t xml:space="preserve">Mana bar</t>
@@ -925,13 +922,13 @@
     <t xml:space="preserve">Micha + Claude</t>
   </si>
   <si>
-    <t xml:space="preserve">Runs 1,000 dungeons with a smart bot and a mash bot, pick the class. Run with: python -m sims.simulate</t>
+    <t xml:space="preserve">Smart bot vs mash bot, pick class and dungeon (or All), rounds with averages and a summary table. Run with: python -m sims.simulate</t>
   </si>
   <si>
     <t xml:space="preserve">Sorcerer class + Mana Tide</t>
   </si>
   <si>
-    <t xml:space="preserve">ManaAbility, 7 elemental abilities, class select. Add tests: can't cast without mana, regen caps at max</t>
+    <t xml:space="preserve">ManaAbility, 7 elemental abilities, class select</t>
   </si>
   <si>
     <t xml:space="preserve">Sorcerer balance sims</t>
@@ -943,57 +940,57 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">Rainforest: 35% -&gt; 86% after 100 HP, 5 Def, Fire Bolt 1.8x. Results on Sim Results tab</t>
+    <t xml:space="preserve">100 HP, 5 Def, Fire Bolt 1.8x, Chain Lightning 12 MP. Results on Sim Results tab</t>
   </si>
   <si>
     <t xml:space="preserve">Smarter sim bot</t>
   </si>
   <si>
-    <t xml:space="preserve">AOE when 2+ enemies, strongest ability first, heals below half HP, Mana Tide only when nothing else is ready. Paladin Spaceship 48% -&gt; 86%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paladin Faith bar</t>
+    <t xml:space="preserve">AOE when 2+ enemies, strongest ability first, heals below half HP, Mana Tide only when nothing else is ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save / Load (JSON)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">save.py: saves name, class, level, XP after clearing a dungeon. Continue screen shows the saved hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tutorial tips per room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tips dict, print in dungeon()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XP rework: small XP from enemies, big from bosses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All dungeons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbers only. Suggested split is on Dungeon Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheetah Growl (stun)</t>
   </si>
   <si>
     <t xml:space="preserve">Micha (mechanic) + Claude (numbers)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fills when you take damage. When full, your next ability gets a power buff, then it empties. Sims on the Sim Results tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-tune enemies for Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All dungeons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faith makes the Paladin stronger, so enemies need a small buff to keep the same difficulty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tutorial tips per room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tips dict, print in dungeon()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XP rework: small XP from enemies, big from bosses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbers only. Suggested split is on Dungeon Plans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheetah Growl (stun)</t>
-  </si>
-  <si>
     <t xml:space="preserve">stunned flag, Move effect, skip turn. No damage vs 0.5x hit undecided</t>
   </si>
   <si>
     <t xml:space="preserve">Undecided</t>
   </si>
   <si>
+    <t xml:space="preserve">Loot / gear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pillar set (common) + subclass set (rare) from Dungeon 2 on. Bonus loot per Spaceship path. Add to the save file</t>
+  </si>
+  <si>
     <t xml:space="preserve">Floors + recon clones</t>
   </si>
   <si>
@@ -1021,21 +1018,15 @@
     <t xml:space="preserve">Boss adds enemies to the fight mid-battle</t>
   </si>
   <si>
-    <t xml:space="preserve">Loot / gear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pillar set (common) + subclass set (rare) from Dungeon 2 on. Bonus loot per Spaceship path</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gold + shops</t>
   </si>
   <si>
     <t xml:space="preserve">Outpost</t>
   </si>
   <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enemies/bosses drop gold, spend at a shop between dungeons (e.g. mana potions)</t>
   </si>
   <si>
@@ -1048,12 +1039,6 @@
     <t xml:space="preserve">Talk to NPCs between dungeons: lore, hints, quests later</t>
   </si>
   <si>
-    <t xml:space="preserve">Save / Load (JSON)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From the Text Prototype build plan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Polish: colours + ASCII art</t>
   </si>
   <si>
@@ -1207,7 +1192,7 @@
     <t xml:space="preserve">Each number = 4,000 simulated full runs of the dungeon (run by Claude, 1 Oct 2026). Smart = reacts to warnings and uses abilities well. Casual = uses whatever is ready, ignores warnings.</t>
   </si>
   <si>
-    <t xml:space="preserve">Idea: Paladin Faith Bar</t>
+    <t xml:space="preserve">Idea: Paladin Faith Bar (dropped)</t>
   </si>
   <si>
     <t xml:space="preserve">•  Faith fills up when the Paladin takes damage (e.g. 2 Faith for every 1 HP lost, full at 100).</t>
@@ -1222,7 +1207,7 @@
     <t xml:space="preserve">•  Open questions: how big the buff is, whether Faith resets each room or carries over, and whether Defend / Divine Aegis add Faith.</t>
   </si>
   <si>
-    <t xml:space="preserve">Status: idea only, not in the code yet. Build Order steps 6-7.</t>
+    <t xml:space="preserve">Status: DROPPED (1 Oct 2026). Decided the Paladin is fine as he is. Kept here for reference.</t>
   </si>
   <si>
     <t xml:space="preserve">Test 1: Should the Paladin have a bar? (Holy Strike costs from the bar, keeps its 4-turn cooldown)</t>
@@ -1285,7 +1270,7 @@
     <t xml:space="preserve">Resolve: fills from damage taken, Holy Strike costs 20</t>
   </si>
   <si>
-    <t xml:space="preserve">Result: Faith (below) was picked over mana and Resolve. It doesn't lock abilities, it rewards taking hits.</t>
+    <t xml:space="preserve">Result: Faith (below) was picked over mana and Resolve, but the whole idea was later dropped - the Paladin stays as he is.</t>
   </si>
   <si>
     <t xml:space="preserve">Test 2: Faith bar - fills from damage taken, buffs your next ability when full</t>
@@ -1336,7 +1321,7 @@
     <t xml:space="preserve">•  Suggested start (green): 2 Faith per HP lost, full at 100, +25% buff, resets each room. About 1-2 buffs per dungeon, +5% smart / +9% casual win rate.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  After adding Faith, re-tune enemies slightly (Build Order step 7) to get back to the old difficulty.</t>
+    <t xml:space="preserve">•  If Faith ever comes back: re-tune enemies slightly afterwards to get back to the old difficulty.</t>
   </si>
   <si>
     <t xml:space="preserve">Test 3: Sorcerer stats - Rainforest at Lv 1 (Micha's simulate.py, 3,000 runs each)</t>
@@ -1835,7 +1820,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="General"/>
@@ -1843,9 +1828,8 @@
     <numFmt numFmtId="168" formatCode="0.0\x"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0.00\x"/>
-    <numFmt numFmtId="171" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1921,6 +1905,15 @@
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFAA3333"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2019,7 +2012,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2100,18 +2093,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2188,7 +2169,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2196,7 +2177,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2214,6 +2195,10 @@
     </xf>
     <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2250,10 +2235,6 @@
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2361,7 +2342,7 @@
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFAA3333"/>
       <rgbColor rgb="FFFFF4D6"/>
       <rgbColor rgb="FFEEF0F4"/>
       <rgbColor rgb="FF660066"/>
@@ -3367,31 +3348,31 @@
   <dimension ref="A1:N81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3439,474 +3420,469 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="21" t="n">
         <v>120</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="24" t="n">
+      <c r="H6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="24" t="n">
+      <c r="I6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="25" t="n">
+      <c r="J6" s="22" t="n">
         <f aca="false">1-1/I6</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="K6" s="24" t="n">
+      <c r="K6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="24" t="n">
+      <c r="L6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="N6" s="26" t="s">
+      <c r="N6" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="24" t="n">
+      <c r="H7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="25" t="n">
+      <c r="J7" s="22" t="n">
         <f aca="false">1-1/I7</f>
         <v>0.5</v>
       </c>
-      <c r="K7" s="24" t="n">
+      <c r="K7" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="L7" s="24" t="n">
+      <c r="L7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="N7" s="26" t="s">
+      <c r="N7" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="M12" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="M12" s="4" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
+      <c r="B13" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="C13" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="D13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="24" t="n">
+      <c r="H13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="23" t="n">
         <f aca="false">INDEX($C$24:$C$43,D13)</f>
         <v>10</v>
       </c>
-      <c r="K13" s="26" t="n">
+      <c r="K13" s="23" t="n">
         <f aca="false">ROUND(J13*E13,0)</f>
         <v>13</v>
       </c>
-      <c r="L13" s="26" t="n">
+      <c r="L13" s="23" t="n">
         <f aca="false">ROUND($C$43*E13,0)</f>
         <v>38</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
+      <c r="B14" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="24" t="n">
+      <c r="H14" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="I14" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="26" t="n">
+      <c r="J14" s="23" t="n">
         <f aca="false">INDEX($C$24:$C$43,D14)</f>
         <v>10</v>
       </c>
-      <c r="K14" s="26" t="n">
+      <c r="K14" s="23" t="n">
         <f aca="false">ROUND(J14*E14,0)</f>
         <v>20</v>
       </c>
-      <c r="L14" s="26" t="n">
+      <c r="L14" s="23" t="n">
         <f aca="false">ROUND($C$43*E14,0)</f>
         <v>58</v>
       </c>
-      <c r="M14" s="23" t="s">
+      <c r="M14" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="B15" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="C15" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="D15" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="24" t="n">
+      <c r="H15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="26" t="s">
+      <c r="I15" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="26" t="n">
+      <c r="J15" s="23" t="n">
         <f aca="false">INDEX($C$24:$C$43,D15)</f>
         <v>11</v>
       </c>
-      <c r="K15" s="26" t="n">
+      <c r="K15" s="23" t="n">
         <f aca="false">ROUND(J15*E15,0)</f>
         <v>14</v>
       </c>
-      <c r="L15" s="26" t="n">
+      <c r="L15" s="23" t="n">
         <f aca="false">ROUND($C$43*E15,0)</f>
         <v>38</v>
       </c>
-      <c r="M15" s="23" t="s">
+      <c r="M15" s="20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="B16" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="C16" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="D16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="H16" s="24" t="n">
+      <c r="H16" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J16" s="23" t="n">
         <f aca="false">INDEX($C$24:$C$43,D16)</f>
         <v>14</v>
       </c>
-      <c r="K16" s="26" t="str">
+      <c r="K16" s="23" t="str">
         <f aca="false">ROUND(INDEX($B$24:$B$43,D16)*E16,0)&amp;" HP"</f>
         <v>42 HP</v>
       </c>
-      <c r="L16" s="26" t="str">
+      <c r="L16" s="23" t="str">
         <f aca="false">ROUND($B$43*E16,0)&amp;" HP"</f>
         <v>87 HP</v>
       </c>
-      <c r="M16" s="23" t="s">
+      <c r="M16" s="20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
+      <c r="B17" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G17" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="24" t="n">
+      <c r="G17" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="23" t="n">
         <f aca="false">INDEX($C$24:$C$43,D17)</f>
         <v>18</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="M17" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="L17" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="M17" s="23" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
+      <c r="B18" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="C18" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="24" t="n">
         <v>1.6</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G18" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" s="24" t="n">
+      <c r="G18" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="I18" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="23" t="n">
         <f aca="false">INDEX($C$24:$C$43,D18)</f>
         <v>22</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="23" t="n">
         <f aca="false">ROUND(J18*E18,0)</f>
         <v>35</v>
       </c>
-      <c r="L18" s="26" t="n">
+      <c r="L18" s="23" t="n">
         <f aca="false">ROUND($C$43*E18,0)</f>
         <v>46</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="M18" s="20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
+      <c r="B19" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="24" t="n">
+      <c r="H19" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="26" t="s">
+      <c r="I19" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="23" t="n">
         <f aca="false">INDEX($C$24:$C$43,D19)</f>
         <v>29</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="23" t="n">
         <f aca="false">ROUND(J19*E19,0)</f>
         <v>116</v>
       </c>
-      <c r="L19" s="26" t="n">
+      <c r="L19" s="23" t="n">
         <f aca="false">ROUND($C$43*E19,0)</f>
         <v>116</v>
       </c>
-      <c r="M19" s="23" t="s">
+      <c r="M19" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
@@ -3918,1042 +3894,1042 @@
         <v>11</v>
       </c>
       <c r="F23" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="n">
+    </row>
+    <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="23" t="n">
         <f aca="false">$C$6+(A24-1)*$F$6</f>
         <v>120</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="23" t="n">
         <f aca="false">$D$6+(A24-1)*$G$6</f>
         <v>10</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="23" t="n">
         <f aca="false">$E$6+(A24-1)*$H$6</f>
         <v>6</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="26" t="n">
         <f aca="false">1-100/(100+D24)</f>
         <v>0.0566037735849057</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="23" t="n">
         <f aca="false">IF(A24&lt;$M$6,50*A24,"MAX")</f>
         <v>50</v>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G24" s="23" t="n">
         <f aca="false">25*A24*(A24-1)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="n">
+      <c r="H24" s="20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="23" t="n">
         <f aca="false">$C$6+(A25-1)*$F$6</f>
         <v>132</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="23" t="n">
         <f aca="false">$D$6+(A25-1)*$G$6</f>
         <v>11</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="23" t="n">
         <f aca="false">$E$6+(A25-1)*$H$6</f>
         <v>9</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="26" t="n">
         <f aca="false">1-100/(100+D25)</f>
         <v>0.0825688073394495</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="23" t="n">
         <f aca="false">IF(A25&lt;$M$6,50*A25,"MAX")</f>
         <v>100</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="23" t="n">
         <f aca="false">25*A25*(A25-1)</f>
         <v>50</v>
       </c>
-      <c r="H25" s="23" t="str">
+      <c r="H25" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A25,$D$13:$D$19,0)),"")</f>
         <v>Holy Ground</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="23" t="n">
         <f aca="false">$C$6+(A26-1)*$F$6</f>
         <v>144</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="23" t="n">
         <f aca="false">$D$6+(A26-1)*$G$6</f>
         <v>12</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="23" t="n">
         <f aca="false">$E$6+(A26-1)*$H$6</f>
         <v>12</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="26" t="n">
         <f aca="false">1-100/(100+D26)</f>
         <v>0.107142857142857</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="23" t="n">
         <f aca="false">IF(A26&lt;$M$6,50*A26,"MAX")</f>
         <v>150</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="23" t="n">
         <f aca="false">25*A26*(A26-1)</f>
         <v>150</v>
       </c>
-      <c r="H26" s="23" t="str">
+      <c r="H26" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A26,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="23" t="n">
         <f aca="false">$C$6+(A27-1)*$F$6</f>
         <v>156</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="23" t="n">
         <f aca="false">$D$6+(A27-1)*$G$6</f>
         <v>13</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="23" t="n">
         <f aca="false">$E$6+(A27-1)*$H$6</f>
         <v>15</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="26" t="n">
         <f aca="false">1-100/(100+D27)</f>
         <v>0.130434782608696</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="23" t="n">
         <f aca="false">IF(A27&lt;$M$6,50*A27,"MAX")</f>
         <v>200</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="23" t="n">
         <f aca="false">25*A27*(A27-1)</f>
         <v>300</v>
       </c>
-      <c r="H27" s="23" t="str">
+      <c r="H27" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A27,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="23" t="n">
         <f aca="false">$C$6+(A28-1)*$F$6</f>
         <v>168</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="23" t="n">
         <f aca="false">$D$6+(A28-1)*$G$6</f>
         <v>14</v>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="23" t="n">
         <f aca="false">$E$6+(A28-1)*$H$6</f>
         <v>18</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="26" t="n">
         <f aca="false">1-100/(100+D28)</f>
         <v>0.152542372881356</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="23" t="n">
         <f aca="false">IF(A28&lt;$M$6,50*A28,"MAX")</f>
         <v>250</v>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="23" t="n">
         <f aca="false">25*A28*(A28-1)</f>
         <v>500</v>
       </c>
-      <c r="H28" s="23" t="str">
+      <c r="H28" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A28,$D$13:$D$19,0)),"")</f>
         <v>Lay on Hands</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="23" t="n">
         <f aca="false">$C$6+(A29-1)*$F$6</f>
         <v>180</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="23" t="n">
         <f aca="false">$D$6+(A29-1)*$G$6</f>
         <v>15</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="23" t="n">
         <f aca="false">$E$6+(A29-1)*$H$6</f>
         <v>21</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="26" t="n">
         <f aca="false">1-100/(100+D29)</f>
         <v>0.173553719008264</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="23" t="n">
         <f aca="false">IF(A29&lt;$M$6,50*A29,"MAX")</f>
         <v>300</v>
       </c>
-      <c r="G29" s="26" t="n">
+      <c r="G29" s="23" t="n">
         <f aca="false">25*A29*(A29-1)</f>
         <v>750</v>
       </c>
-      <c r="H29" s="23" t="str">
+      <c r="H29" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A29,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="23" t="n">
         <f aca="false">$C$6+(A30-1)*$F$6</f>
         <v>192</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="23" t="n">
         <f aca="false">$D$6+(A30-1)*$G$6</f>
         <v>16</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="23" t="n">
         <f aca="false">$E$6+(A30-1)*$H$6</f>
         <v>24</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="26" t="n">
         <f aca="false">1-100/(100+D30)</f>
         <v>0.193548387096774</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="23" t="n">
         <f aca="false">IF(A30&lt;$M$6,50*A30,"MAX")</f>
         <v>350</v>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G30" s="23" t="n">
         <f aca="false">25*A30*(A30-1)</f>
         <v>1050</v>
       </c>
-      <c r="H30" s="23" t="str">
+      <c r="H30" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A30,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="23" t="n">
         <f aca="false">$C$6+(A31-1)*$F$6</f>
         <v>204</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="23" t="n">
         <f aca="false">$D$6+(A31-1)*$G$6</f>
         <v>17</v>
       </c>
-      <c r="D31" s="26" t="n">
+      <c r="D31" s="23" t="n">
         <f aca="false">$E$6+(A31-1)*$H$6</f>
         <v>27</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="26" t="n">
         <f aca="false">1-100/(100+D31)</f>
         <v>0.21259842519685</v>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="23" t="n">
         <f aca="false">IF(A31&lt;$M$6,50*A31,"MAX")</f>
         <v>400</v>
       </c>
-      <c r="G31" s="26" t="n">
+      <c r="G31" s="23" t="n">
         <f aca="false">25*A31*(A31-1)</f>
         <v>1400</v>
       </c>
-      <c r="H31" s="23" t="str">
+      <c r="H31" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A31,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="23" t="n">
         <f aca="false">$C$6+(A32-1)*$F$6</f>
         <v>216</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="23" t="n">
         <f aca="false">$D$6+(A32-1)*$G$6</f>
         <v>18</v>
       </c>
-      <c r="D32" s="26" t="n">
+      <c r="D32" s="23" t="n">
         <f aca="false">$E$6+(A32-1)*$H$6</f>
         <v>30</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="26" t="n">
         <f aca="false">1-100/(100+D32)</f>
         <v>0.230769230769231</v>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="23" t="n">
         <f aca="false">IF(A32&lt;$M$6,50*A32,"MAX")</f>
         <v>450</v>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G32" s="23" t="n">
         <f aca="false">25*A32*(A32-1)</f>
         <v>1800</v>
       </c>
-      <c r="H32" s="23" t="str">
+      <c r="H32" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A32,$D$13:$D$19,0)),"")</f>
         <v>Divine Aegis</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="23" t="n">
         <f aca="false">$C$6+(A33-1)*$F$6</f>
         <v>228</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="23" t="n">
         <f aca="false">$D$6+(A33-1)*$G$6</f>
         <v>19</v>
       </c>
-      <c r="D33" s="26" t="n">
+      <c r="D33" s="23" t="n">
         <f aca="false">$E$6+(A33-1)*$H$6</f>
         <v>33</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="26" t="n">
         <f aca="false">1-100/(100+D33)</f>
         <v>0.24812030075188</v>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="23" t="n">
         <f aca="false">IF(A33&lt;$M$6,50*A33,"MAX")</f>
         <v>500</v>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G33" s="23" t="n">
         <f aca="false">25*A33*(A33-1)</f>
         <v>2250</v>
       </c>
-      <c r="H33" s="23" t="str">
+      <c r="H33" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A33,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="26" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="23" t="n">
         <f aca="false">$C$6+(A34-1)*$F$6</f>
         <v>240</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="23" t="n">
         <f aca="false">$D$6+(A34-1)*$G$6</f>
         <v>20</v>
       </c>
-      <c r="D34" s="26" t="n">
+      <c r="D34" s="23" t="n">
         <f aca="false">$E$6+(A34-1)*$H$6</f>
         <v>36</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="26" t="n">
         <f aca="false">1-100/(100+D34)</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="23" t="n">
         <f aca="false">IF(A34&lt;$M$6,50*A34,"MAX")</f>
         <v>550</v>
       </c>
-      <c r="G34" s="26" t="n">
+      <c r="G34" s="23" t="n">
         <f aca="false">25*A34*(A34-1)</f>
         <v>2750</v>
       </c>
-      <c r="H34" s="23" t="str">
+      <c r="H34" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A34,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="23" t="n">
         <f aca="false">$C$6+(A35-1)*$F$6</f>
         <v>252</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="23" t="n">
         <f aca="false">$D$6+(A35-1)*$G$6</f>
         <v>21</v>
       </c>
-      <c r="D35" s="26" t="n">
+      <c r="D35" s="23" t="n">
         <f aca="false">$E$6+(A35-1)*$H$6</f>
         <v>39</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="26" t="n">
         <f aca="false">1-100/(100+D35)</f>
         <v>0.280575539568345</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="23" t="n">
         <f aca="false">IF(A35&lt;$M$6,50*A35,"MAX")</f>
         <v>600</v>
       </c>
-      <c r="G35" s="26" t="n">
+      <c r="G35" s="23" t="n">
         <f aca="false">25*A35*(A35-1)</f>
         <v>3300</v>
       </c>
-      <c r="H35" s="23" t="str">
+      <c r="H35" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A35,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="26" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="23" t="n">
         <f aca="false">$C$6+(A36-1)*$F$6</f>
         <v>264</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="23" t="n">
         <f aca="false">$D$6+(A36-1)*$G$6</f>
         <v>22</v>
       </c>
-      <c r="D36" s="26" t="n">
+      <c r="D36" s="23" t="n">
         <f aca="false">$E$6+(A36-1)*$H$6</f>
         <v>42</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="26" t="n">
         <f aca="false">1-100/(100+D36)</f>
         <v>0.295774647887324</v>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="23" t="n">
         <f aca="false">IF(A36&lt;$M$6,50*A36,"MAX")</f>
         <v>650</v>
       </c>
-      <c r="G36" s="26" t="n">
+      <c r="G36" s="23" t="n">
         <f aca="false">25*A36*(A36-1)</f>
         <v>3900</v>
       </c>
-      <c r="H36" s="23" t="str">
+      <c r="H36" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A36,$D$13:$D$19,0)),"")</f>
         <v>Radiant Slash</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="26" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="23" t="n">
         <f aca="false">$C$6+(A37-1)*$F$6</f>
         <v>276</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="23" t="n">
         <f aca="false">$D$6+(A37-1)*$G$6</f>
         <v>23</v>
       </c>
-      <c r="D37" s="26" t="n">
+      <c r="D37" s="23" t="n">
         <f aca="false">$E$6+(A37-1)*$H$6</f>
         <v>45</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="26" t="n">
         <f aca="false">1-100/(100+D37)</f>
         <v>0.310344827586207</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="23" t="n">
         <f aca="false">IF(A37&lt;$M$6,50*A37,"MAX")</f>
         <v>700</v>
       </c>
-      <c r="G37" s="26" t="n">
+      <c r="G37" s="23" t="n">
         <f aca="false">25*A37*(A37-1)</f>
         <v>4550</v>
       </c>
-      <c r="H37" s="23" t="str">
+      <c r="H37" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A37,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="26" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="23" t="n">
         <f aca="false">$C$6+(A38-1)*$F$6</f>
         <v>288</v>
       </c>
-      <c r="C38" s="26" t="n">
+      <c r="C38" s="23" t="n">
         <f aca="false">$D$6+(A38-1)*$G$6</f>
         <v>24</v>
       </c>
-      <c r="D38" s="26" t="n">
+      <c r="D38" s="23" t="n">
         <f aca="false">$E$6+(A38-1)*$H$6</f>
         <v>48</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="26" t="n">
         <f aca="false">1-100/(100+D38)</f>
         <v>0.324324324324324</v>
       </c>
-      <c r="F38" s="26" t="n">
+      <c r="F38" s="23" t="n">
         <f aca="false">IF(A38&lt;$M$6,50*A38,"MAX")</f>
         <v>750</v>
       </c>
-      <c r="G38" s="26" t="n">
+      <c r="G38" s="23" t="n">
         <f aca="false">25*A38*(A38-1)</f>
         <v>5250</v>
       </c>
-      <c r="H38" s="23" t="str">
+      <c r="H38" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A38,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="26" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B39" s="26" t="n">
+      <c r="B39" s="23" t="n">
         <f aca="false">$C$6+(A39-1)*$F$6</f>
         <v>300</v>
       </c>
-      <c r="C39" s="26" t="n">
+      <c r="C39" s="23" t="n">
         <f aca="false">$D$6+(A39-1)*$G$6</f>
         <v>25</v>
       </c>
-      <c r="D39" s="26" t="n">
+      <c r="D39" s="23" t="n">
         <f aca="false">$E$6+(A39-1)*$H$6</f>
         <v>51</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="26" t="n">
         <f aca="false">1-100/(100+D39)</f>
         <v>0.337748344370861</v>
       </c>
-      <c r="F39" s="26" t="n">
+      <c r="F39" s="23" t="n">
         <f aca="false">IF(A39&lt;$M$6,50*A39,"MAX")</f>
         <v>800</v>
       </c>
-      <c r="G39" s="26" t="n">
+      <c r="G39" s="23" t="n">
         <f aca="false">25*A39*(A39-1)</f>
         <v>6000</v>
       </c>
-      <c r="H39" s="23" t="str">
+      <c r="H39" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A39,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="26" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="26" t="n">
+      <c r="B40" s="23" t="n">
         <f aca="false">$C$6+(A40-1)*$F$6</f>
         <v>312</v>
       </c>
-      <c r="C40" s="26" t="n">
+      <c r="C40" s="23" t="n">
         <f aca="false">$D$6+(A40-1)*$G$6</f>
         <v>26</v>
       </c>
-      <c r="D40" s="26" t="n">
+      <c r="D40" s="23" t="n">
         <f aca="false">$E$6+(A40-1)*$H$6</f>
         <v>54</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="26" t="n">
         <f aca="false">1-100/(100+D40)</f>
         <v>0.350649350649351</v>
       </c>
-      <c r="F40" s="26" t="n">
+      <c r="F40" s="23" t="n">
         <f aca="false">IF(A40&lt;$M$6,50*A40,"MAX")</f>
         <v>850</v>
       </c>
-      <c r="G40" s="26" t="n">
+      <c r="G40" s="23" t="n">
         <f aca="false">25*A40*(A40-1)</f>
         <v>6800</v>
       </c>
-      <c r="H40" s="23" t="str">
+      <c r="H40" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A40,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="26" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B41" s="26" t="n">
+      <c r="B41" s="23" t="n">
         <f aca="false">$C$6+(A41-1)*$F$6</f>
         <v>324</v>
       </c>
-      <c r="C41" s="26" t="n">
+      <c r="C41" s="23" t="n">
         <f aca="false">$D$6+(A41-1)*$G$6</f>
         <v>27</v>
       </c>
-      <c r="D41" s="26" t="n">
+      <c r="D41" s="23" t="n">
         <f aca="false">$E$6+(A41-1)*$H$6</f>
         <v>57</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="26" t="n">
         <f aca="false">1-100/(100+D41)</f>
         <v>0.363057324840764</v>
       </c>
-      <c r="F41" s="26" t="n">
+      <c r="F41" s="23" t="n">
         <f aca="false">IF(A41&lt;$M$6,50*A41,"MAX")</f>
         <v>900</v>
       </c>
-      <c r="G41" s="26" t="n">
+      <c r="G41" s="23" t="n">
         <f aca="false">25*A41*(A41-1)</f>
         <v>7650</v>
       </c>
-      <c r="H41" s="23" t="str">
+      <c r="H41" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A41,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B42" s="26" t="n">
+      <c r="B42" s="23" t="n">
         <f aca="false">$C$6+(A42-1)*$F$6</f>
         <v>336</v>
       </c>
-      <c r="C42" s="26" t="n">
+      <c r="C42" s="23" t="n">
         <f aca="false">$D$6+(A42-1)*$G$6</f>
         <v>28</v>
       </c>
-      <c r="D42" s="26" t="n">
+      <c r="D42" s="23" t="n">
         <f aca="false">$E$6+(A42-1)*$H$6</f>
         <v>60</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="26" t="n">
         <f aca="false">1-100/(100+D42)</f>
         <v>0.375</v>
       </c>
-      <c r="F42" s="26" t="n">
+      <c r="F42" s="23" t="n">
         <f aca="false">IF(A42&lt;$M$6,50*A42,"MAX")</f>
         <v>950</v>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G42" s="23" t="n">
         <f aca="false">25*A42*(A42-1)</f>
         <v>8550</v>
       </c>
-      <c r="H42" s="23" t="str">
+      <c r="H42" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A42,$D$13:$D$19,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="26" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B43" s="26" t="n">
+      <c r="B43" s="23" t="n">
         <f aca="false">$C$6+(A43-1)*$F$6</f>
         <v>348</v>
       </c>
-      <c r="C43" s="26" t="n">
+      <c r="C43" s="23" t="n">
         <f aca="false">$D$6+(A43-1)*$G$6</f>
         <v>29</v>
       </c>
-      <c r="D43" s="26" t="n">
+      <c r="D43" s="23" t="n">
         <f aca="false">$E$6+(A43-1)*$H$6</f>
         <v>63</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="26" t="n">
         <f aca="false">1-100/(100+D43)</f>
         <v>0.386503067484663</v>
       </c>
-      <c r="F43" s="26" t="str">
+      <c r="F43" s="23" t="str">
         <f aca="false">IF(A43&lt;$M$6,50*A43,"MAX")</f>
         <v>MAX</v>
       </c>
-      <c r="G43" s="26" t="n">
+      <c r="G43" s="23" t="n">
         <f aca="false">25*A43*(A43-1)</f>
         <v>9500</v>
       </c>
-      <c r="H43" s="23" t="str">
+      <c r="H43" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$13:$A$19,MATCH(A43,$D$13:$D$19,0)),"")</f>
         <v>Judgement</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="22" t="s">
-        <v>128</v>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="19" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="C47" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="D47" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="I47" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="J47" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J47" s="4" t="s">
+      <c r="K47" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="4" t="s">
+      <c r="L47" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="L47" s="4" t="s">
+      <c r="M47" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="M47" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="B48" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D48" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F48" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H48" s="24" t="n">
+      <c r="H48" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="I48" s="26" t="s">
+      <c r="I48" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J48" s="26" t="n">
+      <c r="J48" s="23" t="n">
         <f aca="false">INDEX($C$59:$C$78,D48)</f>
         <v>13</v>
       </c>
-      <c r="K48" s="26" t="n">
+      <c r="K48" s="23" t="n">
         <f aca="false">ROUND(J48*E48,0)</f>
         <v>23</v>
       </c>
-      <c r="L48" s="26" t="n">
+      <c r="L48" s="23" t="n">
         <f aca="false">ROUND($C$78*E48,0)</f>
         <v>92</v>
       </c>
-      <c r="M48" s="23" t="s">
+      <c r="M48" s="20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23" t="s">
+      <c r="B49" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="C49" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="C49" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="D49" s="24" t="n">
+      <c r="D49" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="28" t="n">
+      <c r="E49" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="F49" s="24" t="n">
+      <c r="F49" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G49" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="H49" s="24" t="n">
+      <c r="G49" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="H49" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="26" t="s">
+      <c r="I49" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J49" s="26" t="n">
+      <c r="J49" s="23" t="n">
         <f aca="false">INDEX($C$59:$C$78,D49)</f>
         <v>13</v>
       </c>
-      <c r="K49" s="26" t="str">
+      <c r="K49" s="23" t="str">
         <f aca="false">ROUND($K$7*E49,0)&amp;" MP"</f>
         <v>24 MP</v>
       </c>
-      <c r="L49" s="26" t="str">
+      <c r="L49" s="23" t="str">
         <f aca="false">ROUND($K$7*E49,0)&amp;" MP"</f>
         <v>24 MP</v>
       </c>
-      <c r="M49" s="23" t="s">
+      <c r="M49" s="20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="26" t="s">
+      <c r="B50" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F50" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="H50" s="24" t="n">
+      <c r="H50" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="I50" s="26" t="s">
+      <c r="I50" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J50" s="26" t="n">
+      <c r="J50" s="23" t="n">
         <f aca="false">INDEX($C$59:$C$78,D50)</f>
         <v>15</v>
       </c>
-      <c r="K50" s="26" t="n">
+      <c r="K50" s="23" t="n">
         <f aca="false">ROUND(J50*E50,0)</f>
         <v>18</v>
       </c>
-      <c r="L50" s="26" t="n">
+      <c r="L50" s="23" t="n">
         <f aca="false">ROUND($C$78*E50,0)</f>
         <v>61</v>
       </c>
-      <c r="M50" s="23" t="s">
+      <c r="M50" s="20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="20" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23" t="s">
+      <c r="B51" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="B51" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="C51" s="26" t="s">
+      <c r="C51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" s="25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F51" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="D51" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E51" s="28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F51" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="H51" s="24" t="n">
+      <c r="H51" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="I51" s="26" t="s">
+      <c r="I51" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J51" s="26" t="n">
+      <c r="J51" s="23" t="n">
         <f aca="false">INDEX($C$59:$C$78,D51)</f>
         <v>21</v>
       </c>
-      <c r="K51" s="26" t="str">
+      <c r="K51" s="23" t="str">
         <f aca="false">ROUND(INDEX($B$59:$B$78,D51)*E51,0)&amp;" HP"</f>
         <v>26 HP</v>
       </c>
-      <c r="L51" s="26" t="str">
+      <c r="L51" s="23" t="str">
         <f aca="false">ROUND($B$78*E51,0)&amp;" HP"</f>
         <v>50 HP</v>
       </c>
-      <c r="M51" s="23" t="s">
+      <c r="M51" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="20" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23" t="s">
+      <c r="B52" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="C52" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D52" s="24" t="n">
+      <c r="C52" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E52" s="27" t="n">
+      <c r="E52" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="24" t="n">
+      <c r="F52" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G52" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="H52" s="24" t="n">
+      <c r="G52" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="H52" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="I52" s="26" t="s">
+      <c r="I52" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J52" s="26" t="n">
+      <c r="J52" s="23" t="n">
         <f aca="false">INDEX($C$59:$C$78,D52)</f>
         <v>29</v>
       </c>
-      <c r="K52" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="L52" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="M52" s="23" t="s">
+      <c r="K52" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L52" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="23" t="s">
+      <c r="B53" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" s="24" t="n">
+      <c r="C53" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="E53" s="27" t="n">
+      <c r="E53" s="24" t="n">
         <v>1.8</v>
       </c>
-      <c r="F53" s="24" t="n">
+      <c r="F53" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G53" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H53" s="24" t="n">
+      <c r="G53" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H53" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="I53" s="28" t="n">
+      <c r="I53" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="J53" s="26" t="n">
+      <c r="J53" s="23" t="n">
         <f aca="false">INDEX($C$59:$C$78,D53)</f>
         <v>37</v>
       </c>
-      <c r="K53" s="26" t="n">
+      <c r="K53" s="23" t="n">
         <f aca="false">ROUND(J53*E53,0)</f>
         <v>67</v>
       </c>
-      <c r="L53" s="26" t="n">
+      <c r="L53" s="23" t="n">
         <f aca="false">ROUND($C$78*E53,0)</f>
         <v>92</v>
       </c>
-      <c r="M53" s="23" t="s">
+      <c r="M53" s="20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="20" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="23" t="s">
+      <c r="B54" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="B54" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F54" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" s="27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F54" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G54" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H54" s="24" t="n">
+      <c r="H54" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="I54" s="26" t="s">
+      <c r="I54" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J54" s="26" t="n">
+      <c r="J54" s="23" t="n">
         <f aca="false">INDEX($C$59:$C$78,D54)</f>
         <v>51</v>
       </c>
-      <c r="K54" s="26" t="n">
+      <c r="K54" s="23" t="n">
         <f aca="false">ROUND(J54*E54,0)</f>
         <v>230</v>
       </c>
-      <c r="L54" s="26" t="n">
+      <c r="L54" s="23" t="n">
         <f aca="false">ROUND($C$78*E54,0)</f>
         <v>230</v>
       </c>
-      <c r="M54" s="23" t="s">
+      <c r="M54" s="20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="19" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="22" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
@@ -4965,677 +4941,677 @@
         <v>11</v>
       </c>
       <c r="F58" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H58" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="26" t="n">
+    </row>
+    <row r="59" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B59" s="26" t="n">
+      <c r="B59" s="23" t="n">
         <f aca="false">$C$7+(A59-1)*$F$7</f>
         <v>100</v>
       </c>
-      <c r="C59" s="26" t="n">
+      <c r="C59" s="23" t="n">
         <f aca="false">$D$7+(A59-1)*$G$7</f>
         <v>13</v>
       </c>
-      <c r="D59" s="26" t="n">
+      <c r="D59" s="23" t="n">
         <f aca="false">$E$7+(A59-1)*$H$7</f>
         <v>5</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="26" t="n">
         <f aca="false">1-100/(100+D59)</f>
         <v>0.0476190476190477</v>
       </c>
-      <c r="F59" s="26" t="n">
+      <c r="F59" s="23" t="n">
         <f aca="false">IF(A59&lt;$M$7,50*A59,"MAX")</f>
         <v>50</v>
       </c>
-      <c r="G59" s="26" t="n">
+      <c r="G59" s="23" t="n">
         <f aca="false">25*A59*(A59-1)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="23" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="26" t="n">
+      <c r="H59" s="20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B60" s="26" t="n">
+      <c r="B60" s="23" t="n">
         <f aca="false">$C$7+(A60-1)*$F$7</f>
         <v>108</v>
       </c>
-      <c r="C60" s="26" t="n">
+      <c r="C60" s="23" t="n">
         <f aca="false">$D$7+(A60-1)*$G$7</f>
         <v>15</v>
       </c>
-      <c r="D60" s="26" t="n">
+      <c r="D60" s="23" t="n">
         <f aca="false">$E$7+(A60-1)*$H$7</f>
         <v>6</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="26" t="n">
         <f aca="false">1-100/(100+D60)</f>
         <v>0.0566037735849057</v>
       </c>
-      <c r="F60" s="26" t="n">
+      <c r="F60" s="23" t="n">
         <f aca="false">IF(A60&lt;$M$7,50*A60,"MAX")</f>
         <v>100</v>
       </c>
-      <c r="G60" s="26" t="n">
+      <c r="G60" s="23" t="n">
         <f aca="false">25*A60*(A60-1)</f>
         <v>50</v>
       </c>
-      <c r="H60" s="23" t="str">
+      <c r="H60" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A60,$D$48:$D$54,0)),"")</f>
         <v>Chain Lightning</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="26" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B61" s="26" t="n">
+      <c r="B61" s="23" t="n">
         <f aca="false">$C$7+(A61-1)*$F$7</f>
         <v>116</v>
       </c>
-      <c r="C61" s="26" t="n">
+      <c r="C61" s="23" t="n">
         <f aca="false">$D$7+(A61-1)*$G$7</f>
         <v>17</v>
       </c>
-      <c r="D61" s="26" t="n">
+      <c r="D61" s="23" t="n">
         <f aca="false">$E$7+(A61-1)*$H$7</f>
         <v>7</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="26" t="n">
         <f aca="false">1-100/(100+D61)</f>
         <v>0.0654205607476636</v>
       </c>
-      <c r="F61" s="26" t="n">
+      <c r="F61" s="23" t="n">
         <f aca="false">IF(A61&lt;$M$7,50*A61,"MAX")</f>
         <v>150</v>
       </c>
-      <c r="G61" s="26" t="n">
+      <c r="G61" s="23" t="n">
         <f aca="false">25*A61*(A61-1)</f>
         <v>150</v>
       </c>
-      <c r="H61" s="23" t="str">
+      <c r="H61" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A61,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="26" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B62" s="26" t="n">
+      <c r="B62" s="23" t="n">
         <f aca="false">$C$7+(A62-1)*$F$7</f>
         <v>124</v>
       </c>
-      <c r="C62" s="26" t="n">
+      <c r="C62" s="23" t="n">
         <f aca="false">$D$7+(A62-1)*$G$7</f>
         <v>19</v>
       </c>
-      <c r="D62" s="26" t="n">
+      <c r="D62" s="23" t="n">
         <f aca="false">$E$7+(A62-1)*$H$7</f>
         <v>8</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="26" t="n">
         <f aca="false">1-100/(100+D62)</f>
         <v>0.0740740740740741</v>
       </c>
-      <c r="F62" s="26" t="n">
+      <c r="F62" s="23" t="n">
         <f aca="false">IF(A62&lt;$M$7,50*A62,"MAX")</f>
         <v>200</v>
       </c>
-      <c r="G62" s="26" t="n">
+      <c r="G62" s="23" t="n">
         <f aca="false">25*A62*(A62-1)</f>
         <v>300</v>
       </c>
-      <c r="H62" s="23" t="str">
+      <c r="H62" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A62,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="26" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B63" s="26" t="n">
+      <c r="B63" s="23" t="n">
         <f aca="false">$C$7+(A63-1)*$F$7</f>
         <v>132</v>
       </c>
-      <c r="C63" s="26" t="n">
+      <c r="C63" s="23" t="n">
         <f aca="false">$D$7+(A63-1)*$G$7</f>
         <v>21</v>
       </c>
-      <c r="D63" s="26" t="n">
+      <c r="D63" s="23" t="n">
         <f aca="false">$E$7+(A63-1)*$H$7</f>
         <v>9</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="26" t="n">
         <f aca="false">1-100/(100+D63)</f>
         <v>0.0825688073394495</v>
       </c>
-      <c r="F63" s="26" t="n">
+      <c r="F63" s="23" t="n">
         <f aca="false">IF(A63&lt;$M$7,50*A63,"MAX")</f>
         <v>250</v>
       </c>
-      <c r="G63" s="26" t="n">
+      <c r="G63" s="23" t="n">
         <f aca="false">25*A63*(A63-1)</f>
         <v>500</v>
       </c>
-      <c r="H63" s="23" t="str">
+      <c r="H63" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A63,$D$48:$D$54,0)),"")</f>
         <v>Frost Ward</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="26" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="26" t="n">
+      <c r="B64" s="23" t="n">
         <f aca="false">$C$7+(A64-1)*$F$7</f>
         <v>140</v>
       </c>
-      <c r="C64" s="26" t="n">
+      <c r="C64" s="23" t="n">
         <f aca="false">$D$7+(A64-1)*$G$7</f>
         <v>23</v>
       </c>
-      <c r="D64" s="26" t="n">
+      <c r="D64" s="23" t="n">
         <f aca="false">$E$7+(A64-1)*$H$7</f>
         <v>10</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="26" t="n">
         <f aca="false">1-100/(100+D64)</f>
         <v>0.0909090909090909</v>
       </c>
-      <c r="F64" s="26" t="n">
+      <c r="F64" s="23" t="n">
         <f aca="false">IF(A64&lt;$M$7,50*A64,"MAX")</f>
         <v>300</v>
       </c>
-      <c r="G64" s="26" t="n">
+      <c r="G64" s="23" t="n">
         <f aca="false">25*A64*(A64-1)</f>
         <v>750</v>
       </c>
-      <c r="H64" s="23" t="str">
+      <c r="H64" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A64,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="26" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B65" s="26" t="n">
+      <c r="B65" s="23" t="n">
         <f aca="false">$C$7+(A65-1)*$F$7</f>
         <v>148</v>
       </c>
-      <c r="C65" s="26" t="n">
+      <c r="C65" s="23" t="n">
         <f aca="false">$D$7+(A65-1)*$G$7</f>
         <v>25</v>
       </c>
-      <c r="D65" s="26" t="n">
+      <c r="D65" s="23" t="n">
         <f aca="false">$E$7+(A65-1)*$H$7</f>
         <v>11</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="26" t="n">
         <f aca="false">1-100/(100+D65)</f>
         <v>0.0990990990990991</v>
       </c>
-      <c r="F65" s="26" t="n">
+      <c r="F65" s="23" t="n">
         <f aca="false">IF(A65&lt;$M$7,50*A65,"MAX")</f>
         <v>350</v>
       </c>
-      <c r="G65" s="26" t="n">
+      <c r="G65" s="23" t="n">
         <f aca="false">25*A65*(A65-1)</f>
         <v>1050</v>
       </c>
-      <c r="H65" s="23" t="str">
+      <c r="H65" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A65,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="26" t="n">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="26" t="n">
+      <c r="B66" s="23" t="n">
         <f aca="false">$C$7+(A66-1)*$F$7</f>
         <v>156</v>
       </c>
-      <c r="C66" s="26" t="n">
+      <c r="C66" s="23" t="n">
         <f aca="false">$D$7+(A66-1)*$G$7</f>
         <v>27</v>
       </c>
-      <c r="D66" s="26" t="n">
+      <c r="D66" s="23" t="n">
         <f aca="false">$E$7+(A66-1)*$H$7</f>
         <v>12</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="26" t="n">
         <f aca="false">1-100/(100+D66)</f>
         <v>0.107142857142857</v>
       </c>
-      <c r="F66" s="26" t="n">
+      <c r="F66" s="23" t="n">
         <f aca="false">IF(A66&lt;$M$7,50*A66,"MAX")</f>
         <v>400</v>
       </c>
-      <c r="G66" s="26" t="n">
+      <c r="G66" s="23" t="n">
         <f aca="false">25*A66*(A66-1)</f>
         <v>1400</v>
       </c>
-      <c r="H66" s="23" t="str">
+      <c r="H66" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A66,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="26" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B67" s="26" t="n">
+      <c r="B67" s="23" t="n">
         <f aca="false">$C$7+(A67-1)*$F$7</f>
         <v>164</v>
       </c>
-      <c r="C67" s="26" t="n">
+      <c r="C67" s="23" t="n">
         <f aca="false">$D$7+(A67-1)*$G$7</f>
         <v>29</v>
       </c>
-      <c r="D67" s="26" t="n">
+      <c r="D67" s="23" t="n">
         <f aca="false">$E$7+(A67-1)*$H$7</f>
         <v>13</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="26" t="n">
         <f aca="false">1-100/(100+D67)</f>
         <v>0.115044247787611</v>
       </c>
-      <c r="F67" s="26" t="n">
+      <c r="F67" s="23" t="n">
         <f aca="false">IF(A67&lt;$M$7,50*A67,"MAX")</f>
         <v>450</v>
       </c>
-      <c r="G67" s="26" t="n">
+      <c r="G67" s="23" t="n">
         <f aca="false">25*A67*(A67-1)</f>
         <v>1800</v>
       </c>
-      <c r="H67" s="23" t="str">
+      <c r="H67" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A67,$D$48:$D$54,0)),"")</f>
         <v>Wind Step</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="26" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B68" s="26" t="n">
+      <c r="B68" s="23" t="n">
         <f aca="false">$C$7+(A68-1)*$F$7</f>
         <v>172</v>
       </c>
-      <c r="C68" s="26" t="n">
+      <c r="C68" s="23" t="n">
         <f aca="false">$D$7+(A68-1)*$G$7</f>
         <v>31</v>
       </c>
-      <c r="D68" s="26" t="n">
+      <c r="D68" s="23" t="n">
         <f aca="false">$E$7+(A68-1)*$H$7</f>
         <v>14</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="26" t="n">
         <f aca="false">1-100/(100+D68)</f>
         <v>0.12280701754386</v>
       </c>
-      <c r="F68" s="26" t="n">
+      <c r="F68" s="23" t="n">
         <f aca="false">IF(A68&lt;$M$7,50*A68,"MAX")</f>
         <v>500</v>
       </c>
-      <c r="G68" s="26" t="n">
+      <c r="G68" s="23" t="n">
         <f aca="false">25*A68*(A68-1)</f>
         <v>2250</v>
       </c>
-      <c r="H68" s="23" t="str">
+      <c r="H68" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A68,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B69" s="26" t="n">
+      <c r="B69" s="23" t="n">
         <f aca="false">$C$7+(A69-1)*$F$7</f>
         <v>180</v>
       </c>
-      <c r="C69" s="26" t="n">
+      <c r="C69" s="23" t="n">
         <f aca="false">$D$7+(A69-1)*$G$7</f>
         <v>33</v>
       </c>
-      <c r="D69" s="26" t="n">
+      <c r="D69" s="23" t="n">
         <f aca="false">$E$7+(A69-1)*$H$7</f>
         <v>15</v>
       </c>
-      <c r="E69" s="29" t="n">
+      <c r="E69" s="26" t="n">
         <f aca="false">1-100/(100+D69)</f>
         <v>0.130434782608696</v>
       </c>
-      <c r="F69" s="26" t="n">
+      <c r="F69" s="23" t="n">
         <f aca="false">IF(A69&lt;$M$7,50*A69,"MAX")</f>
         <v>550</v>
       </c>
-      <c r="G69" s="26" t="n">
+      <c r="G69" s="23" t="n">
         <f aca="false">25*A69*(A69-1)</f>
         <v>2750</v>
       </c>
-      <c r="H69" s="23" t="str">
+      <c r="H69" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A69,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="26" t="n">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B70" s="26" t="n">
+      <c r="B70" s="23" t="n">
         <f aca="false">$C$7+(A70-1)*$F$7</f>
         <v>188</v>
       </c>
-      <c r="C70" s="26" t="n">
+      <c r="C70" s="23" t="n">
         <f aca="false">$D$7+(A70-1)*$G$7</f>
         <v>35</v>
       </c>
-      <c r="D70" s="26" t="n">
+      <c r="D70" s="23" t="n">
         <f aca="false">$E$7+(A70-1)*$H$7</f>
         <v>16</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="26" t="n">
         <f aca="false">1-100/(100+D70)</f>
         <v>0.137931034482759</v>
       </c>
-      <c r="F70" s="26" t="n">
+      <c r="F70" s="23" t="n">
         <f aca="false">IF(A70&lt;$M$7,50*A70,"MAX")</f>
         <v>600</v>
       </c>
-      <c r="G70" s="26" t="n">
+      <c r="G70" s="23" t="n">
         <f aca="false">25*A70*(A70-1)</f>
         <v>3300</v>
       </c>
-      <c r="H70" s="23" t="str">
+      <c r="H70" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A70,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="26" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B71" s="26" t="n">
+      <c r="B71" s="23" t="n">
         <f aca="false">$C$7+(A71-1)*$F$7</f>
         <v>196</v>
       </c>
-      <c r="C71" s="26" t="n">
+      <c r="C71" s="23" t="n">
         <f aca="false">$D$7+(A71-1)*$G$7</f>
         <v>37</v>
       </c>
-      <c r="D71" s="26" t="n">
+      <c r="D71" s="23" t="n">
         <f aca="false">$E$7+(A71-1)*$H$7</f>
         <v>17</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="26" t="n">
         <f aca="false">1-100/(100+D71)</f>
         <v>0.145299145299145</v>
       </c>
-      <c r="F71" s="26" t="n">
+      <c r="F71" s="23" t="n">
         <f aca="false">IF(A71&lt;$M$7,50*A71,"MAX")</f>
         <v>650</v>
       </c>
-      <c r="G71" s="26" t="n">
+      <c r="G71" s="23" t="n">
         <f aca="false">25*A71*(A71-1)</f>
         <v>3900</v>
       </c>
-      <c r="H71" s="23" t="str">
+      <c r="H71" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A71,$D$48:$D$54,0)),"")</f>
         <v>Steam Burst</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="26" t="n">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B72" s="26" t="n">
+      <c r="B72" s="23" t="n">
         <f aca="false">$C$7+(A72-1)*$F$7</f>
         <v>204</v>
       </c>
-      <c r="C72" s="26" t="n">
+      <c r="C72" s="23" t="n">
         <f aca="false">$D$7+(A72-1)*$G$7</f>
         <v>39</v>
       </c>
-      <c r="D72" s="26" t="n">
+      <c r="D72" s="23" t="n">
         <f aca="false">$E$7+(A72-1)*$H$7</f>
         <v>18</v>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="26" t="n">
         <f aca="false">1-100/(100+D72)</f>
         <v>0.152542372881356</v>
       </c>
-      <c r="F72" s="26" t="n">
+      <c r="F72" s="23" t="n">
         <f aca="false">IF(A72&lt;$M$7,50*A72,"MAX")</f>
         <v>700</v>
       </c>
-      <c r="G72" s="26" t="n">
+      <c r="G72" s="23" t="n">
         <f aca="false">25*A72*(A72-1)</f>
         <v>4550</v>
       </c>
-      <c r="H72" s="23" t="str">
+      <c r="H72" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A72,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="26" t="n">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B73" s="26" t="n">
+      <c r="B73" s="23" t="n">
         <f aca="false">$C$7+(A73-1)*$F$7</f>
         <v>212</v>
       </c>
-      <c r="C73" s="26" t="n">
+      <c r="C73" s="23" t="n">
         <f aca="false">$D$7+(A73-1)*$G$7</f>
         <v>41</v>
       </c>
-      <c r="D73" s="26" t="n">
+      <c r="D73" s="23" t="n">
         <f aca="false">$E$7+(A73-1)*$H$7</f>
         <v>19</v>
       </c>
-      <c r="E73" s="29" t="n">
+      <c r="E73" s="26" t="n">
         <f aca="false">1-100/(100+D73)</f>
         <v>0.159663865546218</v>
       </c>
-      <c r="F73" s="26" t="n">
+      <c r="F73" s="23" t="n">
         <f aca="false">IF(A73&lt;$M$7,50*A73,"MAX")</f>
         <v>750</v>
       </c>
-      <c r="G73" s="26" t="n">
+      <c r="G73" s="23" t="n">
         <f aca="false">25*A73*(A73-1)</f>
         <v>5250</v>
       </c>
-      <c r="H73" s="23" t="str">
+      <c r="H73" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A73,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="26" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B74" s="26" t="n">
+      <c r="B74" s="23" t="n">
         <f aca="false">$C$7+(A74-1)*$F$7</f>
         <v>220</v>
       </c>
-      <c r="C74" s="26" t="n">
+      <c r="C74" s="23" t="n">
         <f aca="false">$D$7+(A74-1)*$G$7</f>
         <v>43</v>
       </c>
-      <c r="D74" s="26" t="n">
+      <c r="D74" s="23" t="n">
         <f aca="false">$E$7+(A74-1)*$H$7</f>
         <v>20</v>
       </c>
-      <c r="E74" s="29" t="n">
+      <c r="E74" s="26" t="n">
         <f aca="false">1-100/(100+D74)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="F74" s="26" t="n">
+      <c r="F74" s="23" t="n">
         <f aca="false">IF(A74&lt;$M$7,50*A74,"MAX")</f>
         <v>800</v>
       </c>
-      <c r="G74" s="26" t="n">
+      <c r="G74" s="23" t="n">
         <f aca="false">25*A74*(A74-1)</f>
         <v>6000</v>
       </c>
-      <c r="H74" s="23" t="str">
+      <c r="H74" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A74,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="26" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B75" s="26" t="n">
+      <c r="B75" s="23" t="n">
         <f aca="false">$C$7+(A75-1)*$F$7</f>
         <v>228</v>
       </c>
-      <c r="C75" s="26" t="n">
+      <c r="C75" s="23" t="n">
         <f aca="false">$D$7+(A75-1)*$G$7</f>
         <v>45</v>
       </c>
-      <c r="D75" s="26" t="n">
+      <c r="D75" s="23" t="n">
         <f aca="false">$E$7+(A75-1)*$H$7</f>
         <v>21</v>
       </c>
-      <c r="E75" s="29" t="n">
+      <c r="E75" s="26" t="n">
         <f aca="false">1-100/(100+D75)</f>
         <v>0.173553719008264</v>
       </c>
-      <c r="F75" s="26" t="n">
+      <c r="F75" s="23" t="n">
         <f aca="false">IF(A75&lt;$M$7,50*A75,"MAX")</f>
         <v>850</v>
       </c>
-      <c r="G75" s="26" t="n">
+      <c r="G75" s="23" t="n">
         <f aca="false">25*A75*(A75-1)</f>
         <v>6800</v>
       </c>
-      <c r="H75" s="23" t="str">
+      <c r="H75" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A75,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="26" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B76" s="26" t="n">
+      <c r="B76" s="23" t="n">
         <f aca="false">$C$7+(A76-1)*$F$7</f>
         <v>236</v>
       </c>
-      <c r="C76" s="26" t="n">
+      <c r="C76" s="23" t="n">
         <f aca="false">$D$7+(A76-1)*$G$7</f>
         <v>47</v>
       </c>
-      <c r="D76" s="26" t="n">
+      <c r="D76" s="23" t="n">
         <f aca="false">$E$7+(A76-1)*$H$7</f>
         <v>22</v>
       </c>
-      <c r="E76" s="29" t="n">
+      <c r="E76" s="26" t="n">
         <f aca="false">1-100/(100+D76)</f>
         <v>0.180327868852459</v>
       </c>
-      <c r="F76" s="26" t="n">
+      <c r="F76" s="23" t="n">
         <f aca="false">IF(A76&lt;$M$7,50*A76,"MAX")</f>
         <v>900</v>
       </c>
-      <c r="G76" s="26" t="n">
+      <c r="G76" s="23" t="n">
         <f aca="false">25*A76*(A76-1)</f>
         <v>7650</v>
       </c>
-      <c r="H76" s="23" t="str">
+      <c r="H76" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A76,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="26" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B77" s="26" t="n">
+      <c r="B77" s="23" t="n">
         <f aca="false">$C$7+(A77-1)*$F$7</f>
         <v>244</v>
       </c>
-      <c r="C77" s="26" t="n">
+      <c r="C77" s="23" t="n">
         <f aca="false">$D$7+(A77-1)*$G$7</f>
         <v>49</v>
       </c>
-      <c r="D77" s="26" t="n">
+      <c r="D77" s="23" t="n">
         <f aca="false">$E$7+(A77-1)*$H$7</f>
         <v>23</v>
       </c>
-      <c r="E77" s="29" t="n">
+      <c r="E77" s="26" t="n">
         <f aca="false">1-100/(100+D77)</f>
         <v>0.186991869918699</v>
       </c>
-      <c r="F77" s="26" t="n">
+      <c r="F77" s="23" t="n">
         <f aca="false">IF(A77&lt;$M$7,50*A77,"MAX")</f>
         <v>950</v>
       </c>
-      <c r="G77" s="26" t="n">
+      <c r="G77" s="23" t="n">
         <f aca="false">25*A77*(A77-1)</f>
         <v>8550</v>
       </c>
-      <c r="H77" s="23" t="str">
+      <c r="H77" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A77,$D$48:$D$54,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="26" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B78" s="26" t="n">
+      <c r="B78" s="23" t="n">
         <f aca="false">$C$7+(A78-1)*$F$7</f>
         <v>252</v>
       </c>
-      <c r="C78" s="26" t="n">
+      <c r="C78" s="23" t="n">
         <f aca="false">$D$7+(A78-1)*$G$7</f>
         <v>51</v>
       </c>
-      <c r="D78" s="26" t="n">
+      <c r="D78" s="23" t="n">
         <f aca="false">$E$7+(A78-1)*$H$7</f>
         <v>24</v>
       </c>
-      <c r="E78" s="29" t="n">
+      <c r="E78" s="26" t="n">
         <f aca="false">1-100/(100+D78)</f>
         <v>0.193548387096774</v>
       </c>
-      <c r="F78" s="26" t="str">
+      <c r="F78" s="23" t="str">
         <f aca="false">IF(A78&lt;$M$7,50*A78,"MAX")</f>
         <v>MAX</v>
       </c>
-      <c r="G78" s="26" t="n">
+      <c r="G78" s="23" t="n">
         <f aca="false">25*A78*(A78-1)</f>
         <v>9500</v>
       </c>
-      <c r="H78" s="23" t="str">
+      <c r="H78" s="20" t="str">
         <f aca="false">IFERROR(INDEX($A$48:$A$54,MATCH(A78,$D$48:$D$54,0)),"")</f>
         <v>Meteor</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="21" t="s">
-        <v>152</v>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5674,250 +5650,250 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="M5" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="30" t="s">
+      <c r="D6" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="E6" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="F6" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="G6" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="H6" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="H6" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="30" t="s">
+      <c r="J6" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="K6" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="L6" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="M6" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="M6" s="30" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="30" t="s">
+      <c r="D7" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="E7" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="F7" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="G7" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="H7" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="I7" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="J7" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="K7" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="L7" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="K7" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="L7" s="30" t="s">
+      <c r="M7" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="M7" s="30" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="D8" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="E8" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="F8" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="G8" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="H8" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="I8" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="J8" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="K8" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="L8" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="L8" s="30" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="B9" s="27" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
+      <c r="C9" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="30" t="s">
+      <c r="F9" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="H9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="I9" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="H9" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="J9" s="30" t="s">
+      <c r="M9" s="27" t="s">
         <v>203</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>210</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -5927,524 +5903,524 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="F13" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="G13" s="30" t="s">
+      <c r="E17" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="D14" s="30" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="D15" s="30" t="s">
+      <c r="E18" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="D19" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="30" t="s">
+      <c r="E19" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="n">
+      <c r="E20" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B21" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30" t="n">
+      <c r="C21" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="28" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B22" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G19" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="D20" s="30" t="s">
+      <c r="C22" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="F20" s="30" t="s">
+      <c r="E22" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="F22" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G22" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="D21" s="30" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="31" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="F22" s="30" t="s">
+      <c r="E28" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="F28" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="F25" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="F26" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="30" t="s">
+      <c r="G28" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="F28" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="32" t="s">
-        <v>235</v>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="31" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="31" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="31" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="34" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="31" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="31" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="31" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="31" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="34" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="31" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -6455,12 +6431,12 @@
       <c r="L41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30" t="s">
+      <c r="A42" s="27"/>
+      <c r="B42" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="30" t="s">
-        <v>269</v>
+      <c r="C42" s="27" t="s">
+        <v>268</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>5</v>
@@ -6470,12 +6446,12 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30" t="s">
+      <c r="A43" s="27"/>
+      <c r="B43" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="30" t="s">
-        <v>269</v>
+      <c r="C43" s="27" t="s">
+        <v>268</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>8</v>
@@ -6485,12 +6461,12 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30" t="s">
+      <c r="A44" s="27"/>
+      <c r="B44" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="30" t="s">
-        <v>269</v>
+      <c r="C44" s="27" t="s">
+        <v>268</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>12</v>
@@ -6500,12 +6476,12 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="C45" s="30" t="s">
+      <c r="A45" s="27"/>
+      <c r="B45" s="27" t="s">
         <v>269</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>268</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>30</v>
@@ -6515,12 +6491,12 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30" t="s">
+      <c r="A46" s="27"/>
+      <c r="B46" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="30" t="s">
-        <v>271</v>
+      <c r="C46" s="27" t="s">
+        <v>270</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>6</v>
@@ -6530,12 +6506,12 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30" t="s">
+      <c r="A47" s="27"/>
+      <c r="B47" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="30" t="s">
-        <v>271</v>
+      <c r="C47" s="27" t="s">
+        <v>270</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>16</v>
@@ -6545,12 +6521,12 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30" t="s">
+      <c r="A48" s="27"/>
+      <c r="B48" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="30" t="s">
-        <v>271</v>
+      <c r="C48" s="27" t="s">
+        <v>270</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>14</v>
@@ -6560,12 +6536,12 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="C49" s="30" t="s">
+      <c r="A49" s="27"/>
+      <c r="B49" s="27" t="s">
         <v>271</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>270</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>45</v>
@@ -6576,59 +6552,59 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="D50" s="35" t="n">
+        <v>272</v>
+      </c>
+      <c r="D50" s="32" t="n">
         <f aca="false">2*D42+3*D43+D44+D45</f>
         <v>76</v>
       </c>
-      <c r="E50" s="35" t="n">
+      <c r="E50" s="32" t="n">
         <f aca="false">2*E42+3*E43+E44+E45</f>
         <v>67</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="D51" s="35" t="n">
+        <v>273</v>
+      </c>
+      <c r="D51" s="32" t="n">
         <f aca="false">2*D42+3*D43+D44</f>
         <v>46</v>
       </c>
-      <c r="E51" s="35" t="n">
+      <c r="E51" s="32" t="n">
         <f aca="false">2*E42+3*E43+E44</f>
         <v>17</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="D52" s="35" t="n">
+        <v>274</v>
+      </c>
+      <c r="D52" s="32" t="n">
         <f aca="false">5*D46+D47+2*D48+D49</f>
         <v>119</v>
       </c>
-      <c r="E52" s="35" t="n">
+      <c r="E52" s="32" t="n">
         <f aca="false">5*E46+E47+2*E48+E49</f>
         <v>121</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="D53" s="35" t="n">
+        <v>275</v>
+      </c>
+      <c r="D53" s="32" t="n">
         <f aca="false">5*D46+D47+2*D48</f>
         <v>74</v>
       </c>
-      <c r="E53" s="35" t="n">
+      <c r="E53" s="32" t="n">
         <f aca="false">5*E46+E47+2*E48</f>
         <v>26</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -6666,578 +6642,526 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
+      <c r="B4" s="33" t="s">
         <v>280</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="D4" s="33" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="E4" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="F4" s="33" t="s">
         <v>284</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="G4" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="36" t="s">
+      <c r="C5" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="H12" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="H17" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="34" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="30" t="s">
+      <c r="B21" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="D21" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="C5" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E5" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F5" s="37" t="s">
+      <c r="E21" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="F21" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="H5" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F6" s="37" t="s">
+      <c r="G21" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F22" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="H7" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>298</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>300</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="E15" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F15" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="H16" s="40" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>320</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="G19" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E22" s="37" t="s">
+      <c r="G22" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="F22" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>340</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="H24" s="39" t="s">
-        <v>196</v>
+      <c r="H22" s="36" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H24"/>
-  <conditionalFormatting sqref="H5:H24">
+  <autoFilter ref="A4:H22"/>
+  <conditionalFormatting sqref="H5:H22">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Done"</formula>
     </cfRule>
@@ -7252,7 +7176,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H24" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H22" type="list">
       <formula1>"Done,In progress,Not started,Undecided"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7286,139 +7210,139 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="41" t="n">
+      <c r="B5" s="38" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C5" s="39" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="B6" s="41" t="n">
+        <v>347</v>
+      </c>
+      <c r="B6" s="38" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B7" s="41" t="n">
+        <v>349</v>
+      </c>
+      <c r="B7" s="38" t="n">
         <v>0.2</v>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="39" t="n">
         <v>1.5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>350</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="B8" s="41" t="n">
+        <v>351</v>
+      </c>
+      <c r="B8" s="38" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="B11" s="43" t="n">
+        <v>357</v>
+      </c>
+      <c r="B11" s="40" t="n">
         <f aca="false">SUM(B5:B8)</f>
         <v>1</v>
       </c>
@@ -7454,12 +7378,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7467,31 +7391,31 @@
         <v>30</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7501,20 +7425,20 @@
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="41" t="n">
+      <c r="C5" s="38" t="n">
         <v>0.25</v>
       </c>
-      <c r="D5" s="42" t="n">
+      <c r="D5" s="39" t="n">
         <v>1.25</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="41" t="n">
         <f aca="false">D5*E5</f>
         <v>2.5</v>
       </c>
-      <c r="G5" s="45" t="n">
+      <c r="G5" s="42" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A5,Monsters!$A$5:$A$17,0))</f>
         <v>12</v>
       </c>
@@ -7527,7 +7451,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7535,22 +7459,22 @@
         <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C6" s="41" t="n">
+        <v>366</v>
+      </c>
+      <c r="C6" s="38" t="n">
         <v>0.2</v>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D6" s="39" t="n">
         <v>2.25</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="41" t="n">
         <f aca="false">D6*E6</f>
         <v>2.25</v>
       </c>
-      <c r="G6" s="45" t="n">
+      <c r="G6" s="42" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A6,Monsters!$A$5:$A$17,0))</f>
         <v>10</v>
       </c>
@@ -7563,7 +7487,7 @@
         <v>34</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7571,22 +7495,22 @@
         <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C7" s="41" t="n">
+        <v>368</v>
+      </c>
+      <c r="C7" s="38" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="42" t="n">
+      <c r="D7" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="41" t="n">
         <f aca="false">D7*E7</f>
         <v>1.6</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="42" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A7,Monsters!$A$5:$A$17,0))</f>
         <v>10</v>
       </c>
@@ -7599,7 +7523,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7609,20 +7533,20 @@
       <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="38" t="n">
         <v>0.2</v>
       </c>
-      <c r="D8" s="42" t="n">
+      <c r="D8" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="41" t="n">
         <f aca="false">D8*E8</f>
         <v>2.5</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="42" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A8,Monsters!$A$5:$A$17,0))</f>
         <v>34</v>
       </c>
@@ -7635,7 +7559,7 @@
         <v>119</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7643,22 +7567,22 @@
         <v>47</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="C9" s="41" t="n">
+        <v>371</v>
+      </c>
+      <c r="C9" s="38" t="n">
         <v>0.15</v>
       </c>
-      <c r="D9" s="42" t="n">
+      <c r="D9" s="39" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="41" t="n">
         <f aca="false">D9*E9</f>
         <v>3</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="42" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A9,Monsters!$A$5:$A$17,0))</f>
         <v>42</v>
       </c>
@@ -7671,7 +7595,7 @@
         <v>189</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7679,22 +7603,22 @@
         <v>47</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C10" s="41" t="n">
+        <v>373</v>
+      </c>
+      <c r="C10" s="38" t="n">
         <v>0.15</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="39" t="n">
         <v>0.9</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="41" t="n">
         <f aca="false">D10*E10</f>
         <v>1.8</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A10,Monsters!$A$5:$A$17,0))</f>
         <v>42</v>
       </c>
@@ -7707,7 +7631,7 @@
         <v>113</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7715,22 +7639,22 @@
         <v>47</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C11" s="41" t="n">
+        <v>374</v>
+      </c>
+      <c r="C11" s="38" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="42" t="n">
+      <c r="D11" s="39" t="n">
         <v>1.4</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="41" t="n">
         <f aca="false">D11*E11</f>
         <v>1.4</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="42" t="n">
         <f aca="false">INDEX(Monsters!$F$5:$F$17,MATCH(A11,Monsters!$A$5:$A$17,0))</f>
         <v>42</v>
       </c>
@@ -7743,12 +7667,12 @@
         <v>88</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -7780,12 +7704,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7796,30 +7720,30 @@
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="46" t="str">
+      <c r="A5" s="43" t="str">
         <f aca="false">Monsters!A5</f>
         <v>Mutated Tadpole</v>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="42" t="n">
         <f aca="false">Monsters!F5</f>
         <v>4</v>
       </c>
@@ -7849,11 +7773,11 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="str">
+      <c r="A6" s="43" t="str">
         <f aca="false">Monsters!A6</f>
         <v>Mutated Frog</v>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="42" t="n">
         <f aca="false">Monsters!F6</f>
         <v>4</v>
       </c>
@@ -7883,11 +7807,11 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="str">
+      <c r="A7" s="43" t="str">
         <f aca="false">Monsters!A7</f>
         <v>Mutated Boar</v>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="42" t="n">
         <f aca="false">Monsters!F7</f>
         <v>12</v>
       </c>
@@ -7917,11 +7841,11 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="str">
+      <c r="A8" s="44" t="str">
         <f aca="false">Monsters!A8</f>
         <v>Mutated Cheetah</v>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="45" t="n">
         <f aca="false">Monsters!F8</f>
         <v>12</v>
       </c>
@@ -7951,11 +7875,11 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="str">
+      <c r="A9" s="43" t="str">
         <f aca="false">Monsters!A9</f>
         <v>Security Drone</v>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="42" t="n">
         <f aca="false">Monsters!F9</f>
         <v>5</v>
       </c>
@@ -7985,11 +7909,11 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="46" t="str">
+      <c r="A10" s="43" t="str">
         <f aca="false">Monsters!A10</f>
         <v>Maintenance Bot</v>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="42" t="n">
         <f aca="false">Monsters!F10</f>
         <v>8</v>
       </c>
@@ -8019,11 +7943,11 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="46" t="str">
+      <c r="A11" s="43" t="str">
         <f aca="false">Monsters!A11</f>
         <v>Sentry Turret</v>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="42" t="n">
         <f aca="false">Monsters!F11</f>
         <v>9</v>
       </c>
@@ -8053,11 +7977,11 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="47" t="str">
+      <c r="A12" s="44" t="str">
         <f aca="false">Monsters!A12</f>
         <v>Rogue Overseer</v>
       </c>
-      <c r="B12" s="48" t="n">
+      <c r="B12" s="45" t="n">
         <f aca="false">Monsters!F12</f>
         <v>10</v>
       </c>
@@ -8087,11 +8011,11 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="str">
+      <c r="A13" s="43" t="str">
         <f aca="false">Monsters!A13</f>
         <v>Rift Wisp</v>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="42" t="n">
         <f aca="false">Monsters!F13</f>
         <v>18</v>
       </c>
@@ -8121,11 +8045,11 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="46" t="str">
+      <c r="A14" s="43" t="str">
         <f aca="false">Monsters!A14</f>
         <v>Rift Knight</v>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="42" t="n">
         <f aca="false">Monsters!F14</f>
         <v>32</v>
       </c>
@@ -8155,11 +8079,11 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46" t="str">
+      <c r="A15" s="43" t="str">
         <f aca="false">Monsters!A15</f>
         <v>Rift Stalker</v>
       </c>
-      <c r="B15" s="45" t="n">
+      <c r="B15" s="42" t="n">
         <f aca="false">Monsters!F15</f>
         <v>35</v>
       </c>
@@ -8189,11 +8113,11 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="47" t="str">
+      <c r="A16" s="44" t="str">
         <f aca="false">Monsters!A16</f>
         <v>Rift Warden</v>
       </c>
-      <c r="B16" s="48" t="n">
+      <c r="B16" s="45" t="n">
         <f aca="false">Monsters!F16</f>
         <v>34</v>
       </c>
@@ -8223,11 +8147,11 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47" t="str">
+      <c r="A17" s="44" t="str">
         <f aca="false">Monsters!A17</f>
         <v>Hollow Colossus</v>
       </c>
-      <c r="B17" s="48" t="n">
+      <c r="B17" s="45" t="n">
         <f aca="false">Monsters!F17</f>
         <v>42</v>
       </c>
@@ -8284,850 +8208,850 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="31" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="31" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="31" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="31" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="46" t="s">
         <v>391</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="47" t="s">
         <v>399</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="B13" s="48" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="C13" s="48" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D13" s="48" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E13" s="48" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="F13" s="47" t="s">
         <v>400</v>
       </c>
-      <c r="D12" s="4" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="B14" s="26" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="F14" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="F12" s="4" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
+      <c r="B15" s="26" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="B13" s="50" t="n">
-        <v>0.887</v>
-      </c>
-      <c r="C13" s="50" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="D13" s="50" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E13" s="50" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="F13" s="49" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
+      <c r="B16" s="26" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="F16" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="F14" s="23" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="B17" s="26" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="F17" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="F15" s="23" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="B18" s="26" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F18" s="20" t="s">
         <v>410</v>
       </c>
-      <c r="B16" s="29" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="C16" s="29" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="E16" s="29" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="F16" s="23" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="B17" s="29" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="B18" s="29" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>416</v>
-      </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="26" t="n">
         <v>0.877</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="26" t="n">
         <v>0.592</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="26" t="n">
         <v>0.903</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="26" t="n">
         <v>0.381</v>
       </c>
-      <c r="F19" s="23" t="s">
-        <v>415</v>
+      <c r="F19" s="20" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="47" t="s">
         <v>399</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="B24" s="48" t="n">
+        <v>0.86625</v>
+      </c>
+      <c r="C24" s="48" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="D24" s="48" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="E24" s="48" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="F24" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="50" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="51" t="s">
+        <v>417</v>
+      </c>
+      <c r="B25" s="52" t="n">
+        <v>0.91575</v>
+      </c>
+      <c r="C25" s="52" t="n">
+        <v>0.72775</v>
+      </c>
+      <c r="D25" s="52" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="E25" s="52" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F25" s="53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H25" s="54" t="n">
+        <v>0.258333333333333</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.92425</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.63175</v>
+      </c>
+      <c r="F26" s="55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="22" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="B27" s="26" t="n">
+        <v>0.87675</v>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.9285</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.62375</v>
+      </c>
+      <c r="F27" s="55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" s="22" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="B28" s="26" t="n">
+        <v>0.95275</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.9685</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="F28" s="55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G28" s="55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>0.308333333333333</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49" t="s">
-        <v>404</v>
-      </c>
-      <c r="B24" s="50" t="n">
-        <v>0.86625</v>
-      </c>
-      <c r="C24" s="50" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="D24" s="50" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="E24" s="50" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="F24" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="52" t="n">
-        <v>0.225</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="53" t="s">
+      <c r="B29" s="26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>0.815</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.9635</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.78075</v>
+      </c>
+      <c r="F29" s="55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G29" s="55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H29" s="22" t="n">
+        <v>0.304166666666667</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>422</v>
       </c>
-      <c r="B25" s="54" t="n">
-        <v>0.91575</v>
-      </c>
-      <c r="C25" s="54" t="n">
-        <v>0.72775</v>
-      </c>
-      <c r="D25" s="54" t="n">
-        <v>0.9435</v>
-      </c>
-      <c r="E25" s="54" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="F25" s="55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G25" s="55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H25" s="56" t="n">
-        <v>0.258333333333333</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="s">
+      <c r="B30" s="26" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="F30" s="55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G30" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>0.316666666666667</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="B26" s="29" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="C26" s="29" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>0.92425</v>
-      </c>
-      <c r="E26" s="29" t="n">
-        <v>0.63175</v>
-      </c>
-      <c r="F26" s="57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G26" s="57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H26" s="25" t="n">
-        <v>0.225</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
+      <c r="B31" s="26" t="n">
+        <v>0.93475</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>0.75075</v>
+      </c>
+      <c r="F31" s="55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G31" s="55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>0.266666666666667</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="B27" s="29" t="n">
-        <v>0.87675</v>
-      </c>
-      <c r="C27" s="29" t="n">
-        <v>0.6865</v>
-      </c>
-      <c r="D27" s="29" t="n">
-        <v>0.9285</v>
-      </c>
-      <c r="E27" s="29" t="n">
-        <v>0.62375</v>
-      </c>
-      <c r="F27" s="57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H27" s="25" t="n">
-        <v>0.225</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="s">
+      <c r="B32" s="26" t="n">
+        <v>0.98525</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>0.90425</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>0.99625</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="F32" s="55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G32" s="55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="B28" s="29" t="n">
-        <v>0.95275</v>
-      </c>
-      <c r="C28" s="29" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="E28" s="29" t="n">
-        <v>0.7745</v>
-      </c>
-      <c r="F28" s="57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G28" s="57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H28" s="25" t="n">
-        <v>0.308333333333333</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
+      <c r="B33" s="26" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>0.8385</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>0.98725</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="F33" s="55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G33" s="55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="31" t="s">
         <v>426</v>
       </c>
-      <c r="B29" s="29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C29" s="29" t="n">
-        <v>0.815</v>
-      </c>
-      <c r="D29" s="29" t="n">
-        <v>0.9635</v>
-      </c>
-      <c r="E29" s="29" t="n">
-        <v>0.78075</v>
-      </c>
-      <c r="F29" s="57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G29" s="57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H29" s="25" t="n">
-        <v>0.304166666666667</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="31" t="s">
         <v>427</v>
       </c>
-      <c r="B30" s="29" t="n">
-        <v>0.96875</v>
-      </c>
-      <c r="C30" s="29" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="D30" s="29" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="E30" s="29" t="n">
-        <v>0.8535</v>
-      </c>
-      <c r="F30" s="57" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G30" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="25" t="n">
-        <v>0.316666666666667</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="31" t="s">
         <v>428</v>
       </c>
-      <c r="B31" s="29" t="n">
-        <v>0.93475</v>
-      </c>
-      <c r="C31" s="29" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="D31" s="29" t="n">
-        <v>0.9675</v>
-      </c>
-      <c r="E31" s="29" t="n">
-        <v>0.75075</v>
-      </c>
-      <c r="F31" s="57" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G31" s="57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H31" s="25" t="n">
-        <v>0.266666666666667</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="31" t="s">
         <v>429</v>
-      </c>
-      <c r="B32" s="29" t="n">
-        <v>0.98525</v>
-      </c>
-      <c r="C32" s="29" t="n">
-        <v>0.90425</v>
-      </c>
-      <c r="D32" s="29" t="n">
-        <v>0.99625</v>
-      </c>
-      <c r="E32" s="29" t="n">
-        <v>0.9605</v>
-      </c>
-      <c r="F32" s="57" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G32" s="57" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H32" s="25" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="B33" s="29" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="C33" s="29" t="n">
-        <v>0.8385</v>
-      </c>
-      <c r="D33" s="29" t="n">
-        <v>0.98725</v>
-      </c>
-      <c r="E33" s="29" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="F33" s="57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G33" s="57" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H33" s="25" t="n">
-        <v>0.325</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="34" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B41" s="4" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="B42" s="48" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="C42" s="48" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="D42" s="47" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D43" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="C41" s="4" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="49" t="s">
+      <c r="B44" s="26" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="D44" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B42" s="50" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="C42" s="50" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="D42" s="49" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23" t="s">
+      <c r="B45" s="26" t="n">
+        <v>0.818</v>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="D45" s="20"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="B43" s="29" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="C43" s="29" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="D43" s="23" t="s">
+      <c r="B46" s="26" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="D46" s="20"/>
+    </row>
+    <row r="47" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23" t="s">
+      <c r="B47" s="26" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D47" s="20" t="s">
         <v>442</v>
       </c>
-      <c r="B44" s="29" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="C44" s="29" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="D44" s="23" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23" t="s">
+      <c r="B48" s="26" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D48" s="20"/>
+    </row>
+    <row r="49" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="51" t="s">
         <v>444</v>
       </c>
-      <c r="B45" s="29" t="n">
-        <v>0.818</v>
-      </c>
-      <c r="C45" s="29" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="D45" s="23"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="23" t="s">
+      <c r="B49" s="52" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="C49" s="52" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="D49" s="51" t="s">
         <v>445</v>
       </c>
-      <c r="B46" s="29" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="C46" s="29" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="D46" s="23"/>
-    </row>
-    <row r="47" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="B47" s="29" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="C47" s="29" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="D47" s="23" t="s">
+      <c r="B50" s="26" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D50" s="20" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="B48" s="29" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="C48" s="29" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D48" s="23"/>
-    </row>
-    <row r="49" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="53" t="s">
-        <v>449</v>
-      </c>
-      <c r="B49" s="54" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="C49" s="54" t="n">
-        <v>0.069</v>
-      </c>
-      <c r="D49" s="53" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="B50" s="29" t="n">
-        <v>0.958</v>
-      </c>
-      <c r="C50" s="29" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="B51" s="29" t="n">
+      <c r="B51" s="26" t="n">
         <v>0.975</v>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="26" t="n">
         <v>0.162</v>
       </c>
-      <c r="D51" s="23" t="s">
-        <v>452</v>
+      <c r="D51" s="20" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C57" s="48" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="D57" s="47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B58" s="26" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="C58" s="26" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="B59" s="26" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="D59" s="20" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="22" t="s">
+    <row r="60" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>438</v>
-      </c>
-      <c r="B57" s="50" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="C57" s="50" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="D57" s="49" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="23" t="s">
+      <c r="B60" s="26" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="B58" s="29" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="C58" s="29" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="D58" s="23" t="s">
+      <c r="B61" s="26" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="20" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="23" t="s">
+      <c r="B62" s="26" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="B59" s="29" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="C59" s="29" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="D59" s="23" t="s">
+      <c r="B63" s="26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="D63" s="20" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="23" t="s">
+    <row r="64" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="51" t="s">
         <v>460</v>
       </c>
-      <c r="B60" s="29" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="C60" s="29" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="D60" s="23" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="23" t="s">
+      <c r="B64" s="52" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C64" s="52" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="D64" s="51" t="s">
         <v>461</v>
       </c>
-      <c r="B61" s="29" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="C61" s="29" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="23" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="20" t="s">
         <v>462</v>
       </c>
-      <c r="B62" s="29" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="C62" s="29" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D62" s="23" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="23" t="s">
+      <c r="B65" s="26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C65" s="26" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="D65" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="B63" s="29" t="n">
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="B66" s="26" t="n">
         <v>0.86</v>
       </c>
-      <c r="C63" s="29" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="53" t="s">
+      <c r="C66" s="26" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="B64" s="54" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C64" s="54" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="D64" s="53" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="31" t="s">
         <v>466</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="23" t="s">
-        <v>467</v>
-      </c>
-      <c r="B65" s="29" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C65" s="29" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="23" t="s">
-        <v>469</v>
-      </c>
-      <c r="B66" s="29" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C66" s="29" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="58" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="58" t="s">
-        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -9159,702 +9083,702 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="s">
+        <v>469</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>470</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>471</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>472</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
+      <c r="G4" s="33" t="s">
         <v>474</v>
       </c>
-      <c r="B4" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="C4" s="36" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
         <v>475</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="B5" s="27" t="s">
         <v>476</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="C5" s="27" t="s">
         <v>477</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="D5" s="27" t="s">
         <v>478</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="E5" s="27" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
+      <c r="F5" s="27" t="s">
         <v>480</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="G5" s="27" t="s">
         <v>481</v>
       </c>
-      <c r="C5" s="30" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>482</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D6" s="27" t="s">
         <v>483</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E6" s="27" t="s">
         <v>484</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F6" s="27" t="s">
         <v>485</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G6" s="27" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
-        <v>480</v>
-      </c>
-      <c r="B6" s="30" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>488</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>490</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>491</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C8" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>493</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>494</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="s">
         <v>487</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="B9" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>495</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>502</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>505</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>506</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>507</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>508</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>509</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>510</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>511</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>488</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="C13" s="27" t="s">
         <v>489</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="D13" s="27" t="s">
         <v>490</v>
       </c>
-      <c r="G6" s="30" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>493</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>494</v>
-      </c>
-      <c r="D7" s="30" t="s">
+      <c r="E13" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>513</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>514</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>517</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>519</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>525</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>529</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>531</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>534</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>535</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>542</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>543</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>545</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>546</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>549</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="30" t="s">
-        <v>495</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>496</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="B8" s="30" t="s">
+      <c r="E22" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>552</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B23" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="D8" s="30" t="s">
+      <c r="C23" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>554</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>556</v>
+      </c>
+      <c r="D24" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E24" s="27" t="s">
+        <v>557</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>558</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="27" t="s">
         <v>498</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>499</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>500</v>
-      </c>
-      <c r="D9" s="30" t="s">
+      <c r="B25" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>559</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>543</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>560</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>561</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>562</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>563</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>564</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>566</v>
+      </c>
+      <c r="D27" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="30" t="s">
-        <v>501</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>502</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
+      <c r="E27" s="27" t="s">
+        <v>567</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>568</v>
+      </c>
+      <c r="G27" s="27" t="s">
         <v>503</v>
       </c>
-      <c r="B10" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>504</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>505</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>506</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>507</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>569</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>570</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>571</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>572</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>573</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>574</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>575</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>576</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="27" t="s">
+        <v>577</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>579</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>580</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>503</v>
       </c>
-      <c r="B11" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>509</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>510</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>511</v>
-      </c>
-      <c r="F11" s="30" t="s">
-        <v>512</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>514</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>515</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>516</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>493</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>494</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>495</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>517</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>518</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>519</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>520</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>521</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>522</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>523</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>525</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>526</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>527</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>528</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>529</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>530</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>531</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B17" s="30" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="27" t="s">
+        <v>577</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="G31" s="27" t="s">
         <v>481</v>
       </c>
-      <c r="C17" s="30" t="s">
-        <v>533</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>534</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>535</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>536</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>481</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>537</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>538</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>539</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>540</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>542</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>543</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>545</v>
-      </c>
-      <c r="G19" s="30" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>547</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>548</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>549</v>
-      </c>
-      <c r="F20" s="30" t="s">
-        <v>550</v>
-      </c>
-      <c r="G20" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>551</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>555</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="30" t="s">
-        <v>556</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>557</v>
-      </c>
-      <c r="G22" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>558</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>559</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>560</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>561</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>562</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>563</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>564</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>548</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="F25" s="30" t="s">
-        <v>566</v>
-      </c>
-      <c r="G25" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>567</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>568</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>569</v>
-      </c>
-      <c r="F26" s="30" t="s">
-        <v>570</v>
-      </c>
-      <c r="G26" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>571</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>572</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>573</v>
-      </c>
-      <c r="G27" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>574</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>575</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>576</v>
-      </c>
-      <c r="F28" s="30" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
         <v>577</v>
       </c>
-      <c r="G28" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>578</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>579</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>580</v>
-      </c>
-      <c r="F29" s="30" t="s">
-        <v>581</v>
-      </c>
-      <c r="G29" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30" t="s">
-        <v>582</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>583</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>584</v>
-      </c>
-      <c r="E30" s="30" t="s">
+      <c r="B32" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="27" t="s">
         <v>585</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="D32" s="27" t="s">
         <v>586</v>
       </c>
-      <c r="G30" s="30" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30" t="s">
-        <v>582</v>
-      </c>
-      <c r="B31" s="30" t="s">
+      <c r="E32" s="27" t="s">
+        <v>587</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="27" t="s">
+        <v>577</v>
+      </c>
+      <c r="B33" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="30" t="s">
-        <v>587</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>588</v>
-      </c>
-      <c r="F31" s="30" t="s">
+      <c r="C33" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>591</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>592</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="G33" s="27" t="s">
         <v>589</v>
-      </c>
-      <c r="G31" s="30" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="s">
-        <v>582</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>590</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>591</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>592</v>
-      </c>
-      <c r="F32" s="30" t="s">
-        <v>593</v>
-      </c>
-      <c r="G32" s="30" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30" t="s">
-        <v>582</v>
-      </c>
-      <c r="B33" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>595</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>596</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>597</v>
-      </c>
-      <c r="F33" s="30" t="s">
-        <v>598</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>594</v>
       </c>
     </row>
   </sheetData>
